--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEBC5014-9880-4DC5-A18C-799395A778E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E4F4D5-F4E1-4634-8AD2-2DFE562DFCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="274">
   <si>
     <t>OEM</t>
   </si>
@@ -782,6 +782,69 @@
   </si>
   <si>
     <t>High-speed heavy</t>
+  </si>
+  <si>
+    <t>GENERIC</t>
+  </si>
+  <si>
+    <t>ENGEL 40</t>
+  </si>
+  <si>
+    <t>Filled via engineering scaling model</t>
+  </si>
+  <si>
+    <t>ENGEL 50</t>
+  </si>
+  <si>
+    <t>ENGEL 80</t>
+  </si>
+  <si>
+    <t>ENGEL 100</t>
+  </si>
+  <si>
+    <t>ENGEL 130</t>
+  </si>
+  <si>
+    <t>ENGEL 160</t>
+  </si>
+  <si>
+    <t>ENGEL 180</t>
+  </si>
+  <si>
+    <t>ENGEL 200</t>
+  </si>
+  <si>
+    <t>ENGEL 220</t>
+  </si>
+  <si>
+    <t>ENGEL 280</t>
+  </si>
+  <si>
+    <t>ENGEL 380</t>
+  </si>
+  <si>
+    <t>ENGEL 450</t>
+  </si>
+  <si>
+    <t>ENGEL 550</t>
+  </si>
+  <si>
+    <t>ENGEL 700</t>
+  </si>
+  <si>
+    <t>ENGEL 900</t>
+  </si>
+  <si>
+    <t>ENGEL 1100</t>
+  </si>
+  <si>
+    <t>ENGEL 1500</t>
+  </si>
+  <si>
+    <t>ENGEL 2000</t>
+  </si>
+  <si>
+    <t>ENGEL 3000</t>
   </si>
 </sst>
 </file>
@@ -1144,8 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1159,7 +1221,7 @@
     <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1207,7 +1269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1251,7 +1313,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1295,7 +1357,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1401,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1383,7 +1445,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1412,7 +1474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1453,7 +1515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1494,7 +1556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1535,7 +1597,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1638,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1617,7 +1679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1658,7 +1720,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1699,7 +1761,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1740,7 +1802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1781,7 +1843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1822,7 +1884,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1863,7 +1925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1904,7 +1966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1945,7 +2007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1986,7 +2048,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2027,7 +2089,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2068,7 +2130,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -2109,7 +2171,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2150,7 +2212,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2191,7 +2253,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -2232,7 +2294,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -2273,7 +2335,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2314,7 +2376,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2355,7 +2417,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2396,7 +2458,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2437,7 +2499,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -2478,7 +2540,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -2519,7 +2581,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -2560,7 +2622,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -2601,7 +2663,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2642,7 +2704,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -2683,7 +2745,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -2724,7 +2786,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>96</v>
       </c>
@@ -2765,7 +2827,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>96</v>
       </c>
@@ -2806,7 +2868,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -2847,7 +2909,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>96</v>
       </c>
@@ -2888,7 +2950,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2929,7 +2991,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -2970,7 +3032,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -3011,7 +3073,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -3052,7 +3114,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -3093,7 +3155,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>96</v>
       </c>
@@ -3134,7 +3196,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -3175,7 +3237,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -3216,7 +3278,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -3257,7 +3319,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -3298,7 +3360,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>96</v>
       </c>
@@ -3339,7 +3401,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>96</v>
       </c>
@@ -3380,7 +3442,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>96</v>
       </c>
@@ -3421,7 +3483,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>96</v>
       </c>
@@ -3462,7 +3524,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>96</v>
       </c>
@@ -3503,7 +3565,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>96</v>
       </c>
@@ -3544,7 +3606,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>96</v>
       </c>
@@ -3585,7 +3647,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -3626,7 +3688,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -3667,7 +3729,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>96</v>
       </c>
@@ -3708,7 +3770,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>96</v>
       </c>
@@ -3749,7 +3811,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>96</v>
       </c>
@@ -3790,7 +3852,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -3831,7 +3893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>153</v>
       </c>
@@ -3872,7 +3934,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>153</v>
       </c>
@@ -3913,7 +3975,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>153</v>
       </c>
@@ -3954,7 +4016,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -3995,7 +4057,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>153</v>
       </c>
@@ -4036,7 +4098,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -4077,7 +4139,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>153</v>
       </c>
@@ -4118,7 +4180,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>153</v>
       </c>
@@ -4159,7 +4221,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>153</v>
       </c>
@@ -4200,7 +4262,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -4241,7 +4303,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -4282,7 +4344,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -4323,7 +4385,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>153</v>
       </c>
@@ -4364,7 +4426,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>153</v>
       </c>
@@ -4405,7 +4467,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>153</v>
       </c>
@@ -4446,7 +4508,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>153</v>
       </c>
@@ -4487,7 +4549,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>153</v>
       </c>
@@ -4528,7 +4590,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -4569,7 +4631,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>153</v>
       </c>
@@ -4610,7 +4672,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>153</v>
       </c>
@@ -4651,7 +4713,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -4692,7 +4754,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>153</v>
       </c>
@@ -4733,7 +4795,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>153</v>
       </c>
@@ -4774,7 +4836,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>153</v>
       </c>
@@ -4815,7 +4877,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>153</v>
       </c>
@@ -4856,7 +4918,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>153</v>
       </c>
@@ -4897,7 +4959,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>153</v>
       </c>
@@ -4938,7 +5000,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>153</v>
       </c>
@@ -5430,7 +5492,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>210</v>
       </c>
@@ -5471,7 +5533,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -5512,7 +5574,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -5553,7 +5615,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>210</v>
       </c>
@@ -5594,7 +5656,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>210</v>
       </c>
@@ -5635,7 +5697,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>210</v>
       </c>
@@ -5676,7 +5738,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>210</v>
       </c>
@@ -5717,7 +5779,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>210</v>
       </c>
@@ -5758,7 +5820,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>210</v>
       </c>
@@ -5799,7 +5861,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>210</v>
       </c>
@@ -5840,7 +5902,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>210</v>
       </c>
@@ -5881,7 +5943,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>210</v>
       </c>
@@ -5922,7 +5984,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>210</v>
       </c>
@@ -5963,7 +6025,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>210</v>
       </c>
@@ -6004,14 +6066,844 @@
         <v>252</v>
       </c>
     </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" t="s">
+        <v>253</v>
+      </c>
+      <c r="C119" t="s">
+        <v>254</v>
+      </c>
+      <c r="D119">
+        <v>40</v>
+      </c>
+      <c r="E119">
+        <v>442</v>
+      </c>
+      <c r="F119">
+        <v>442</v>
+      </c>
+      <c r="G119">
+        <v>375</v>
+      </c>
+      <c r="H119">
+        <v>375</v>
+      </c>
+      <c r="I119">
+        <v>795</v>
+      </c>
+      <c r="J119">
+        <v>176</v>
+      </c>
+      <c r="K119">
+        <v>530</v>
+      </c>
+      <c r="L119">
+        <v>353</v>
+      </c>
+      <c r="M119" t="s">
+        <v>255</v>
+      </c>
+      <c r="N119">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" t="s">
+        <v>253</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="D120">
+        <v>50</v>
+      </c>
+      <c r="E120">
+        <v>494</v>
+      </c>
+      <c r="F120">
+        <v>494</v>
+      </c>
+      <c r="G120">
+        <v>419</v>
+      </c>
+      <c r="H120">
+        <v>419</v>
+      </c>
+      <c r="I120">
+        <v>889</v>
+      </c>
+      <c r="J120">
+        <v>197</v>
+      </c>
+      <c r="K120">
+        <v>592</v>
+      </c>
+      <c r="L120">
+        <v>395</v>
+      </c>
+      <c r="M120" t="s">
+        <v>255</v>
+      </c>
+      <c r="N120">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>14</v>
+      </c>
+      <c r="B121" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" t="s">
+        <v>257</v>
+      </c>
+      <c r="D121">
+        <v>80</v>
+      </c>
+      <c r="E121">
+        <v>626</v>
+      </c>
+      <c r="F121">
+        <v>626</v>
+      </c>
+      <c r="G121">
+        <v>532</v>
+      </c>
+      <c r="H121">
+        <v>532</v>
+      </c>
+      <c r="I121">
+        <v>1126</v>
+      </c>
+      <c r="J121">
+        <v>250</v>
+      </c>
+      <c r="K121">
+        <v>751</v>
+      </c>
+      <c r="L121">
+        <v>500</v>
+      </c>
+      <c r="M121" t="s">
+        <v>255</v>
+      </c>
+      <c r="N121">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>14</v>
+      </c>
+      <c r="B122" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" t="s">
+        <v>258</v>
+      </c>
+      <c r="D122">
+        <v>100</v>
+      </c>
+      <c r="E122">
+        <v>700</v>
+      </c>
+      <c r="F122">
+        <v>700</v>
+      </c>
+      <c r="G122">
+        <v>595</v>
+      </c>
+      <c r="H122">
+        <v>595</v>
+      </c>
+      <c r="I122">
+        <v>1260</v>
+      </c>
+      <c r="J122">
+        <v>280</v>
+      </c>
+      <c r="K122">
+        <v>840</v>
+      </c>
+      <c r="L122">
+        <v>560</v>
+      </c>
+      <c r="M122" t="s">
+        <v>255</v>
+      </c>
+      <c r="N122">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" t="s">
+        <v>253</v>
+      </c>
+      <c r="C123" t="s">
+        <v>259</v>
+      </c>
+      <c r="D123">
+        <v>130</v>
+      </c>
+      <c r="E123">
+        <v>798</v>
+      </c>
+      <c r="F123">
+        <v>798</v>
+      </c>
+      <c r="G123">
+        <v>678</v>
+      </c>
+      <c r="H123">
+        <v>678</v>
+      </c>
+      <c r="I123">
+        <v>1436</v>
+      </c>
+      <c r="J123">
+        <v>319</v>
+      </c>
+      <c r="K123">
+        <v>957</v>
+      </c>
+      <c r="L123">
+        <v>638</v>
+      </c>
+      <c r="M123" t="s">
+        <v>255</v>
+      </c>
+      <c r="N123">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" t="s">
+        <v>260</v>
+      </c>
+      <c r="D124">
+        <v>160</v>
+      </c>
+      <c r="E124">
+        <v>885</v>
+      </c>
+      <c r="F124">
+        <v>885</v>
+      </c>
+      <c r="G124">
+        <v>752</v>
+      </c>
+      <c r="H124">
+        <v>752</v>
+      </c>
+      <c r="I124">
+        <v>1593</v>
+      </c>
+      <c r="J124">
+        <v>354</v>
+      </c>
+      <c r="K124">
+        <v>1062</v>
+      </c>
+      <c r="L124">
+        <v>708</v>
+      </c>
+      <c r="M124" t="s">
+        <v>255</v>
+      </c>
+      <c r="N124">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" t="s">
+        <v>253</v>
+      </c>
+      <c r="C125" t="s">
+        <v>261</v>
+      </c>
+      <c r="D125">
+        <v>180</v>
+      </c>
+      <c r="E125">
+        <v>939</v>
+      </c>
+      <c r="F125">
+        <v>939</v>
+      </c>
+      <c r="G125">
+        <v>798</v>
+      </c>
+      <c r="H125">
+        <v>798</v>
+      </c>
+      <c r="I125">
+        <v>1690</v>
+      </c>
+      <c r="J125">
+        <v>375</v>
+      </c>
+      <c r="K125">
+        <v>1126</v>
+      </c>
+      <c r="L125">
+        <v>751</v>
+      </c>
+      <c r="M125" t="s">
+        <v>255</v>
+      </c>
+      <c r="N125">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" t="s">
+        <v>262</v>
+      </c>
+      <c r="D126">
+        <v>200</v>
+      </c>
+      <c r="E126">
+        <v>989</v>
+      </c>
+      <c r="F126">
+        <v>989</v>
+      </c>
+      <c r="G126">
+        <v>840</v>
+      </c>
+      <c r="H126">
+        <v>840</v>
+      </c>
+      <c r="I126">
+        <v>1780</v>
+      </c>
+      <c r="J126">
+        <v>395</v>
+      </c>
+      <c r="K126">
+        <v>1186</v>
+      </c>
+      <c r="L126">
+        <v>791</v>
+      </c>
+      <c r="M126" t="s">
+        <v>255</v>
+      </c>
+      <c r="N126">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" t="s">
+        <v>253</v>
+      </c>
+      <c r="C127" t="s">
+        <v>263</v>
+      </c>
+      <c r="D127">
+        <v>220</v>
+      </c>
+      <c r="E127">
+        <v>1038</v>
+      </c>
+      <c r="F127">
+        <v>1038</v>
+      </c>
+      <c r="G127">
+        <v>882</v>
+      </c>
+      <c r="H127">
+        <v>882</v>
+      </c>
+      <c r="I127">
+        <v>1868</v>
+      </c>
+      <c r="J127">
+        <v>415</v>
+      </c>
+      <c r="K127">
+        <v>1245</v>
+      </c>
+      <c r="L127">
+        <v>830</v>
+      </c>
+      <c r="M127" t="s">
+        <v>255</v>
+      </c>
+      <c r="N127">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
+        <v>264</v>
+      </c>
+      <c r="D128">
+        <v>280</v>
+      </c>
+      <c r="E128">
+        <v>1171</v>
+      </c>
+      <c r="F128">
+        <v>1171</v>
+      </c>
+      <c r="G128">
+        <v>995</v>
+      </c>
+      <c r="H128">
+        <v>995</v>
+      </c>
+      <c r="I128">
+        <v>2107</v>
+      </c>
+      <c r="J128">
+        <v>468</v>
+      </c>
+      <c r="K128">
+        <v>1405</v>
+      </c>
+      <c r="L128">
+        <v>936</v>
+      </c>
+      <c r="M128" t="s">
+        <v>255</v>
+      </c>
+      <c r="N128">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129" t="s">
+        <v>265</v>
+      </c>
+      <c r="D129">
+        <v>380</v>
+      </c>
+      <c r="E129">
+        <v>1364</v>
+      </c>
+      <c r="F129">
+        <v>1364</v>
+      </c>
+      <c r="G129">
+        <v>1159</v>
+      </c>
+      <c r="H129">
+        <v>1159</v>
+      </c>
+      <c r="I129">
+        <v>2455</v>
+      </c>
+      <c r="J129">
+        <v>545</v>
+      </c>
+      <c r="K129">
+        <v>1636</v>
+      </c>
+      <c r="L129">
+        <v>1091</v>
+      </c>
+      <c r="M129" t="s">
+        <v>255</v>
+      </c>
+      <c r="N129">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" t="s">
+        <v>253</v>
+      </c>
+      <c r="C130" t="s">
+        <v>266</v>
+      </c>
+      <c r="D130">
+        <v>450</v>
+      </c>
+      <c r="E130">
+        <v>1484</v>
+      </c>
+      <c r="F130">
+        <v>1484</v>
+      </c>
+      <c r="G130">
+        <v>1261</v>
+      </c>
+      <c r="H130">
+        <v>1261</v>
+      </c>
+      <c r="I130">
+        <v>2671</v>
+      </c>
+      <c r="J130">
+        <v>593</v>
+      </c>
+      <c r="K130">
+        <v>1780</v>
+      </c>
+      <c r="L130">
+        <v>1187</v>
+      </c>
+      <c r="M130" t="s">
+        <v>255</v>
+      </c>
+      <c r="N130">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" t="s">
+        <v>253</v>
+      </c>
+      <c r="C131" t="s">
+        <v>267</v>
+      </c>
+      <c r="D131">
+        <v>550</v>
+      </c>
+      <c r="E131">
+        <v>1641</v>
+      </c>
+      <c r="F131">
+        <v>1641</v>
+      </c>
+      <c r="G131">
+        <v>1394</v>
+      </c>
+      <c r="H131">
+        <v>1394</v>
+      </c>
+      <c r="I131">
+        <v>2953</v>
+      </c>
+      <c r="J131">
+        <v>656</v>
+      </c>
+      <c r="K131">
+        <v>1969</v>
+      </c>
+      <c r="L131">
+        <v>1312</v>
+      </c>
+      <c r="M131" t="s">
+        <v>255</v>
+      </c>
+      <c r="N131">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" t="s">
+        <v>253</v>
+      </c>
+      <c r="C132" t="s">
+        <v>268</v>
+      </c>
+      <c r="D132">
+        <v>700</v>
+      </c>
+      <c r="E132">
+        <v>1852</v>
+      </c>
+      <c r="F132">
+        <v>1852</v>
+      </c>
+      <c r="G132">
+        <v>1574</v>
+      </c>
+      <c r="H132">
+        <v>1574</v>
+      </c>
+      <c r="I132">
+        <v>3333</v>
+      </c>
+      <c r="J132">
+        <v>740</v>
+      </c>
+      <c r="K132">
+        <v>2222</v>
+      </c>
+      <c r="L132">
+        <v>1481</v>
+      </c>
+      <c r="M132" t="s">
+        <v>255</v>
+      </c>
+      <c r="N132">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" t="s">
+        <v>253</v>
+      </c>
+      <c r="C133" t="s">
+        <v>269</v>
+      </c>
+      <c r="D133">
+        <v>900</v>
+      </c>
+      <c r="E133">
+        <v>2100</v>
+      </c>
+      <c r="F133">
+        <v>2100</v>
+      </c>
+      <c r="G133">
+        <v>1785</v>
+      </c>
+      <c r="H133">
+        <v>1785</v>
+      </c>
+      <c r="I133">
+        <v>3780</v>
+      </c>
+      <c r="J133">
+        <v>840</v>
+      </c>
+      <c r="K133">
+        <v>2520</v>
+      </c>
+      <c r="L133">
+        <v>1680</v>
+      </c>
+      <c r="M133" t="s">
+        <v>255</v>
+      </c>
+      <c r="N133">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>14</v>
+      </c>
+      <c r="B134" t="s">
+        <v>253</v>
+      </c>
+      <c r="C134" t="s">
+        <v>270</v>
+      </c>
+      <c r="D134">
+        <v>1100</v>
+      </c>
+      <c r="E134">
+        <v>2321</v>
+      </c>
+      <c r="F134">
+        <v>2321</v>
+      </c>
+      <c r="G134">
+        <v>1972</v>
+      </c>
+      <c r="H134">
+        <v>1972</v>
+      </c>
+      <c r="I134">
+        <v>4177</v>
+      </c>
+      <c r="J134">
+        <v>928</v>
+      </c>
+      <c r="K134">
+        <v>2785</v>
+      </c>
+      <c r="L134">
+        <v>1856</v>
+      </c>
+      <c r="M134" t="s">
+        <v>255</v>
+      </c>
+      <c r="N134">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>14</v>
+      </c>
+      <c r="B135" t="s">
+        <v>253</v>
+      </c>
+      <c r="C135" t="s">
+        <v>271</v>
+      </c>
+      <c r="D135">
+        <v>1500</v>
+      </c>
+      <c r="E135">
+        <v>2711</v>
+      </c>
+      <c r="F135">
+        <v>2711</v>
+      </c>
+      <c r="G135">
+        <v>2304</v>
+      </c>
+      <c r="H135">
+        <v>2304</v>
+      </c>
+      <c r="I135">
+        <v>4879</v>
+      </c>
+      <c r="J135">
+        <v>1084</v>
+      </c>
+      <c r="K135">
+        <v>3253</v>
+      </c>
+      <c r="L135">
+        <v>2168</v>
+      </c>
+      <c r="M135" t="s">
+        <v>255</v>
+      </c>
+      <c r="N135">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" t="s">
+        <v>253</v>
+      </c>
+      <c r="C136" t="s">
+        <v>272</v>
+      </c>
+      <c r="D136">
+        <v>2000</v>
+      </c>
+      <c r="E136">
+        <v>3130</v>
+      </c>
+      <c r="F136">
+        <v>3130</v>
+      </c>
+      <c r="G136">
+        <v>2660</v>
+      </c>
+      <c r="H136">
+        <v>2660</v>
+      </c>
+      <c r="I136">
+        <v>5634</v>
+      </c>
+      <c r="J136">
+        <v>1252</v>
+      </c>
+      <c r="K136">
+        <v>3756</v>
+      </c>
+      <c r="L136">
+        <v>2504</v>
+      </c>
+      <c r="M136" t="s">
+        <v>255</v>
+      </c>
+      <c r="N136">
+        <v>3756</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>14</v>
+      </c>
+      <c r="B137" t="s">
+        <v>253</v>
+      </c>
+      <c r="C137" t="s">
+        <v>273</v>
+      </c>
+      <c r="D137">
+        <v>3000</v>
+      </c>
+      <c r="E137">
+        <v>3834</v>
+      </c>
+      <c r="F137">
+        <v>3834</v>
+      </c>
+      <c r="G137">
+        <v>3258</v>
+      </c>
+      <c r="H137">
+        <v>3258</v>
+      </c>
+      <c r="I137">
+        <v>6901</v>
+      </c>
+      <c r="J137">
+        <v>1533</v>
+      </c>
+      <c r="K137">
+        <v>4600</v>
+      </c>
+      <c r="L137">
+        <v>3067</v>
+      </c>
+      <c r="M137" t="s">
+        <v>255</v>
+      </c>
+      <c r="N137">
+        <v>4600</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N118" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ELION"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N118" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huanger9\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1488E8E0-68A9-49D3-90F2-E52FDCD77911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C8A395-37EE-435C-A60F-42E0472D6FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20052" yWindow="-288" windowWidth="20376" windowHeight="12096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
   <si>
     <t>OEM</t>
   </si>
@@ -676,9 +689,6 @@
     <t>Small-mid</t>
   </si>
   <si>
-    <t>ELION 800</t>
-  </si>
-  <si>
     <t>ELION 1000</t>
   </si>
   <si>
@@ -848,13 +858,22 @@
   </si>
   <si>
     <t>ENGEL 3000</t>
+  </si>
+  <si>
+    <t>ELION 800-N60</t>
+  </si>
+  <si>
+    <t>ELION 800-N130</t>
+  </si>
+  <si>
+    <t>ELION 800-N270</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -866,6 +885,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1210,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1316,6 +1341,10 @@
       <c r="L2">
         <v>300</v>
       </c>
+      <c r="M2">
+        <f>3.14*O2*O2/4*L2/1000</f>
+        <v>56.578874999999996</v>
+      </c>
       <c r="N2">
         <v>90</v>
       </c>
@@ -2976,10 +3005,10 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" t="s">
         <v>255</v>
-      </c>
-      <c r="C38" t="s">
-        <v>256</v>
       </c>
       <c r="D38">
         <v>40</v>
@@ -3018,7 +3047,7 @@
         <v>12.6</v>
       </c>
       <c r="P38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3026,10 +3055,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D39">
         <v>50</v>
@@ -3068,7 +3097,7 @@
         <v>14.1</v>
       </c>
       <c r="P39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -3076,10 +3105,10 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40">
         <v>80</v>
@@ -3118,7 +3147,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="P40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3126,10 +3155,10 @@
         <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -3168,7 +3197,7 @@
         <v>20</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -3176,10 +3205,10 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D42">
         <v>130</v>
@@ -3218,7 +3247,7 @@
         <v>22.8</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3226,10 +3255,10 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D43">
         <v>160</v>
@@ -3268,7 +3297,7 @@
         <v>25.3</v>
       </c>
       <c r="P43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -3276,10 +3305,10 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D44">
         <v>180</v>
@@ -3318,7 +3347,7 @@
         <v>26.8</v>
       </c>
       <c r="P44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3326,10 +3355,10 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D45">
         <v>200</v>
@@ -3368,7 +3397,7 @@
         <v>28.3</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3376,10 +3405,10 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D46">
         <v>220</v>
@@ -3418,7 +3447,7 @@
         <v>29.7</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3426,10 +3455,10 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D47">
         <v>280</v>
@@ -3468,7 +3497,7 @@
         <v>33.5</v>
       </c>
       <c r="P47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -3476,10 +3505,10 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D48">
         <v>380</v>
@@ -3518,7 +3547,7 @@
         <v>39</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -3526,10 +3555,10 @@
         <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D49">
         <v>450</v>
@@ -3568,7 +3597,7 @@
         <v>42.4</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3576,10 +3605,10 @@
         <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D50">
         <v>550</v>
@@ -3618,7 +3647,7 @@
         <v>46.9</v>
       </c>
       <c r="P50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3626,10 +3655,10 @@
         <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D51">
         <v>700</v>
@@ -3668,7 +3697,7 @@
         <v>52.9</v>
       </c>
       <c r="P51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3676,10 +3705,10 @@
         <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D52">
         <v>900</v>
@@ -3718,7 +3747,7 @@
         <v>60</v>
       </c>
       <c r="P52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -3726,10 +3755,10 @@
         <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D53">
         <v>1100</v>
@@ -3768,7 +3797,7 @@
         <v>66.3</v>
       </c>
       <c r="P53" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -3776,10 +3805,10 @@
         <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D54">
         <v>1500</v>
@@ -3818,7 +3847,7 @@
         <v>77.5</v>
       </c>
       <c r="P54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -3826,10 +3855,10 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D55">
         <v>2000</v>
@@ -3868,7 +3897,7 @@
         <v>89.4</v>
       </c>
       <c r="P55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -3876,10 +3905,10 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D56">
         <v>3000</v>
@@ -3918,7 +3947,7 @@
         <v>109.5</v>
       </c>
       <c r="P56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -5339,7 +5368,7 @@
         <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="D87">
         <v>85</v>
@@ -5360,19 +5389,22 @@
         <v>650</v>
       </c>
       <c r="J87">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K87">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="L87">
-        <v>400</v>
+        <v>350</v>
+      </c>
+      <c r="M87">
+        <v>200</v>
       </c>
       <c r="N87">
-        <v>127.5</v>
+        <v>47</v>
       </c>
       <c r="O87">
-        <v>18.399999999999999</v>
+        <v>16</v>
       </c>
       <c r="P87" t="s">
         <v>215</v>
@@ -5386,43 +5418,46 @@
         <v>213</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="D88">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E88">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="F88">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G88">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="H88">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="I88">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="J88">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K88">
         <v>500</v>
       </c>
       <c r="L88">
-        <v>450</v>
+        <v>350</v>
+      </c>
+      <c r="M88">
+        <v>200</v>
       </c>
       <c r="N88">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="O88">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P88" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
@@ -5433,43 +5468,46 @@
         <v>213</v>
       </c>
       <c r="C89" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="D89">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="E89">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F89">
-        <v>700</v>
+        <v>621</v>
       </c>
       <c r="G89">
+        <v>410</v>
+      </c>
+      <c r="H89">
+        <v>410</v>
+      </c>
+      <c r="I89">
+        <v>650</v>
+      </c>
+      <c r="J89">
+        <v>200</v>
+      </c>
+      <c r="K89">
         <v>500</v>
       </c>
-      <c r="H89">
-        <v>500</v>
-      </c>
-      <c r="I89">
-        <v>800</v>
-      </c>
-      <c r="J89">
-        <v>250</v>
-      </c>
-      <c r="K89">
-        <v>550</v>
-      </c>
       <c r="L89">
-        <v>500</v>
+        <v>350</v>
+      </c>
+      <c r="M89">
+        <v>200</v>
       </c>
       <c r="N89">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="O89">
-        <v>22.8</v>
+        <v>18</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
@@ -5480,43 +5518,43 @@
         <v>213</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D90">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="E90">
-        <v>820</v>
+        <v>680</v>
       </c>
       <c r="F90">
-        <v>760</v>
+        <v>620</v>
       </c>
       <c r="G90">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="H90">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="I90">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="J90">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="K90">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L90">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="N90">
-        <v>285</v>
+        <v>165</v>
       </c>
       <c r="O90">
-        <v>27.6</v>
+        <v>21</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
@@ -5527,43 +5565,43 @@
         <v>213</v>
       </c>
       <c r="C91" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D91">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="E91">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F91">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="G91">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="H91">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="I91">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J91">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K91">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L91">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N91">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="O91">
-        <v>31</v>
+        <v>22.8</v>
       </c>
       <c r="P91" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
@@ -5574,43 +5612,43 @@
         <v>213</v>
       </c>
       <c r="C92" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D92">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="E92">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="F92">
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="G92">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="H92">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="I92">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J92">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K92">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L92">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="N92">
-        <v>465</v>
+        <v>285</v>
       </c>
       <c r="O92">
-        <v>35.200000000000003</v>
+        <v>27.6</v>
       </c>
       <c r="P92" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
@@ -5621,43 +5659,43 @@
         <v>213</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D93">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="E93">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="F93">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="G93">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H93">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I93">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J93">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K93">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L93">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N93">
-        <v>525</v>
+        <v>360</v>
       </c>
       <c r="O93">
-        <v>37.4</v>
+        <v>31</v>
       </c>
       <c r="P93" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
@@ -5668,43 +5706,43 @@
         <v>213</v>
       </c>
       <c r="C94" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D94">
-        <v>460</v>
+        <v>310</v>
       </c>
       <c r="E94">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="F94">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="G94">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="H94">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="I94">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="J94">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="K94">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="L94">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="N94">
-        <v>690</v>
+        <v>465</v>
       </c>
       <c r="O94">
-        <v>42.9</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="P94" t="s">
-        <v>73</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
@@ -5715,43 +5753,43 @@
         <v>213</v>
       </c>
       <c r="C95" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D95">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E95">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F95">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G95">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H95">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I95">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J95">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K95">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L95">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N95">
-        <v>825</v>
+        <v>525</v>
       </c>
       <c r="O95">
-        <v>46.9</v>
+        <v>37.4</v>
       </c>
       <c r="P95" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
@@ -5759,46 +5797,46 @@
         <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D96">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="E96">
-        <v>750</v>
+        <v>1150</v>
       </c>
       <c r="F96">
-        <v>700</v>
+        <v>1050</v>
       </c>
       <c r="G96">
-        <v>500</v>
+        <v>820</v>
       </c>
       <c r="H96">
-        <v>500</v>
+        <v>820</v>
       </c>
       <c r="I96">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="J96">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K96">
-        <v>550</v>
+        <v>900</v>
       </c>
       <c r="L96">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="N96">
-        <v>195</v>
+        <v>690</v>
       </c>
       <c r="O96">
-        <v>22.8</v>
+        <v>42.9</v>
       </c>
       <c r="P96" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
@@ -5806,46 +5844,46 @@
         <v>212</v>
       </c>
       <c r="B97" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C97" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D97">
-        <v>190</v>
+        <v>550</v>
       </c>
       <c r="E97">
-        <v>820</v>
+        <v>1250</v>
       </c>
       <c r="F97">
-        <v>760</v>
+        <v>1150</v>
       </c>
       <c r="G97">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="H97">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="I97">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="J97">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K97">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L97">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="N97">
-        <v>285</v>
+        <v>825</v>
       </c>
       <c r="O97">
-        <v>27.6</v>
+        <v>46.9</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
@@ -5853,46 +5891,46 @@
         <v>212</v>
       </c>
       <c r="B98" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" t="s">
         <v>228</v>
       </c>
-      <c r="C98" t="s">
-        <v>233</v>
-      </c>
       <c r="D98">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="E98">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F98">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="G98">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="H98">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="I98">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J98">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K98">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L98">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N98">
-        <v>360</v>
+        <v>195</v>
       </c>
       <c r="O98">
-        <v>31</v>
+        <v>22.8</v>
       </c>
       <c r="P98" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
@@ -5900,46 +5938,46 @@
         <v>212</v>
       </c>
       <c r="B99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C99" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D99">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="E99">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="F99">
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="G99">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="H99">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="I99">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J99">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K99">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L99">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="N99">
-        <v>465</v>
+        <v>285</v>
       </c>
       <c r="O99">
-        <v>35.200000000000003</v>
+        <v>27.6</v>
       </c>
       <c r="P99" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
@@ -5947,46 +5985,46 @@
         <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D100">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="E100">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="F100">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="G100">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H100">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I100">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J100">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K100">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L100">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N100">
-        <v>525</v>
+        <v>360</v>
       </c>
       <c r="O100">
-        <v>37.4</v>
+        <v>31</v>
       </c>
       <c r="P100" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
@@ -5994,46 +6032,46 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C101" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D101">
-        <v>460</v>
+        <v>310</v>
       </c>
       <c r="E101">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="F101">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="G101">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="H101">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="I101">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="J101">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="K101">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="L101">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="N101">
-        <v>690</v>
+        <v>465</v>
       </c>
       <c r="O101">
-        <v>42.9</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
@@ -6041,46 +6079,46 @@
         <v>212</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D102">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E102">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F102">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G102">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H102">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I102">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J102">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K102">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L102">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N102">
-        <v>825</v>
+        <v>525</v>
       </c>
       <c r="O102">
-        <v>46.9</v>
+        <v>37.4</v>
       </c>
       <c r="P102" t="s">
-        <v>88</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
@@ -6088,46 +6126,46 @@
         <v>212</v>
       </c>
       <c r="B103" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C103" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D103">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="E103">
-        <v>880</v>
+        <v>1150</v>
       </c>
       <c r="F103">
-        <v>810</v>
+        <v>1050</v>
       </c>
       <c r="G103">
-        <v>610</v>
+        <v>820</v>
       </c>
       <c r="H103">
-        <v>610</v>
+        <v>820</v>
       </c>
       <c r="I103">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="J103">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K103">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="L103">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="N103">
-        <v>330</v>
+        <v>690</v>
       </c>
       <c r="O103">
-        <v>29.7</v>
+        <v>42.9</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
@@ -6135,46 +6173,46 @@
         <v>212</v>
       </c>
       <c r="B104" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C104" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D104">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="E104">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="F104">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="G104">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="H104">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="I104">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J104">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K104">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="L104">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="N104">
-        <v>525</v>
+        <v>825</v>
       </c>
       <c r="O104">
-        <v>37.4</v>
+        <v>46.9</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
@@ -6182,46 +6220,46 @@
         <v>212</v>
       </c>
       <c r="B105" t="s">
+        <v>240</v>
+      </c>
+      <c r="C105" t="s">
         <v>241</v>
       </c>
-      <c r="C105" t="s">
-        <v>246</v>
-      </c>
       <c r="D105">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="E105">
-        <v>1150</v>
+        <v>880</v>
       </c>
       <c r="F105">
-        <v>1050</v>
+        <v>810</v>
       </c>
       <c r="G105">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="H105">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="I105">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J105">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K105">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L105">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N105">
-        <v>675</v>
+        <v>330</v>
       </c>
       <c r="O105">
-        <v>42.4</v>
+        <v>29.7</v>
       </c>
       <c r="P105" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
@@ -6229,46 +6267,46 @@
         <v>212</v>
       </c>
       <c r="B106" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C106" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D106">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E106">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F106">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G106">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H106">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I106">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J106">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K106">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L106">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N106">
-        <v>825</v>
+        <v>525</v>
       </c>
       <c r="O106">
-        <v>46.9</v>
+        <v>37.4</v>
       </c>
       <c r="P106" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
@@ -6276,46 +6314,46 @@
         <v>212</v>
       </c>
       <c r="B107" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C107" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D107">
-        <v>240</v>
+        <v>450</v>
       </c>
       <c r="E107">
+        <v>1150</v>
+      </c>
+      <c r="F107">
+        <v>1050</v>
+      </c>
+      <c r="G107">
+        <v>820</v>
+      </c>
+      <c r="H107">
+        <v>820</v>
+      </c>
+      <c r="I107">
+        <v>1300</v>
+      </c>
+      <c r="J107">
+        <v>400</v>
+      </c>
+      <c r="K107">
         <v>900</v>
       </c>
-      <c r="F107">
-        <v>830</v>
-      </c>
-      <c r="G107">
-        <v>610</v>
-      </c>
-      <c r="H107">
-        <v>610</v>
-      </c>
-      <c r="I107">
-        <v>1000</v>
-      </c>
-      <c r="J107">
-        <v>300</v>
-      </c>
-      <c r="K107">
-        <v>700</v>
-      </c>
       <c r="L107">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="N107">
-        <v>360</v>
+        <v>675</v>
       </c>
       <c r="O107">
-        <v>31</v>
+        <v>42.4</v>
       </c>
       <c r="P107" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
@@ -6323,46 +6361,46 @@
         <v>212</v>
       </c>
       <c r="B108" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C108" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D108">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="E108">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="F108">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="G108">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="H108">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="I108">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J108">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K108">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="L108">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="N108">
-        <v>525</v>
+        <v>825</v>
       </c>
       <c r="O108">
-        <v>37.4</v>
+        <v>46.9</v>
       </c>
       <c r="P108" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
@@ -6370,140 +6408,140 @@
         <v>212</v>
       </c>
       <c r="B109" t="s">
+        <v>249</v>
+      </c>
+      <c r="C109" t="s">
         <v>250</v>
       </c>
-      <c r="C109" t="s">
-        <v>253</v>
-      </c>
       <c r="D109">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="E109">
-        <v>1150</v>
+        <v>900</v>
       </c>
       <c r="F109">
-        <v>1050</v>
+        <v>830</v>
       </c>
       <c r="G109">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="H109">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="I109">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J109">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K109">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L109">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N109">
-        <v>690</v>
+        <v>360</v>
       </c>
       <c r="O109">
-        <v>42.9</v>
+        <v>31</v>
       </c>
       <c r="P109" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>249</v>
       </c>
       <c r="C110" t="s">
-        <v>100</v>
+        <v>251</v>
       </c>
       <c r="D110">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="E110">
-        <v>560</v>
+        <v>1050</v>
       </c>
       <c r="F110">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="G110">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="H110">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="I110">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="J110">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K110">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="L110">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="N110">
-        <v>82.5</v>
+        <v>525</v>
       </c>
       <c r="O110">
-        <v>14.8</v>
+        <v>37.4</v>
       </c>
       <c r="P110" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>249</v>
       </c>
       <c r="C111" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="D111">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="E111">
-        <v>630</v>
+        <v>1150</v>
       </c>
       <c r="F111">
-        <v>580</v>
+        <v>1050</v>
       </c>
       <c r="G111">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="H111">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="I111">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="J111">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K111">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="L111">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="N111">
-        <v>112.5</v>
+        <v>690</v>
       </c>
       <c r="O111">
-        <v>17.3</v>
+        <v>42.9</v>
       </c>
       <c r="P111" t="s">
-        <v>103</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
@@ -6514,43 +6552,43 @@
         <v>99</v>
       </c>
       <c r="C112" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D112">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="E112">
-        <v>750</v>
+        <v>560</v>
       </c>
       <c r="F112">
-        <v>680</v>
+        <v>510</v>
       </c>
       <c r="G112">
-        <v>510</v>
+        <v>360</v>
       </c>
       <c r="H112">
-        <v>510</v>
+        <v>360</v>
       </c>
       <c r="I112">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J112">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K112">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="L112">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="N112">
-        <v>214.5</v>
+        <v>82.5</v>
       </c>
       <c r="O112">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
       <c r="P112" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
@@ -6561,43 +6599,43 @@
         <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D113">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="E113">
-        <v>830</v>
+        <v>630</v>
       </c>
       <c r="F113">
-        <v>760</v>
+        <v>580</v>
       </c>
       <c r="G113">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="H113">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="I113">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J113">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K113">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="L113">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="N113">
-        <v>297</v>
+        <v>112.5</v>
       </c>
       <c r="O113">
-        <v>28.1</v>
+        <v>17.3</v>
       </c>
       <c r="P113" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
@@ -6608,43 +6646,43 @@
         <v>99</v>
       </c>
       <c r="C114" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D114">
-        <v>308</v>
+        <v>143</v>
       </c>
       <c r="E114">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F114">
-        <v>840</v>
+        <v>680</v>
       </c>
       <c r="G114">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="H114">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="I114">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J114">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K114">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L114">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N114">
-        <v>462</v>
+        <v>214.5</v>
       </c>
       <c r="O114">
-        <v>35.1</v>
+        <v>23.9</v>
       </c>
       <c r="P114" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
@@ -6655,43 +6693,43 @@
         <v>99</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D115">
-        <v>385</v>
+        <v>198</v>
       </c>
       <c r="E115">
-        <v>1020</v>
+        <v>830</v>
       </c>
       <c r="F115">
-        <v>950</v>
+        <v>760</v>
       </c>
       <c r="G115">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="H115">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="I115">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J115">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K115">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="L115">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N115">
-        <v>577.5</v>
+        <v>297</v>
       </c>
       <c r="O115">
-        <v>39.200000000000003</v>
+        <v>28.1</v>
       </c>
       <c r="P115" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
@@ -6702,43 +6740,43 @@
         <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D116">
-        <v>495</v>
+        <v>308</v>
       </c>
       <c r="E116">
-        <v>1150</v>
+        <v>900</v>
       </c>
       <c r="F116">
-        <v>1050</v>
+        <v>840</v>
       </c>
       <c r="G116">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="H116">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="I116">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J116">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K116">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L116">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N116">
-        <v>742.5</v>
+        <v>462</v>
       </c>
       <c r="O116">
-        <v>44.5</v>
+        <v>35.1</v>
       </c>
       <c r="P116" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
@@ -6749,43 +6787,43 @@
         <v>99</v>
       </c>
       <c r="C117" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D117">
-        <v>550</v>
+        <v>385</v>
       </c>
       <c r="E117">
-        <v>1250</v>
+        <v>1020</v>
       </c>
       <c r="F117">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G117">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H117">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I117">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J117">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="K117">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L117">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N117">
-        <v>825</v>
+        <v>577.5</v>
       </c>
       <c r="O117">
-        <v>46.9</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="P117" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
@@ -6793,46 +6831,46 @@
         <v>98</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C118" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D118">
-        <v>143</v>
+        <v>495</v>
       </c>
       <c r="E118">
-        <v>750</v>
+        <v>1150</v>
       </c>
       <c r="F118">
-        <v>680</v>
+        <v>1050</v>
       </c>
       <c r="G118">
-        <v>510</v>
+        <v>820</v>
       </c>
       <c r="H118">
-        <v>510</v>
+        <v>820</v>
       </c>
       <c r="I118">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="J118">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="K118">
-        <v>550</v>
+        <v>900</v>
       </c>
       <c r="L118">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="N118">
-        <v>214.5</v>
+        <v>742.5</v>
       </c>
       <c r="O118">
-        <v>23.9</v>
+        <v>44.5</v>
       </c>
       <c r="P118" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
@@ -6840,46 +6878,46 @@
         <v>98</v>
       </c>
       <c r="B119" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C119" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D119">
-        <v>198</v>
+        <v>550</v>
       </c>
       <c r="E119">
-        <v>830</v>
+        <v>1250</v>
       </c>
       <c r="F119">
-        <v>760</v>
+        <v>1150</v>
       </c>
       <c r="G119">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="H119">
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="I119">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="J119">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K119">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L119">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="N119">
-        <v>297</v>
+        <v>825</v>
       </c>
       <c r="O119">
-        <v>28.1</v>
+        <v>46.9</v>
       </c>
       <c r="P119" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
@@ -6890,43 +6928,43 @@
         <v>114</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D120">
-        <v>242</v>
+        <v>143</v>
       </c>
       <c r="E120">
-        <v>880</v>
+        <v>750</v>
       </c>
       <c r="F120">
-        <v>810</v>
+        <v>680</v>
       </c>
       <c r="G120">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="H120">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="I120">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J120">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K120">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L120">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N120">
-        <v>363</v>
+        <v>214.5</v>
       </c>
       <c r="O120">
-        <v>31.1</v>
+        <v>23.9</v>
       </c>
       <c r="P120" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
@@ -6937,43 +6975,43 @@
         <v>114</v>
       </c>
       <c r="C121" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D121">
-        <v>308</v>
+        <v>198</v>
       </c>
       <c r="E121">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="F121">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="G121">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="H121">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="I121">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J121">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K121">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L121">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="N121">
-        <v>462</v>
+        <v>297</v>
       </c>
       <c r="O121">
-        <v>35.1</v>
+        <v>28.1</v>
       </c>
       <c r="P121" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
@@ -6984,43 +7022,43 @@
         <v>114</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D122">
-        <v>385</v>
+        <v>242</v>
       </c>
       <c r="E122">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="F122">
-        <v>950</v>
+        <v>810</v>
       </c>
       <c r="G122">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H122">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I122">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J122">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K122">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L122">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N122">
-        <v>577.5</v>
+        <v>363</v>
       </c>
       <c r="O122">
-        <v>39.200000000000003</v>
+        <v>31.1</v>
       </c>
       <c r="P122" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
@@ -7028,46 +7066,46 @@
         <v>98</v>
       </c>
       <c r="B123" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C123" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D123">
-        <v>33</v>
+        <v>308</v>
       </c>
       <c r="E123">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="F123">
-        <v>420</v>
+        <v>850</v>
       </c>
       <c r="G123">
-        <v>300</v>
+        <v>660</v>
       </c>
       <c r="H123">
-        <v>300</v>
+        <v>660</v>
       </c>
       <c r="I123">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="J123">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="K123">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="L123">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="N123">
-        <v>49.5</v>
+        <v>462</v>
       </c>
       <c r="O123">
-        <v>11.5</v>
+        <v>35.1</v>
       </c>
       <c r="P123" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
@@ -7075,46 +7113,46 @@
         <v>98</v>
       </c>
       <c r="B124" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C124" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D124">
-        <v>55</v>
+        <v>385</v>
       </c>
       <c r="E124">
-        <v>560</v>
+        <v>1050</v>
       </c>
       <c r="F124">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="G124">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="H124">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="I124">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="J124">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K124">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="L124">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="N124">
-        <v>82.5</v>
+        <v>577.5</v>
       </c>
       <c r="O124">
-        <v>14.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="P124" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
@@ -7125,43 +7163,43 @@
         <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D125">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E125">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="F125">
-        <v>580</v>
+        <v>420</v>
       </c>
       <c r="G125">
-        <v>410</v>
+        <v>300</v>
       </c>
       <c r="H125">
-        <v>410</v>
+        <v>300</v>
       </c>
       <c r="I125">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J125">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K125">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="L125">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N125">
-        <v>112.5</v>
+        <v>49.5</v>
       </c>
       <c r="O125">
-        <v>17.3</v>
+        <v>11.5</v>
       </c>
       <c r="P125" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
@@ -7172,43 +7210,43 @@
         <v>125</v>
       </c>
       <c r="C126" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D126">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="E126">
-        <v>750</v>
+        <v>560</v>
       </c>
       <c r="F126">
-        <v>680</v>
+        <v>510</v>
       </c>
       <c r="G126">
-        <v>510</v>
+        <v>360</v>
       </c>
       <c r="H126">
-        <v>510</v>
+        <v>360</v>
       </c>
       <c r="I126">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J126">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K126">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="L126">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="N126">
-        <v>214.5</v>
+        <v>82.5</v>
       </c>
       <c r="O126">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
       <c r="P126" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
@@ -7219,43 +7257,43 @@
         <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D127">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="E127">
-        <v>830</v>
+        <v>630</v>
       </c>
       <c r="F127">
-        <v>760</v>
+        <v>580</v>
       </c>
       <c r="G127">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="H127">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="I127">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J127">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K127">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="L127">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="N127">
-        <v>297</v>
+        <v>112.5</v>
       </c>
       <c r="O127">
-        <v>28.1</v>
+        <v>17.3</v>
       </c>
       <c r="P127" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
@@ -7266,43 +7304,43 @@
         <v>125</v>
       </c>
       <c r="C128" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D128">
-        <v>308</v>
+        <v>143</v>
       </c>
       <c r="E128">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F128">
-        <v>840</v>
+        <v>680</v>
       </c>
       <c r="G128">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="H128">
-        <v>610</v>
+        <v>510</v>
       </c>
       <c r="I128">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J128">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K128">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L128">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N128">
-        <v>462</v>
+        <v>214.5</v>
       </c>
       <c r="O128">
-        <v>35.1</v>
+        <v>23.9</v>
       </c>
       <c r="P128" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
@@ -7313,43 +7351,43 @@
         <v>125</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D129">
-        <v>385</v>
+        <v>198</v>
       </c>
       <c r="E129">
-        <v>1020</v>
+        <v>830</v>
       </c>
       <c r="F129">
-        <v>950</v>
+        <v>760</v>
       </c>
       <c r="G129">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="H129">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="I129">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J129">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K129">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="L129">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N129">
-        <v>577.5</v>
+        <v>297</v>
       </c>
       <c r="O129">
-        <v>39.200000000000003</v>
+        <v>28.1</v>
       </c>
       <c r="P129" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
@@ -7357,19 +7395,19 @@
         <v>98</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D130">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="E130">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="F130">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="G130">
         <v>610</v>
@@ -7390,13 +7428,13 @@
         <v>700</v>
       </c>
       <c r="N130">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="O130">
-        <v>29.7</v>
+        <v>35.1</v>
       </c>
       <c r="P130" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
@@ -7404,16 +7442,16 @@
         <v>98</v>
       </c>
       <c r="B131" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C131" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D131">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="E131">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="F131">
         <v>950</v>
@@ -7428,7 +7466,7 @@
         <v>1200</v>
       </c>
       <c r="J131">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="K131">
         <v>800</v>
@@ -7437,13 +7475,13 @@
         <v>800</v>
       </c>
       <c r="N131">
-        <v>525</v>
+        <v>577.5</v>
       </c>
       <c r="O131">
-        <v>37.4</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="P131" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
@@ -7454,43 +7492,43 @@
         <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D132">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="E132">
-        <v>1150</v>
+        <v>880</v>
       </c>
       <c r="F132">
-        <v>1050</v>
+        <v>810</v>
       </c>
       <c r="G132">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="H132">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="I132">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J132">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K132">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L132">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N132">
-        <v>675</v>
+        <v>330</v>
       </c>
       <c r="O132">
-        <v>42.4</v>
+        <v>29.7</v>
       </c>
       <c r="P132" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
@@ -7501,43 +7539,43 @@
         <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D133">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E133">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F133">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G133">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H133">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I133">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J133">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K133">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L133">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N133">
-        <v>750</v>
+        <v>525</v>
       </c>
       <c r="O133">
-        <v>44.7</v>
+        <v>37.4</v>
       </c>
       <c r="P133" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
@@ -7545,46 +7583,46 @@
         <v>98</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D134">
-        <v>231</v>
+        <v>450</v>
       </c>
       <c r="E134">
-        <v>880</v>
+        <v>1150</v>
       </c>
       <c r="F134">
-        <v>810</v>
+        <v>1050</v>
       </c>
       <c r="G134">
-        <v>610</v>
+        <v>820</v>
       </c>
       <c r="H134">
-        <v>610</v>
+        <v>820</v>
       </c>
       <c r="I134">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="J134">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K134">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="L134">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="N134">
-        <v>346.5</v>
+        <v>675</v>
       </c>
       <c r="O134">
-        <v>30.4</v>
+        <v>42.4</v>
       </c>
       <c r="P134" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
@@ -7592,46 +7630,46 @@
         <v>98</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C135" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D135">
-        <v>308</v>
+        <v>500</v>
       </c>
       <c r="E135">
-        <v>950</v>
+        <v>1250</v>
       </c>
       <c r="F135">
-        <v>850</v>
+        <v>1150</v>
       </c>
       <c r="G135">
-        <v>660</v>
+        <v>920</v>
       </c>
       <c r="H135">
-        <v>660</v>
+        <v>920</v>
       </c>
       <c r="I135">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="J135">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="K135">
+        <v>1000</v>
+      </c>
+      <c r="L135">
+        <v>1000</v>
+      </c>
+      <c r="N135">
         <v>750</v>
       </c>
-      <c r="L135">
-        <v>750</v>
-      </c>
-      <c r="N135">
-        <v>462</v>
-      </c>
       <c r="O135">
-        <v>35.1</v>
+        <v>44.7</v>
       </c>
       <c r="P135" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
@@ -7642,43 +7680,43 @@
         <v>147</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D136">
-        <v>385</v>
+        <v>231</v>
       </c>
       <c r="E136">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="F136">
-        <v>950</v>
+        <v>810</v>
       </c>
       <c r="G136">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H136">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I136">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J136">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K136">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L136">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N136">
-        <v>577.5</v>
+        <v>346.5</v>
       </c>
       <c r="O136">
-        <v>39.200000000000003</v>
+        <v>30.4</v>
       </c>
       <c r="P136" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
@@ -7689,49 +7727,144 @@
         <v>147</v>
       </c>
       <c r="C137" t="s">
+        <v>150</v>
+      </c>
+      <c r="D137">
+        <v>308</v>
+      </c>
+      <c r="E137">
+        <v>950</v>
+      </c>
+      <c r="F137">
+        <v>850</v>
+      </c>
+      <c r="G137">
+        <v>660</v>
+      </c>
+      <c r="H137">
+        <v>660</v>
+      </c>
+      <c r="I137">
+        <v>1100</v>
+      </c>
+      <c r="J137">
+        <v>350</v>
+      </c>
+      <c r="K137">
+        <v>750</v>
+      </c>
+      <c r="L137">
+        <v>750</v>
+      </c>
+      <c r="N137">
+        <v>462</v>
+      </c>
+      <c r="O137">
+        <v>35.1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>98</v>
+      </c>
+      <c r="B138" t="s">
+        <v>147</v>
+      </c>
+      <c r="C138" t="s">
+        <v>152</v>
+      </c>
+      <c r="D138">
+        <v>385</v>
+      </c>
+      <c r="E138">
+        <v>1050</v>
+      </c>
+      <c r="F138">
+        <v>950</v>
+      </c>
+      <c r="G138">
+        <v>710</v>
+      </c>
+      <c r="H138">
+        <v>710</v>
+      </c>
+      <c r="I138">
+        <v>1200</v>
+      </c>
+      <c r="J138">
+        <v>400</v>
+      </c>
+      <c r="K138">
+        <v>800</v>
+      </c>
+      <c r="L138">
+        <v>800</v>
+      </c>
+      <c r="N138">
+        <v>577.5</v>
+      </c>
+      <c r="O138">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="P138" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>98</v>
+      </c>
+      <c r="B139" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" t="s">
         <v>153</v>
       </c>
-      <c r="D137">
+      <c r="D139">
         <v>550</v>
       </c>
-      <c r="E137">
+      <c r="E139">
         <v>1250</v>
       </c>
-      <c r="F137">
+      <c r="F139">
         <v>1150</v>
       </c>
-      <c r="G137">
+      <c r="G139">
         <v>920</v>
       </c>
-      <c r="H137">
+      <c r="H139">
         <v>920</v>
       </c>
-      <c r="I137">
+      <c r="I139">
         <v>1400</v>
       </c>
-      <c r="J137">
+      <c r="J139">
         <v>450</v>
       </c>
-      <c r="K137">
+      <c r="K139">
         <v>1000</v>
       </c>
-      <c r="L137">
+      <c r="L139">
         <v>1000</v>
       </c>
-      <c r="N137">
+      <c r="N139">
         <v>825</v>
       </c>
-      <c r="O137">
+      <c r="O139">
         <v>46.9</v>
       </c>
-      <c r="P137" t="s">
+      <c r="P139" t="s">
         <v>154</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O137">
-    <sortCondition ref="A2:A137"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O139">
+    <sortCondition ref="A2:A139"/>
   </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huanger9\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C8A395-37EE-435C-A60F-42E0472D6FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FEE493-5521-40EC-A850-8632C8F77634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="294">
   <si>
     <t>OEM</t>
   </si>
@@ -867,6 +867,54 @@
   </si>
   <si>
     <t>ELION 800-N270</t>
+  </si>
+  <si>
+    <t>e-mac</t>
+  </si>
+  <si>
+    <t>e-mac 100</t>
+  </si>
+  <si>
+    <t>Validated spec</t>
+  </si>
+  <si>
+    <t>e-mac 130</t>
+  </si>
+  <si>
+    <t>30-45</t>
+  </si>
+  <si>
+    <t>Tie-bar confirmed</t>
+  </si>
+  <si>
+    <t>e-mac 180</t>
+  </si>
+  <si>
+    <t>35-50</t>
+  </si>
+  <si>
+    <t>Common config</t>
+  </si>
+  <si>
+    <t>e-mac 220</t>
+  </si>
+  <si>
+    <t>40-55</t>
+  </si>
+  <si>
+    <t>Estimated larger class</t>
+  </si>
+  <si>
+    <t>e-mac 500</t>
+  </si>
+  <si>
+    <t>55-80</t>
+  </si>
+  <si>
+    <t>Max class</t>
+  </si>
+  <si>
+    <t>e-mac 85</t>
   </si>
 </sst>
 </file>
@@ -928,11 +976,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1235,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7860,6 +7910,268 @@
         <v>154</v>
       </c>
     </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D140" s="2">
+        <v>100</v>
+      </c>
+      <c r="E140" s="2">
+        <v>650</v>
+      </c>
+      <c r="F140" s="2">
+        <v>600</v>
+      </c>
+      <c r="G140" s="2">
+        <v>460</v>
+      </c>
+      <c r="H140" s="2">
+        <v>410</v>
+      </c>
+      <c r="I140" s="2">
+        <v>800</v>
+      </c>
+      <c r="J140" s="2">
+        <v>150</v>
+      </c>
+      <c r="K140" s="2">
+        <v>450</v>
+      </c>
+      <c r="L140" s="2">
+        <v>350</v>
+      </c>
+      <c r="M140" s="2">
+        <v>150</v>
+      </c>
+      <c r="N140" s="2">
+        <v>202</v>
+      </c>
+      <c r="O140" s="2">
+        <v>40</v>
+      </c>
+      <c r="P140" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D141" s="2">
+        <v>130</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2">
+        <v>530</v>
+      </c>
+      <c r="H141" s="2">
+        <v>530</v>
+      </c>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2">
+        <v>150</v>
+      </c>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2">
+        <v>400</v>
+      </c>
+      <c r="M141" s="2">
+        <v>150</v>
+      </c>
+      <c r="N141" s="2">
+        <v>250</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="P141" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D142" s="2">
+        <v>180</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2">
+        <v>570</v>
+      </c>
+      <c r="H142" s="2">
+        <v>570</v>
+      </c>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2">
+        <v>150</v>
+      </c>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2">
+        <v>450</v>
+      </c>
+      <c r="M142" s="2">
+        <v>150</v>
+      </c>
+      <c r="N142" s="2">
+        <v>300</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="P142" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D143" s="2">
+        <v>220</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2">
+        <v>650</v>
+      </c>
+      <c r="H143" s="2">
+        <v>650</v>
+      </c>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2">
+        <v>150</v>
+      </c>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2">
+        <v>500</v>
+      </c>
+      <c r="M143" s="2">
+        <v>150</v>
+      </c>
+      <c r="N143" s="2">
+        <v>350</v>
+      </c>
+      <c r="O143" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="P143" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D144" s="2">
+        <v>500</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2">
+        <v>830</v>
+      </c>
+      <c r="H144" s="2">
+        <v>830</v>
+      </c>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2">
+        <v>150</v>
+      </c>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2">
+        <v>700</v>
+      </c>
+      <c r="M144" s="2">
+        <v>150</v>
+      </c>
+      <c r="N144" s="2">
+        <v>600</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="P144" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D145" s="3">
+        <v>85</v>
+      </c>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3">
+        <v>470</v>
+      </c>
+      <c r="H145" s="3">
+        <v>420</v>
+      </c>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3">
+        <v>150</v>
+      </c>
+      <c r="K145" s="3"/>
+      <c r="L145" s="3">
+        <v>320</v>
+      </c>
+      <c r="M145" s="3">
+        <v>150</v>
+      </c>
+      <c r="N145" s="3">
+        <v>23</v>
+      </c>
+      <c r="O145" s="3">
+        <v>20</v>
+      </c>
+      <c r="P145" s="3"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O139">
     <sortCondition ref="A2:A139"/>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FEE493-5521-40EC-A850-8632C8F77634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC512D8A-979E-43CD-AECA-E5D11896EDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="300">
   <si>
     <t>OEM</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Mold Max (mm)</t>
   </si>
   <si>
-    <t>Stroke (mm)</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -689,24 +686,6 @@
     <t>Small-mid</t>
   </si>
   <si>
-    <t>ELION 1000</t>
-  </si>
-  <si>
-    <t>Mid precision</t>
-  </si>
-  <si>
-    <t>ELION 1200</t>
-  </si>
-  <si>
-    <t>ELION 1750</t>
-  </si>
-  <si>
-    <t>ELION 2200</t>
-  </si>
-  <si>
-    <t>ELION 2800</t>
-  </si>
-  <si>
     <t>ELION 3200</t>
   </si>
   <si>
@@ -915,6 +894,45 @@
   </si>
   <si>
     <t>e-mac 85</t>
+  </si>
+  <si>
+    <t>ELION 1200-N250</t>
+  </si>
+  <si>
+    <t>ELION 1200-N510</t>
+  </si>
+  <si>
+    <t>ELION 1750-N250</t>
+  </si>
+  <si>
+    <t>ELION 1750-N510</t>
+  </si>
+  <si>
+    <t>ELION 1750-N870</t>
+  </si>
+  <si>
+    <t>ELION 2200-N250</t>
+  </si>
+  <si>
+    <t>ELION 2200-N510</t>
+  </si>
+  <si>
+    <t>ELION 2200-N870</t>
+  </si>
+  <si>
+    <t>ELION 2800-N510</t>
+  </si>
+  <si>
+    <t>ELION 2800-N870</t>
+  </si>
+  <si>
+    <t>Mold Weight Max (kg)</t>
+  </si>
+  <si>
+    <t>Mold Weight Moving Platen Max (kg)</t>
+  </si>
+  <si>
+    <t>Screw Stroke (mm)</t>
   </si>
 </sst>
 </file>
@@ -941,12 +959,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -976,13 +1000,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1285,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1297,14 +1323,16 @@
     <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1339,30 +1367,36 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
       </c>
       <c r="D2">
         <v>60</v>
@@ -1401,19 +1435,19 @@
       <c r="O2">
         <v>15.5</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -1448,19 +1482,19 @@
       <c r="O3">
         <v>20</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
       </c>
       <c r="D4">
         <v>60</v>
@@ -1495,19 +1529,19 @@
       <c r="O4">
         <v>15.5</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
       </c>
       <c r="D5">
         <v>150</v>
@@ -1542,19 +1576,19 @@
       <c r="O5">
         <v>24.5</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
       </c>
       <c r="D6">
         <v>290</v>
@@ -1589,19 +1623,19 @@
       <c r="O6">
         <v>34.1</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
       </c>
       <c r="D7">
         <v>150</v>
@@ -1636,19 +1670,19 @@
       <c r="O7">
         <v>24.5</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
       </c>
       <c r="D8">
         <v>350</v>
@@ -1683,19 +1717,19 @@
       <c r="O8">
         <v>37.4</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
       </c>
       <c r="D9">
         <v>400</v>
@@ -1730,19 +1764,19 @@
       <c r="O9">
         <v>40</v>
       </c>
-      <c r="P9" t="s">
+      <c r="R9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
       </c>
       <c r="D10">
         <v>800</v>
@@ -1777,19 +1811,19 @@
       <c r="O10">
         <v>56.6</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
       </c>
       <c r="D11">
         <v>800</v>
@@ -1824,19 +1858,19 @@
       <c r="O11">
         <v>56.6</v>
       </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
       </c>
       <c r="D12">
         <v>1300</v>
@@ -1871,19 +1905,19 @@
       <c r="O12">
         <v>72.099999999999994</v>
       </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
       </c>
       <c r="D13">
         <v>2100</v>
@@ -1918,19 +1952,19 @@
       <c r="O13">
         <v>91.7</v>
       </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -1965,19 +1999,19 @@
       <c r="O14">
         <v>20</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
       </c>
       <c r="D15">
         <v>150</v>
@@ -2012,19 +2046,19 @@
       <c r="O15">
         <v>24.5</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>62</v>
       </c>
       <c r="D16">
         <v>290</v>
@@ -2059,19 +2093,19 @@
       <c r="O16">
         <v>34.1</v>
       </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
       </c>
       <c r="D17">
         <v>150</v>
@@ -2106,19 +2140,19 @@
       <c r="O17">
         <v>24.5</v>
       </c>
-      <c r="P17" t="s">
+      <c r="R17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
       </c>
       <c r="D18">
         <v>350</v>
@@ -2153,19 +2187,19 @@
       <c r="O18">
         <v>37.4</v>
       </c>
-      <c r="P18" t="s">
+      <c r="R18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
       </c>
       <c r="D19">
         <v>400</v>
@@ -2200,19 +2234,19 @@
       <c r="O19">
         <v>40</v>
       </c>
-      <c r="P19" t="s">
+      <c r="R19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
       </c>
       <c r="D20">
         <v>800</v>
@@ -2247,19 +2281,19 @@
       <c r="O20">
         <v>56.6</v>
       </c>
-      <c r="P20" t="s">
+      <c r="R20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
       </c>
       <c r="D21">
         <v>800</v>
@@ -2294,19 +2328,19 @@
       <c r="O21">
         <v>56.6</v>
       </c>
-      <c r="P21" t="s">
+      <c r="R21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>74</v>
       </c>
       <c r="D22">
         <v>1300</v>
@@ -2341,19 +2375,19 @@
       <c r="O22">
         <v>72.099999999999994</v>
       </c>
-      <c r="P22" t="s">
+      <c r="R22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
       </c>
       <c r="D23">
         <v>290</v>
@@ -2388,19 +2422,19 @@
       <c r="O23">
         <v>34.1</v>
       </c>
-      <c r="P23" t="s">
+      <c r="R23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
       </c>
       <c r="D24">
         <v>350</v>
@@ -2435,19 +2469,19 @@
       <c r="O24">
         <v>37.4</v>
       </c>
-      <c r="P24" t="s">
+      <c r="R24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
       </c>
       <c r="D25">
         <v>400</v>
@@ -2482,19 +2516,19 @@
       <c r="O25">
         <v>40</v>
       </c>
-      <c r="P25" t="s">
+      <c r="R25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>83</v>
       </c>
       <c r="D26">
         <v>800</v>
@@ -2529,19 +2563,19 @@
       <c r="O26">
         <v>56.6</v>
       </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
       </c>
       <c r="D27">
         <v>800</v>
@@ -2576,19 +2610,19 @@
       <c r="O27">
         <v>56.6</v>
       </c>
-      <c r="P27" t="s">
+      <c r="R27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
       </c>
       <c r="D28">
         <v>1300</v>
@@ -2623,19 +2657,19 @@
       <c r="O28">
         <v>72.099999999999994</v>
       </c>
-      <c r="P28" t="s">
+      <c r="R28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
       </c>
       <c r="D29">
         <v>2100</v>
@@ -2670,19 +2704,19 @@
       <c r="O29">
         <v>91.7</v>
       </c>
-      <c r="P29" t="s">
+      <c r="R29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
       </c>
       <c r="D30">
         <v>30</v>
@@ -2717,19 +2751,19 @@
       <c r="O30">
         <v>11</v>
       </c>
-      <c r="P30" t="s">
+      <c r="R30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
       </c>
       <c r="D31">
         <v>60</v>
@@ -2764,19 +2798,19 @@
       <c r="O31">
         <v>15.5</v>
       </c>
-      <c r="P31" t="s">
+      <c r="R31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -2811,19 +2845,19 @@
       <c r="O32">
         <v>20</v>
       </c>
-      <c r="P32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
         <v>16</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>18</v>
       </c>
       <c r="D33">
         <v>1100</v>
@@ -2861,19 +2895,19 @@
       <c r="O33">
         <v>66.3</v>
       </c>
-      <c r="P33" t="s">
+      <c r="R33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>20</v>
-      </c>
-      <c r="C34" t="s">
-        <v>21</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -2911,19 +2945,19 @@
       <c r="O34">
         <v>20</v>
       </c>
-      <c r="P34" t="s">
+      <c r="R34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>23</v>
-      </c>
-      <c r="C35" t="s">
-        <v>24</v>
       </c>
       <c r="D35">
         <v>500</v>
@@ -2961,19 +2995,19 @@
       <c r="O35">
         <v>44.7</v>
       </c>
-      <c r="P35" t="s">
+      <c r="R35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" t="s">
-        <v>26</v>
       </c>
       <c r="D36">
         <v>60</v>
@@ -3011,19 +3045,19 @@
       <c r="O36">
         <v>15.5</v>
       </c>
-      <c r="P36" t="s">
+      <c r="R36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>28</v>
-      </c>
-      <c r="C37" t="s">
-        <v>29</v>
       </c>
       <c r="D37">
         <v>380</v>
@@ -3046,19 +3080,19 @@
       <c r="O37">
         <v>39</v>
       </c>
-      <c r="P37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D38">
         <v>40</v>
@@ -3096,19 +3130,19 @@
       <c r="O38">
         <v>12.6</v>
       </c>
-      <c r="P38" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R38" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D39">
         <v>50</v>
@@ -3146,19 +3180,19 @@
       <c r="O39">
         <v>14.1</v>
       </c>
-      <c r="P39" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D40">
         <v>80</v>
@@ -3196,19 +3230,19 @@
       <c r="O40">
         <v>17.899999999999999</v>
       </c>
-      <c r="P40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R40" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D41">
         <v>100</v>
@@ -3246,19 +3280,19 @@
       <c r="O41">
         <v>20</v>
       </c>
-      <c r="P41" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R41" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D42">
         <v>130</v>
@@ -3296,19 +3330,19 @@
       <c r="O42">
         <v>22.8</v>
       </c>
-      <c r="P42" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" t="s">
         <v>254</v>
-      </c>
-      <c r="C43" t="s">
-        <v>261</v>
       </c>
       <c r="D43">
         <v>160</v>
@@ -3346,19 +3380,19 @@
       <c r="O43">
         <v>25.3</v>
       </c>
-      <c r="P43" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D44">
         <v>180</v>
@@ -3396,19 +3430,19 @@
       <c r="O44">
         <v>26.8</v>
       </c>
-      <c r="P44" t="s">
+      <c r="R44" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" t="s">
-        <v>263</v>
       </c>
       <c r="D45">
         <v>200</v>
@@ -3446,19 +3480,19 @@
       <c r="O45">
         <v>28.3</v>
       </c>
-      <c r="P45" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D46">
         <v>220</v>
@@ -3496,19 +3530,19 @@
       <c r="O46">
         <v>29.7</v>
       </c>
-      <c r="P46" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R46" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D47">
         <v>280</v>
@@ -3546,19 +3580,19 @@
       <c r="O47">
         <v>33.5</v>
       </c>
-      <c r="P47" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R47" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C48" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D48">
         <v>380</v>
@@ -3596,19 +3630,19 @@
       <c r="O48">
         <v>39</v>
       </c>
-      <c r="P48" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D49">
         <v>450</v>
@@ -3646,19 +3680,19 @@
       <c r="O49">
         <v>42.4</v>
       </c>
-      <c r="P49" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R49" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C50" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D50">
         <v>550</v>
@@ -3696,19 +3730,19 @@
       <c r="O50">
         <v>46.9</v>
       </c>
-      <c r="P50" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R50" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D51">
         <v>700</v>
@@ -3746,19 +3780,19 @@
       <c r="O51">
         <v>52.9</v>
       </c>
-      <c r="P51" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C52" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D52">
         <v>900</v>
@@ -3796,19 +3830,19 @@
       <c r="O52">
         <v>60</v>
       </c>
-      <c r="P52" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R52" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C53" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D53">
         <v>1100</v>
@@ -3846,19 +3880,19 @@
       <c r="O53">
         <v>66.3</v>
       </c>
-      <c r="P53" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R53" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C54" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D54">
         <v>1500</v>
@@ -3896,19 +3930,19 @@
       <c r="O54">
         <v>77.5</v>
       </c>
-      <c r="P54" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R54" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D55">
         <v>2000</v>
@@ -3946,19 +3980,19 @@
       <c r="O55">
         <v>89.4</v>
       </c>
-      <c r="P55" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D56">
         <v>3000</v>
@@ -3996,19 +4030,19 @@
       <c r="O56">
         <v>109.5</v>
       </c>
-      <c r="P56" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" t="s">
         <v>155</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>156</v>
-      </c>
-      <c r="C57" t="s">
-        <v>157</v>
       </c>
       <c r="D57">
         <v>130</v>
@@ -4043,19 +4077,19 @@
       <c r="O57">
         <v>22.8</v>
       </c>
-      <c r="P57" t="s">
+      <c r="R57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>155</v>
-      </c>
-      <c r="B58" t="s">
-        <v>156</v>
-      </c>
-      <c r="C58" t="s">
-        <v>159</v>
       </c>
       <c r="D58">
         <v>180</v>
@@ -4090,19 +4124,19 @@
       <c r="O58">
         <v>26.8</v>
       </c>
-      <c r="P58" t="s">
+      <c r="R58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>155</v>
-      </c>
-      <c r="B59" t="s">
-        <v>156</v>
-      </c>
-      <c r="C59" t="s">
-        <v>161</v>
       </c>
       <c r="D59">
         <v>220</v>
@@ -4137,19 +4171,19 @@
       <c r="O59">
         <v>29.7</v>
       </c>
-      <c r="P59" t="s">
+      <c r="R59" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>154</v>
+      </c>
+      <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>155</v>
-      </c>
-      <c r="B60" t="s">
-        <v>156</v>
-      </c>
-      <c r="C60" t="s">
-        <v>163</v>
       </c>
       <c r="D60">
         <v>280</v>
@@ -4184,19 +4218,19 @@
       <c r="O60">
         <v>33.5</v>
       </c>
-      <c r="P60" t="s">
+      <c r="R60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>155</v>
-      </c>
-      <c r="B61" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" t="s">
-        <v>165</v>
       </c>
       <c r="D61">
         <v>350</v>
@@ -4231,19 +4265,19 @@
       <c r="O61">
         <v>37.4</v>
       </c>
-      <c r="P61" t="s">
+      <c r="R61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" t="s">
-        <v>167</v>
       </c>
       <c r="D62">
         <v>420</v>
@@ -4278,19 +4312,19 @@
       <c r="O62">
         <v>41</v>
       </c>
-      <c r="P62" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R62" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>154</v>
+      </c>
+      <c r="B63" t="s">
         <v>155</v>
       </c>
-      <c r="B63" t="s">
-        <v>156</v>
-      </c>
       <c r="C63" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D63">
         <v>520</v>
@@ -4325,19 +4359,19 @@
       <c r="O63">
         <v>45.6</v>
       </c>
-      <c r="P63" t="s">
+      <c r="R63" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s">
+        <v>155</v>
+      </c>
+      <c r="C64" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>155</v>
-      </c>
-      <c r="B64" t="s">
-        <v>156</v>
-      </c>
-      <c r="C64" t="s">
-        <v>170</v>
       </c>
       <c r="D64">
         <v>600</v>
@@ -4372,19 +4406,19 @@
       <c r="O64">
         <v>49</v>
       </c>
-      <c r="P64" t="s">
+      <c r="R64" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>155</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>172</v>
-      </c>
-      <c r="C65" t="s">
-        <v>173</v>
       </c>
       <c r="D65">
         <v>130</v>
@@ -4419,19 +4453,19 @@
       <c r="O65">
         <v>22.8</v>
       </c>
-      <c r="P65" t="s">
+      <c r="R65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>154</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>155</v>
-      </c>
-      <c r="B66" t="s">
-        <v>172</v>
-      </c>
-      <c r="C66" t="s">
-        <v>175</v>
       </c>
       <c r="D66">
         <v>180</v>
@@ -4466,19 +4500,19 @@
       <c r="O66">
         <v>26.8</v>
       </c>
-      <c r="P66" t="s">
+      <c r="R66" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" t="s">
-        <v>177</v>
       </c>
       <c r="D67">
         <v>220</v>
@@ -4513,19 +4547,19 @@
       <c r="O67">
         <v>29.7</v>
       </c>
-      <c r="P67" t="s">
+      <c r="R67" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" t="s">
+        <v>171</v>
+      </c>
+      <c r="C68" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" t="s">
-        <v>172</v>
-      </c>
-      <c r="C68" t="s">
-        <v>179</v>
       </c>
       <c r="D68">
         <v>280</v>
@@ -4560,19 +4594,19 @@
       <c r="O68">
         <v>33.5</v>
       </c>
-      <c r="P68" t="s">
+      <c r="R68" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>155</v>
-      </c>
-      <c r="B69" t="s">
-        <v>172</v>
-      </c>
-      <c r="C69" t="s">
-        <v>181</v>
       </c>
       <c r="D69">
         <v>350</v>
@@ -4607,19 +4641,19 @@
       <c r="O69">
         <v>37.4</v>
       </c>
-      <c r="P69" t="s">
+      <c r="R69" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>154</v>
+      </c>
+      <c r="B70" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>155</v>
-      </c>
-      <c r="B70" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" t="s">
-        <v>183</v>
       </c>
       <c r="D70">
         <v>420</v>
@@ -4654,19 +4688,19 @@
       <c r="O70">
         <v>41</v>
       </c>
-      <c r="P70" t="s">
+      <c r="R70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>155</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>185</v>
-      </c>
-      <c r="C71" t="s">
-        <v>186</v>
       </c>
       <c r="D71">
         <v>130</v>
@@ -4701,19 +4735,19 @@
       <c r="O71">
         <v>22.8</v>
       </c>
-      <c r="P71" t="s">
+      <c r="R71" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" t="s">
+        <v>184</v>
+      </c>
+      <c r="C72" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>155</v>
-      </c>
-      <c r="B72" t="s">
-        <v>185</v>
-      </c>
-      <c r="C72" t="s">
-        <v>188</v>
       </c>
       <c r="D72">
         <v>180</v>
@@ -4748,19 +4782,19 @@
       <c r="O72">
         <v>26.8</v>
       </c>
-      <c r="P72" t="s">
+      <c r="R72" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" t="s">
-        <v>190</v>
       </c>
       <c r="D73">
         <v>220</v>
@@ -4795,19 +4829,19 @@
       <c r="O73">
         <v>29.7</v>
       </c>
-      <c r="P73" t="s">
+      <c r="R73" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>155</v>
-      </c>
-      <c r="B74" t="s">
-        <v>185</v>
-      </c>
-      <c r="C74" t="s">
-        <v>192</v>
       </c>
       <c r="D74">
         <v>250</v>
@@ -4842,19 +4876,19 @@
       <c r="O74">
         <v>31.6</v>
       </c>
-      <c r="P74" t="s">
+      <c r="R74" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>155</v>
-      </c>
-      <c r="B75" t="s">
-        <v>185</v>
-      </c>
-      <c r="C75" t="s">
-        <v>194</v>
       </c>
       <c r="D75">
         <v>300</v>
@@ -4889,19 +4923,19 @@
       <c r="O75">
         <v>34.6</v>
       </c>
-      <c r="P75" t="s">
+      <c r="R75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" t="s">
+        <v>184</v>
+      </c>
+      <c r="C76" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>155</v>
-      </c>
-      <c r="B76" t="s">
-        <v>185</v>
-      </c>
-      <c r="C76" t="s">
-        <v>196</v>
       </c>
       <c r="D76">
         <v>350</v>
@@ -4936,19 +4970,19 @@
       <c r="O76">
         <v>37.4</v>
       </c>
-      <c r="P76" t="s">
+      <c r="R76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s">
+        <v>184</v>
+      </c>
+      <c r="C77" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>155</v>
-      </c>
-      <c r="B77" t="s">
-        <v>185</v>
-      </c>
-      <c r="C77" t="s">
-        <v>198</v>
       </c>
       <c r="D77">
         <v>400</v>
@@ -4983,19 +5017,19 @@
       <c r="O77">
         <v>40</v>
       </c>
-      <c r="P77" t="s">
+      <c r="R77" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>155</v>
-      </c>
-      <c r="B78" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" t="s">
-        <v>200</v>
       </c>
       <c r="D78">
         <v>500</v>
@@ -5030,19 +5064,19 @@
       <c r="O78">
         <v>44.7</v>
       </c>
-      <c r="P78" t="s">
+      <c r="R78" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>202</v>
-      </c>
-      <c r="C79" t="s">
-        <v>203</v>
       </c>
       <c r="D79">
         <v>13</v>
@@ -5077,19 +5111,19 @@
       <c r="O79">
         <v>7.2</v>
       </c>
-      <c r="P79" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R79" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D80">
         <v>33</v>
@@ -5124,19 +5158,19 @@
       <c r="O80">
         <v>11.5</v>
       </c>
-      <c r="P80" t="s">
+      <c r="R80" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>154</v>
+      </c>
+      <c r="B81" t="s">
+        <v>201</v>
+      </c>
+      <c r="C81" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>155</v>
-      </c>
-      <c r="B81" t="s">
-        <v>202</v>
-      </c>
-      <c r="C81" t="s">
-        <v>206</v>
       </c>
       <c r="D81">
         <v>66</v>
@@ -5171,19 +5205,19 @@
       <c r="O81">
         <v>16.2</v>
       </c>
-      <c r="P81" t="s">
+      <c r="R81" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" t="s">
+        <v>201</v>
+      </c>
+      <c r="C82" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>155</v>
-      </c>
-      <c r="B82" t="s">
-        <v>202</v>
-      </c>
-      <c r="C82" t="s">
-        <v>208</v>
       </c>
       <c r="D82">
         <v>100</v>
@@ -5218,19 +5252,19 @@
       <c r="O82">
         <v>20</v>
       </c>
-      <c r="P82" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R82" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B83" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C83" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D83">
         <v>150</v>
@@ -5265,19 +5299,19 @@
       <c r="O83">
         <v>24.5</v>
       </c>
-      <c r="P83" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R83" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B84" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D84">
         <v>200</v>
@@ -5312,19 +5346,19 @@
       <c r="O84">
         <v>28.3</v>
       </c>
-      <c r="P84" t="s">
+      <c r="R84" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>212</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>213</v>
-      </c>
-      <c r="C85" t="s">
-        <v>214</v>
       </c>
       <c r="D85">
         <v>55</v>
@@ -5359,19 +5393,19 @@
       <c r="O85">
         <v>14.8</v>
       </c>
-      <c r="P85" t="s">
+      <c r="R85" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>212</v>
-      </c>
-      <c r="B86" t="s">
-        <v>213</v>
-      </c>
-      <c r="C86" t="s">
-        <v>216</v>
       </c>
       <c r="D86">
         <v>65</v>
@@ -5406,19 +5440,19 @@
       <c r="O86">
         <v>16.100000000000001</v>
       </c>
-      <c r="P86" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" t="s">
         <v>212</v>
       </c>
-      <c r="B87" t="s">
-        <v>213</v>
-      </c>
-      <c r="C87" t="s">
-        <v>275</v>
+      <c r="C87" s="4" t="s">
+        <v>268</v>
       </c>
       <c r="D87">
         <v>85</v>
@@ -5445,882 +5479,954 @@
         <v>500</v>
       </c>
       <c r="L87">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="M87">
         <v>200</v>
       </c>
       <c r="N87">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O87">
         <v>16</v>
       </c>
-      <c r="P87" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="P87" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>704</v>
+      </c>
+      <c r="R87" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B88" t="s">
-        <v>213</v>
-      </c>
-      <c r="C88" t="s">
-        <v>276</v>
-      </c>
-      <c r="D88">
+      <c r="C88" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D88" s="3">
         <v>85</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="3">
         <v>650</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="3">
         <v>621</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="3">
         <v>410</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="3">
         <v>410</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="3">
         <v>650</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="3">
         <v>200</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="3">
         <v>500</v>
       </c>
-      <c r="L88">
+      <c r="L88" s="3">
+        <v>100</v>
+      </c>
+      <c r="M88" s="3">
+        <v>200</v>
+      </c>
+      <c r="N88" s="3">
+        <v>24</v>
+      </c>
+      <c r="O88" s="3">
+        <v>18</v>
+      </c>
+      <c r="P88" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>704</v>
+      </c>
+      <c r="R88" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D89" s="3">
+        <v>85</v>
+      </c>
+      <c r="E89" s="3">
+        <v>650</v>
+      </c>
+      <c r="F89" s="3">
+        <v>621</v>
+      </c>
+      <c r="G89" s="3">
+        <v>410</v>
+      </c>
+      <c r="H89" s="3">
+        <v>410</v>
+      </c>
+      <c r="I89" s="3">
+        <v>650</v>
+      </c>
+      <c r="J89" s="3">
+        <v>200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>500</v>
+      </c>
+      <c r="L89" s="3">
+        <v>100</v>
+      </c>
+      <c r="M89" s="3">
+        <v>200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>30</v>
+      </c>
+      <c r="O89" s="3">
+        <v>20</v>
+      </c>
+      <c r="P89" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>704</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D90" s="3">
+        <v>85</v>
+      </c>
+      <c r="E90" s="3">
+        <v>650</v>
+      </c>
+      <c r="F90" s="3">
+        <v>621</v>
+      </c>
+      <c r="G90" s="3">
+        <v>410</v>
+      </c>
+      <c r="H90" s="3">
+        <v>410</v>
+      </c>
+      <c r="I90" s="3">
+        <v>650</v>
+      </c>
+      <c r="J90" s="3">
+        <v>200</v>
+      </c>
+      <c r="K90" s="3">
+        <v>500</v>
+      </c>
+      <c r="L90" s="3">
+        <v>100</v>
+      </c>
+      <c r="M90" s="3">
+        <v>200</v>
+      </c>
+      <c r="N90" s="3">
+        <v>47</v>
+      </c>
+      <c r="O90" s="3">
+        <v>25</v>
+      </c>
+      <c r="P90" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q90" s="3">
+        <v>704</v>
+      </c>
+      <c r="R90" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D91">
+        <v>85</v>
+      </c>
+      <c r="E91">
+        <v>650</v>
+      </c>
+      <c r="F91">
+        <v>621</v>
+      </c>
+      <c r="G91">
+        <v>410</v>
+      </c>
+      <c r="H91">
+        <v>410</v>
+      </c>
+      <c r="I91">
+        <v>650</v>
+      </c>
+      <c r="J91" s="3">
+        <v>400</v>
+      </c>
+      <c r="K91" s="3">
+        <v>700</v>
+      </c>
+      <c r="L91">
         <v>350</v>
       </c>
-      <c r="M88">
+      <c r="M91">
         <v>200</v>
       </c>
-      <c r="N88">
+      <c r="N91">
         <v>77</v>
       </c>
-      <c r="O88">
+      <c r="O91">
         <v>18</v>
       </c>
-      <c r="P88" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="P91" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>704</v>
+      </c>
+      <c r="R91" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B89" t="s">
-        <v>213</v>
-      </c>
-      <c r="C89" t="s">
-        <v>277</v>
-      </c>
-      <c r="D89">
+      <c r="C92" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D92" s="3">
         <v>85</v>
       </c>
-      <c r="E89">
+      <c r="E92" s="3">
         <v>650</v>
       </c>
-      <c r="F89">
+      <c r="F92" s="3">
         <v>621</v>
       </c>
-      <c r="G89">
+      <c r="G92" s="3">
         <v>410</v>
       </c>
-      <c r="H89">
+      <c r="H92" s="3">
         <v>410</v>
       </c>
-      <c r="I89">
+      <c r="I92" s="3">
         <v>650</v>
       </c>
-      <c r="J89">
+      <c r="J92" s="3">
+        <v>400</v>
+      </c>
+      <c r="K92" s="3">
+        <v>700</v>
+      </c>
+      <c r="L92" s="3">
+        <v>350</v>
+      </c>
+      <c r="M92" s="3">
         <v>200</v>
       </c>
-      <c r="K89">
+      <c r="N92" s="3">
+        <v>77</v>
+      </c>
+      <c r="O92" s="3">
+        <v>18</v>
+      </c>
+      <c r="P92" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>704</v>
+      </c>
+      <c r="R92" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>211</v>
+      </c>
+      <c r="B93" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D93">
+        <v>85</v>
+      </c>
+      <c r="E93">
+        <v>650</v>
+      </c>
+      <c r="F93">
+        <v>621</v>
+      </c>
+      <c r="G93">
+        <v>410</v>
+      </c>
+      <c r="H93">
+        <v>410</v>
+      </c>
+      <c r="I93">
+        <v>650</v>
+      </c>
+      <c r="J93" s="3">
+        <v>400</v>
+      </c>
+      <c r="K93" s="3">
+        <v>700</v>
+      </c>
+      <c r="L93">
+        <v>127</v>
+      </c>
+      <c r="M93">
+        <v>200</v>
+      </c>
+      <c r="N93">
+        <v>85</v>
+      </c>
+      <c r="O93">
+        <v>33</v>
+      </c>
+      <c r="P93" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>704</v>
+      </c>
+      <c r="R93" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D94" s="3">
+        <v>85</v>
+      </c>
+      <c r="E94" s="3">
+        <v>650</v>
+      </c>
+      <c r="F94" s="3">
+        <v>621</v>
+      </c>
+      <c r="G94" s="3">
+        <v>410</v>
+      </c>
+      <c r="H94" s="3">
+        <v>410</v>
+      </c>
+      <c r="I94" s="3">
+        <v>650</v>
+      </c>
+      <c r="J94" s="3">
+        <v>400</v>
+      </c>
+      <c r="K94" s="3">
+        <v>700</v>
+      </c>
+      <c r="L94" s="3">
+        <v>127</v>
+      </c>
+      <c r="M94" s="3">
+        <v>200</v>
+      </c>
+      <c r="N94" s="3">
+        <v>113</v>
+      </c>
+      <c r="O94" s="3">
+        <v>36</v>
+      </c>
+      <c r="P94" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>704</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D95" s="3">
+        <v>85</v>
+      </c>
+      <c r="E95" s="3">
+        <v>650</v>
+      </c>
+      <c r="F95" s="3">
+        <v>621</v>
+      </c>
+      <c r="G95" s="3">
+        <v>410</v>
+      </c>
+      <c r="H95" s="3">
+        <v>410</v>
+      </c>
+      <c r="I95" s="3">
+        <v>650</v>
+      </c>
+      <c r="J95" s="3">
+        <v>400</v>
+      </c>
+      <c r="K95" s="3">
+        <v>700</v>
+      </c>
+      <c r="L95" s="3">
+        <v>127</v>
+      </c>
+      <c r="M95" s="3">
+        <v>200</v>
+      </c>
+      <c r="N95" s="3">
+        <v>154</v>
+      </c>
+      <c r="O95" s="3">
+        <v>40</v>
+      </c>
+      <c r="P95" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q95" s="3">
+        <v>704</v>
+      </c>
+      <c r="R95" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>211</v>
+      </c>
+      <c r="B96" t="s">
+        <v>212</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D96">
+        <v>130</v>
+      </c>
+      <c r="E96">
+        <v>750</v>
+      </c>
+      <c r="F96">
+        <v>700</v>
+      </c>
+      <c r="G96">
+        <v>510</v>
+      </c>
+      <c r="H96" s="3">
+        <v>510</v>
+      </c>
+      <c r="I96">
+        <v>800</v>
+      </c>
+      <c r="J96">
+        <v>250</v>
+      </c>
+      <c r="K96">
+        <v>550</v>
+      </c>
+      <c r="L96">
         <v>500</v>
       </c>
-      <c r="L89">
+      <c r="N96">
+        <v>154</v>
+      </c>
+      <c r="O96">
+        <v>22.8</v>
+      </c>
+      <c r="R96" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D97" s="3">
+        <v>130</v>
+      </c>
+      <c r="E97" s="3">
+        <v>750</v>
+      </c>
+      <c r="F97" s="3">
+        <v>700</v>
+      </c>
+      <c r="G97" s="3">
+        <v>510</v>
+      </c>
+      <c r="H97" s="3">
+        <v>510</v>
+      </c>
+      <c r="I97" s="3">
+        <v>800</v>
+      </c>
+      <c r="J97" s="3">
+        <v>250</v>
+      </c>
+      <c r="K97" s="3">
+        <v>550</v>
+      </c>
+      <c r="L97" s="3">
+        <v>500</v>
+      </c>
+      <c r="N97" s="3">
+        <v>301</v>
+      </c>
+      <c r="O97" s="3">
+        <v>22.8</v>
+      </c>
+      <c r="R97" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>211</v>
+      </c>
+      <c r="B98" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98">
+        <v>190</v>
+      </c>
+      <c r="E98">
+        <v>820</v>
+      </c>
+      <c r="F98">
+        <v>760</v>
+      </c>
+      <c r="G98">
+        <v>560</v>
+      </c>
+      <c r="H98">
+        <v>560</v>
+      </c>
+      <c r="I98">
+        <v>900</v>
+      </c>
+      <c r="J98">
+        <v>300</v>
+      </c>
+      <c r="K98">
+        <v>600</v>
+      </c>
+      <c r="L98">
+        <v>600</v>
+      </c>
+      <c r="N98" s="3">
+        <v>154</v>
+      </c>
+      <c r="O98">
+        <v>27.6</v>
+      </c>
+      <c r="R98" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D99" s="3">
+        <v>190</v>
+      </c>
+      <c r="E99" s="3">
+        <v>820</v>
+      </c>
+      <c r="F99" s="3">
+        <v>760</v>
+      </c>
+      <c r="G99" s="3">
+        <v>560</v>
+      </c>
+      <c r="H99" s="3">
+        <v>560</v>
+      </c>
+      <c r="I99" s="3">
+        <v>900</v>
+      </c>
+      <c r="J99" s="3">
+        <v>300</v>
+      </c>
+      <c r="K99" s="3">
+        <v>600</v>
+      </c>
+      <c r="L99" s="3">
+        <v>600</v>
+      </c>
+      <c r="N99" s="3">
+        <v>301</v>
+      </c>
+      <c r="O99" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="R99" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D100" s="3">
+        <v>190</v>
+      </c>
+      <c r="E100" s="3">
+        <v>820</v>
+      </c>
+      <c r="F100" s="3">
+        <v>760</v>
+      </c>
+      <c r="G100" s="3">
+        <v>560</v>
+      </c>
+      <c r="H100" s="3">
+        <v>560</v>
+      </c>
+      <c r="I100" s="3">
+        <v>900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>300</v>
+      </c>
+      <c r="K100" s="3">
+        <v>600</v>
+      </c>
+      <c r="L100" s="3">
+        <v>600</v>
+      </c>
+      <c r="N100" s="3">
+        <v>579</v>
+      </c>
+      <c r="O100" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>211</v>
+      </c>
+      <c r="B101" t="s">
+        <v>212</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D101">
+        <v>240</v>
+      </c>
+      <c r="E101">
+        <v>900</v>
+      </c>
+      <c r="F101">
+        <v>830</v>
+      </c>
+      <c r="G101">
+        <v>670</v>
+      </c>
+      <c r="H101">
+        <v>620</v>
+      </c>
+      <c r="I101">
+        <v>1000</v>
+      </c>
+      <c r="J101">
+        <v>300</v>
+      </c>
+      <c r="K101">
+        <v>700</v>
+      </c>
+      <c r="L101">
+        <v>700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>154</v>
+      </c>
+      <c r="O101">
+        <v>31</v>
+      </c>
+      <c r="R101" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D102" s="3">
+        <v>240</v>
+      </c>
+      <c r="E102" s="3">
+        <v>900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>830</v>
+      </c>
+      <c r="G102" s="3">
+        <v>670</v>
+      </c>
+      <c r="H102" s="3">
+        <v>620</v>
+      </c>
+      <c r="I102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>300</v>
+      </c>
+      <c r="K102" s="3">
+        <v>700</v>
+      </c>
+      <c r="L102" s="3">
+        <v>700</v>
+      </c>
+      <c r="N102" s="3">
+        <v>301</v>
+      </c>
+      <c r="O102" s="3">
+        <v>31</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D103" s="3">
+        <v>240</v>
+      </c>
+      <c r="E103" s="3">
+        <v>900</v>
+      </c>
+      <c r="F103" s="3">
+        <v>830</v>
+      </c>
+      <c r="G103" s="3">
+        <v>670</v>
+      </c>
+      <c r="H103" s="3">
+        <v>620</v>
+      </c>
+      <c r="I103" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J103" s="3">
+        <v>300</v>
+      </c>
+      <c r="K103" s="3">
+        <v>700</v>
+      </c>
+      <c r="L103" s="3">
+        <v>700</v>
+      </c>
+      <c r="N103" s="3">
+        <v>579</v>
+      </c>
+      <c r="O103" s="3">
+        <v>31</v>
+      </c>
+      <c r="R103" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>211</v>
+      </c>
+      <c r="B104" t="s">
+        <v>212</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D104">
+        <v>310</v>
+      </c>
+      <c r="E104">
+        <v>950</v>
+      </c>
+      <c r="F104">
+        <v>880</v>
+      </c>
+      <c r="G104">
+        <v>720</v>
+      </c>
+      <c r="H104">
+        <v>670</v>
+      </c>
+      <c r="I104">
+        <v>1100</v>
+      </c>
+      <c r="J104">
         <v>350</v>
       </c>
-      <c r="M89">
-        <v>200</v>
-      </c>
-      <c r="N89">
-        <v>154</v>
-      </c>
-      <c r="O89">
-        <v>18</v>
-      </c>
-      <c r="P89" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="K104">
+        <v>750</v>
+      </c>
+      <c r="L104">
+        <v>750</v>
+      </c>
+      <c r="N104" s="3">
+        <v>301</v>
+      </c>
+      <c r="O104">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="R104" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B90" t="s">
-        <v>213</v>
-      </c>
-      <c r="C90" t="s">
-        <v>218</v>
-      </c>
-      <c r="D90">
-        <v>110</v>
-      </c>
-      <c r="E90">
-        <v>680</v>
-      </c>
-      <c r="F90">
-        <v>620</v>
-      </c>
-      <c r="G90">
-        <v>450</v>
-      </c>
-      <c r="H90">
-        <v>450</v>
-      </c>
-      <c r="I90">
+      <c r="C105" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D105" s="3">
+        <v>310</v>
+      </c>
+      <c r="E105" s="3">
+        <v>950</v>
+      </c>
+      <c r="F105" s="3">
+        <v>880</v>
+      </c>
+      <c r="G105" s="3">
+        <v>720</v>
+      </c>
+      <c r="H105" s="3">
+        <v>670</v>
+      </c>
+      <c r="I105" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J105" s="3">
+        <v>350</v>
+      </c>
+      <c r="K105" s="3">
         <v>750</v>
       </c>
-      <c r="J90">
-        <v>220</v>
-      </c>
-      <c r="K90">
-        <v>500</v>
-      </c>
-      <c r="L90">
-        <v>450</v>
-      </c>
-      <c r="N90">
-        <v>165</v>
-      </c>
-      <c r="O90">
-        <v>21</v>
-      </c>
-      <c r="P90" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="L105" s="3">
+        <v>750</v>
+      </c>
+      <c r="N105" s="3">
+        <v>579</v>
+      </c>
+      <c r="O105" s="3">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="R105" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" t="s">
         <v>212</v>
       </c>
-      <c r="B91" t="s">
-        <v>213</v>
-      </c>
-      <c r="C91" t="s">
-        <v>220</v>
-      </c>
-      <c r="D91">
-        <v>130</v>
-      </c>
-      <c r="E91">
-        <v>750</v>
-      </c>
-      <c r="F91">
-        <v>700</v>
-      </c>
-      <c r="G91">
-        <v>500</v>
-      </c>
-      <c r="H91">
-        <v>500</v>
-      </c>
-      <c r="I91">
-        <v>800</v>
-      </c>
-      <c r="J91">
-        <v>250</v>
-      </c>
-      <c r="K91">
-        <v>550</v>
-      </c>
-      <c r="L91">
-        <v>500</v>
-      </c>
-      <c r="N91">
-        <v>195</v>
-      </c>
-      <c r="O91">
-        <v>22.8</v>
-      </c>
-      <c r="P91" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>212</v>
-      </c>
-      <c r="B92" t="s">
-        <v>213</v>
-      </c>
-      <c r="C92" t="s">
-        <v>221</v>
-      </c>
-      <c r="D92">
-        <v>190</v>
-      </c>
-      <c r="E92">
-        <v>820</v>
-      </c>
-      <c r="F92">
-        <v>760</v>
-      </c>
-      <c r="G92">
-        <v>560</v>
-      </c>
-      <c r="H92">
-        <v>560</v>
-      </c>
-      <c r="I92">
-        <v>900</v>
-      </c>
-      <c r="J92">
-        <v>300</v>
-      </c>
-      <c r="K92">
-        <v>600</v>
-      </c>
-      <c r="L92">
-        <v>600</v>
-      </c>
-      <c r="N92">
-        <v>285</v>
-      </c>
-      <c r="O92">
-        <v>27.6</v>
-      </c>
-      <c r="P92" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>212</v>
-      </c>
-      <c r="B93" t="s">
-        <v>213</v>
-      </c>
-      <c r="C93" t="s">
-        <v>222</v>
-      </c>
-      <c r="D93">
-        <v>240</v>
-      </c>
-      <c r="E93">
-        <v>900</v>
-      </c>
-      <c r="F93">
-        <v>830</v>
-      </c>
-      <c r="G93">
-        <v>610</v>
-      </c>
-      <c r="H93">
-        <v>610</v>
-      </c>
-      <c r="I93">
-        <v>1000</v>
-      </c>
-      <c r="J93">
-        <v>300</v>
-      </c>
-      <c r="K93">
-        <v>700</v>
-      </c>
-      <c r="L93">
-        <v>700</v>
-      </c>
-      <c r="N93">
-        <v>360</v>
-      </c>
-      <c r="O93">
-        <v>31</v>
-      </c>
-      <c r="P93" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>212</v>
-      </c>
-      <c r="B94" t="s">
-        <v>213</v>
-      </c>
-      <c r="C94" t="s">
-        <v>223</v>
-      </c>
-      <c r="D94">
-        <v>310</v>
-      </c>
-      <c r="E94">
-        <v>950</v>
-      </c>
-      <c r="F94">
-        <v>880</v>
-      </c>
-      <c r="G94">
-        <v>660</v>
-      </c>
-      <c r="H94">
-        <v>660</v>
-      </c>
-      <c r="I94">
-        <v>1100</v>
-      </c>
-      <c r="J94">
-        <v>350</v>
-      </c>
-      <c r="K94">
-        <v>750</v>
-      </c>
-      <c r="L94">
-        <v>750</v>
-      </c>
-      <c r="N94">
-        <v>465</v>
-      </c>
-      <c r="O94">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="P94" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>212</v>
-      </c>
-      <c r="B95" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" t="s">
-        <v>224</v>
-      </c>
-      <c r="D95">
-        <v>350</v>
-      </c>
-      <c r="E95">
-        <v>1050</v>
-      </c>
-      <c r="F95">
-        <v>950</v>
-      </c>
-      <c r="G95">
-        <v>710</v>
-      </c>
-      <c r="H95">
-        <v>710</v>
-      </c>
-      <c r="I95">
-        <v>1200</v>
-      </c>
-      <c r="J95">
-        <v>400</v>
-      </c>
-      <c r="K95">
-        <v>800</v>
-      </c>
-      <c r="L95">
-        <v>800</v>
-      </c>
-      <c r="N95">
-        <v>525</v>
-      </c>
-      <c r="O95">
-        <v>37.4</v>
-      </c>
-      <c r="P95" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>212</v>
-      </c>
-      <c r="B96" t="s">
-        <v>213</v>
-      </c>
-      <c r="C96" t="s">
-        <v>225</v>
-      </c>
-      <c r="D96">
-        <v>460</v>
-      </c>
-      <c r="E96">
-        <v>1150</v>
-      </c>
-      <c r="F96">
-        <v>1050</v>
-      </c>
-      <c r="G96">
-        <v>820</v>
-      </c>
-      <c r="H96">
-        <v>820</v>
-      </c>
-      <c r="I96">
-        <v>1300</v>
-      </c>
-      <c r="J96">
-        <v>400</v>
-      </c>
-      <c r="K96">
-        <v>900</v>
-      </c>
-      <c r="L96">
-        <v>900</v>
-      </c>
-      <c r="N96">
-        <v>690</v>
-      </c>
-      <c r="O96">
-        <v>42.9</v>
-      </c>
-      <c r="P96" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>212</v>
-      </c>
-      <c r="B97" t="s">
-        <v>213</v>
-      </c>
-      <c r="C97" t="s">
-        <v>226</v>
-      </c>
-      <c r="D97">
-        <v>550</v>
-      </c>
-      <c r="E97">
-        <v>1250</v>
-      </c>
-      <c r="F97">
-        <v>1150</v>
-      </c>
-      <c r="G97">
-        <v>920</v>
-      </c>
-      <c r="H97">
-        <v>920</v>
-      </c>
-      <c r="I97">
-        <v>1400</v>
-      </c>
-      <c r="J97">
-        <v>450</v>
-      </c>
-      <c r="K97">
-        <v>1000</v>
-      </c>
-      <c r="L97">
-        <v>1000</v>
-      </c>
-      <c r="N97">
-        <v>825</v>
-      </c>
-      <c r="O97">
-        <v>46.9</v>
-      </c>
-      <c r="P97" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>212</v>
-      </c>
-      <c r="B98" t="s">
-        <v>227</v>
-      </c>
-      <c r="C98" t="s">
-        <v>228</v>
-      </c>
-      <c r="D98">
-        <v>130</v>
-      </c>
-      <c r="E98">
-        <v>750</v>
-      </c>
-      <c r="F98">
-        <v>700</v>
-      </c>
-      <c r="G98">
-        <v>500</v>
-      </c>
-      <c r="H98">
-        <v>500</v>
-      </c>
-      <c r="I98">
-        <v>800</v>
-      </c>
-      <c r="J98">
-        <v>250</v>
-      </c>
-      <c r="K98">
-        <v>550</v>
-      </c>
-      <c r="L98">
-        <v>500</v>
-      </c>
-      <c r="N98">
-        <v>195</v>
-      </c>
-      <c r="O98">
-        <v>22.8</v>
-      </c>
-      <c r="P98" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>212</v>
-      </c>
-      <c r="B99" t="s">
-        <v>227</v>
-      </c>
-      <c r="C99" t="s">
-        <v>230</v>
-      </c>
-      <c r="D99">
-        <v>190</v>
-      </c>
-      <c r="E99">
-        <v>820</v>
-      </c>
-      <c r="F99">
-        <v>760</v>
-      </c>
-      <c r="G99">
-        <v>560</v>
-      </c>
-      <c r="H99">
-        <v>560</v>
-      </c>
-      <c r="I99">
-        <v>900</v>
-      </c>
-      <c r="J99">
-        <v>300</v>
-      </c>
-      <c r="K99">
-        <v>600</v>
-      </c>
-      <c r="L99">
-        <v>600</v>
-      </c>
-      <c r="N99">
-        <v>285</v>
-      </c>
-      <c r="O99">
-        <v>27.6</v>
-      </c>
-      <c r="P99" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>212</v>
-      </c>
-      <c r="B100" t="s">
-        <v>227</v>
-      </c>
-      <c r="C100" t="s">
-        <v>232</v>
-      </c>
-      <c r="D100">
-        <v>240</v>
-      </c>
-      <c r="E100">
-        <v>900</v>
-      </c>
-      <c r="F100">
-        <v>830</v>
-      </c>
-      <c r="G100">
-        <v>610</v>
-      </c>
-      <c r="H100">
-        <v>610</v>
-      </c>
-      <c r="I100">
-        <v>1000</v>
-      </c>
-      <c r="J100">
-        <v>300</v>
-      </c>
-      <c r="K100">
-        <v>700</v>
-      </c>
-      <c r="L100">
-        <v>700</v>
-      </c>
-      <c r="N100">
-        <v>360</v>
-      </c>
-      <c r="O100">
-        <v>31</v>
-      </c>
-      <c r="P100" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>212</v>
-      </c>
-      <c r="B101" t="s">
-        <v>227</v>
-      </c>
-      <c r="C101" t="s">
-        <v>234</v>
-      </c>
-      <c r="D101">
-        <v>310</v>
-      </c>
-      <c r="E101">
-        <v>950</v>
-      </c>
-      <c r="F101">
-        <v>880</v>
-      </c>
-      <c r="G101">
-        <v>660</v>
-      </c>
-      <c r="H101">
-        <v>660</v>
-      </c>
-      <c r="I101">
-        <v>1100</v>
-      </c>
-      <c r="J101">
-        <v>350</v>
-      </c>
-      <c r="K101">
-        <v>750</v>
-      </c>
-      <c r="L101">
-        <v>750</v>
-      </c>
-      <c r="N101">
-        <v>465</v>
-      </c>
-      <c r="O101">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="P101" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>212</v>
-      </c>
-      <c r="B102" t="s">
-        <v>227</v>
-      </c>
-      <c r="C102" t="s">
-        <v>236</v>
-      </c>
-      <c r="D102">
-        <v>350</v>
-      </c>
-      <c r="E102">
-        <v>1050</v>
-      </c>
-      <c r="F102">
-        <v>950</v>
-      </c>
-      <c r="G102">
-        <v>710</v>
-      </c>
-      <c r="H102">
-        <v>710</v>
-      </c>
-      <c r="I102">
-        <v>1200</v>
-      </c>
-      <c r="J102">
-        <v>400</v>
-      </c>
-      <c r="K102">
-        <v>800</v>
-      </c>
-      <c r="L102">
-        <v>800</v>
-      </c>
-      <c r="N102">
-        <v>525</v>
-      </c>
-      <c r="O102">
-        <v>37.4</v>
-      </c>
-      <c r="P102" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>212</v>
-      </c>
-      <c r="B103" t="s">
-        <v>227</v>
-      </c>
-      <c r="C103" t="s">
-        <v>238</v>
-      </c>
-      <c r="D103">
-        <v>460</v>
-      </c>
-      <c r="E103">
-        <v>1150</v>
-      </c>
-      <c r="F103">
-        <v>1050</v>
-      </c>
-      <c r="G103">
-        <v>820</v>
-      </c>
-      <c r="H103">
-        <v>820</v>
-      </c>
-      <c r="I103">
-        <v>1300</v>
-      </c>
-      <c r="J103">
-        <v>400</v>
-      </c>
-      <c r="K103">
-        <v>900</v>
-      </c>
-      <c r="L103">
-        <v>900</v>
-      </c>
-      <c r="N103">
-        <v>690</v>
-      </c>
-      <c r="O103">
-        <v>42.9</v>
-      </c>
-      <c r="P103" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>212</v>
-      </c>
-      <c r="B104" t="s">
-        <v>227</v>
-      </c>
-      <c r="C104" t="s">
-        <v>239</v>
-      </c>
-      <c r="D104">
-        <v>550</v>
-      </c>
-      <c r="E104">
-        <v>1250</v>
-      </c>
-      <c r="F104">
-        <v>1150</v>
-      </c>
-      <c r="G104">
-        <v>920</v>
-      </c>
-      <c r="H104">
-        <v>920</v>
-      </c>
-      <c r="I104">
-        <v>1400</v>
-      </c>
-      <c r="J104">
-        <v>450</v>
-      </c>
-      <c r="K104">
-        <v>1000</v>
-      </c>
-      <c r="L104">
-        <v>1000</v>
-      </c>
-      <c r="N104">
-        <v>825</v>
-      </c>
-      <c r="O104">
-        <v>46.9</v>
-      </c>
-      <c r="P104" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>212</v>
-      </c>
-      <c r="B105" t="s">
-        <v>240</v>
-      </c>
-      <c r="C105" t="s">
-        <v>241</v>
-      </c>
-      <c r="D105">
-        <v>220</v>
-      </c>
-      <c r="E105">
-        <v>880</v>
-      </c>
-      <c r="F105">
-        <v>810</v>
-      </c>
-      <c r="G105">
-        <v>610</v>
-      </c>
-      <c r="H105">
-        <v>610</v>
-      </c>
-      <c r="I105">
-        <v>1000</v>
-      </c>
-      <c r="J105">
-        <v>300</v>
-      </c>
-      <c r="K105">
-        <v>700</v>
-      </c>
-      <c r="L105">
-        <v>700</v>
-      </c>
-      <c r="N105">
-        <v>330</v>
-      </c>
-      <c r="O105">
-        <v>29.7</v>
-      </c>
-      <c r="P105" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>212</v>
-      </c>
-      <c r="B106" t="s">
-        <v>240</v>
-      </c>
       <c r="C106" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="D106">
         <v>350</v>
@@ -6355,22 +6461,22 @@
       <c r="O106">
         <v>37.4</v>
       </c>
-      <c r="P106" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R106" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" t="s">
         <v>212</v>
       </c>
-      <c r="B107" t="s">
-        <v>240</v>
-      </c>
       <c r="C107" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="D107">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="E107">
         <v>1150</v>
@@ -6397,24 +6503,24 @@
         <v>900</v>
       </c>
       <c r="N107">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="O107">
-        <v>42.4</v>
-      </c>
-      <c r="P107" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+        <v>42.9</v>
+      </c>
+      <c r="R107" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>211</v>
+      </c>
+      <c r="B108" t="s">
         <v>212</v>
       </c>
-      <c r="B108" t="s">
-        <v>240</v>
-      </c>
       <c r="C108" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="D108">
         <v>550</v>
@@ -6449,357 +6555,357 @@
       <c r="O108">
         <v>46.9</v>
       </c>
-      <c r="P108" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R108" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="C109" t="s">
+        <v>221</v>
+      </c>
+      <c r="D109">
+        <v>130</v>
+      </c>
+      <c r="E109">
+        <v>750</v>
+      </c>
+      <c r="F109">
+        <v>700</v>
+      </c>
+      <c r="G109">
+        <v>500</v>
+      </c>
+      <c r="H109">
+        <v>500</v>
+      </c>
+      <c r="I109">
+        <v>800</v>
+      </c>
+      <c r="J109">
         <v>250</v>
       </c>
-      <c r="D109">
+      <c r="K109">
+        <v>550</v>
+      </c>
+      <c r="L109">
+        <v>500</v>
+      </c>
+      <c r="N109">
+        <v>195</v>
+      </c>
+      <c r="O109">
+        <v>22.8</v>
+      </c>
+      <c r="R109" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>211</v>
+      </c>
+      <c r="B110" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" t="s">
+        <v>223</v>
+      </c>
+      <c r="D110">
+        <v>190</v>
+      </c>
+      <c r="E110">
+        <v>820</v>
+      </c>
+      <c r="F110">
+        <v>760</v>
+      </c>
+      <c r="G110">
+        <v>560</v>
+      </c>
+      <c r="H110">
+        <v>560</v>
+      </c>
+      <c r="I110">
+        <v>900</v>
+      </c>
+      <c r="J110">
+        <v>300</v>
+      </c>
+      <c r="K110">
+        <v>600</v>
+      </c>
+      <c r="L110">
+        <v>600</v>
+      </c>
+      <c r="N110">
+        <v>285</v>
+      </c>
+      <c r="O110">
+        <v>27.6</v>
+      </c>
+      <c r="R110" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" t="s">
+        <v>225</v>
+      </c>
+      <c r="D111">
         <v>240</v>
       </c>
-      <c r="E109">
+      <c r="E111">
         <v>900</v>
       </c>
-      <c r="F109">
+      <c r="F111">
         <v>830</v>
       </c>
-      <c r="G109">
+      <c r="G111">
         <v>610</v>
       </c>
-      <c r="H109">
+      <c r="H111">
         <v>610</v>
       </c>
-      <c r="I109">
+      <c r="I111">
         <v>1000</v>
       </c>
-      <c r="J109">
+      <c r="J111">
         <v>300</v>
       </c>
-      <c r="K109">
+      <c r="K111">
         <v>700</v>
       </c>
-      <c r="L109">
+      <c r="L111">
         <v>700</v>
       </c>
-      <c r="N109">
+      <c r="N111">
         <v>360</v>
       </c>
-      <c r="O109">
+      <c r="O111">
         <v>31</v>
       </c>
-      <c r="P109" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>212</v>
-      </c>
-      <c r="B110" t="s">
-        <v>249</v>
-      </c>
-      <c r="C110" t="s">
-        <v>251</v>
-      </c>
-      <c r="D110">
+      <c r="R111" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>211</v>
+      </c>
+      <c r="B112" t="s">
+        <v>220</v>
+      </c>
+      <c r="C112" t="s">
+        <v>227</v>
+      </c>
+      <c r="D112">
+        <v>310</v>
+      </c>
+      <c r="E112">
+        <v>950</v>
+      </c>
+      <c r="F112">
+        <v>880</v>
+      </c>
+      <c r="G112">
+        <v>660</v>
+      </c>
+      <c r="H112">
+        <v>660</v>
+      </c>
+      <c r="I112">
+        <v>1100</v>
+      </c>
+      <c r="J112">
         <v>350</v>
       </c>
-      <c r="E110">
+      <c r="K112">
+        <v>750</v>
+      </c>
+      <c r="L112">
+        <v>750</v>
+      </c>
+      <c r="N112">
+        <v>465</v>
+      </c>
+      <c r="O112">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="R112" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>211</v>
+      </c>
+      <c r="B113" t="s">
+        <v>220</v>
+      </c>
+      <c r="C113" t="s">
+        <v>229</v>
+      </c>
+      <c r="D113">
+        <v>350</v>
+      </c>
+      <c r="E113">
         <v>1050</v>
       </c>
-      <c r="F110">
+      <c r="F113">
         <v>950</v>
       </c>
-      <c r="G110">
+      <c r="G113">
         <v>710</v>
       </c>
-      <c r="H110">
+      <c r="H113">
         <v>710</v>
       </c>
-      <c r="I110">
+      <c r="I113">
         <v>1200</v>
       </c>
-      <c r="J110">
+      <c r="J113">
         <v>400</v>
       </c>
-      <c r="K110">
+      <c r="K113">
         <v>800</v>
       </c>
-      <c r="L110">
+      <c r="L113">
         <v>800</v>
       </c>
-      <c r="N110">
+      <c r="N113">
         <v>525</v>
       </c>
-      <c r="O110">
+      <c r="O113">
         <v>37.4</v>
       </c>
-      <c r="P110" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>212</v>
-      </c>
-      <c r="B111" t="s">
-        <v>249</v>
-      </c>
-      <c r="C111" t="s">
-        <v>252</v>
-      </c>
-      <c r="D111">
+      <c r="R113" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>211</v>
+      </c>
+      <c r="B114" t="s">
+        <v>220</v>
+      </c>
+      <c r="C114" t="s">
+        <v>231</v>
+      </c>
+      <c r="D114">
         <v>460</v>
       </c>
-      <c r="E111">
+      <c r="E114">
         <v>1150</v>
       </c>
-      <c r="F111">
+      <c r="F114">
         <v>1050</v>
       </c>
-      <c r="G111">
+      <c r="G114">
         <v>820</v>
       </c>
-      <c r="H111">
+      <c r="H114">
         <v>820</v>
       </c>
-      <c r="I111">
+      <c r="I114">
         <v>1300</v>
       </c>
-      <c r="J111">
+      <c r="J114">
         <v>400</v>
       </c>
-      <c r="K111">
+      <c r="K114">
         <v>900</v>
       </c>
-      <c r="L111">
+      <c r="L114">
         <v>900</v>
       </c>
-      <c r="N111">
+      <c r="N114">
         <v>690</v>
       </c>
-      <c r="O111">
+      <c r="O114">
         <v>42.9</v>
       </c>
-      <c r="P111" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>98</v>
-      </c>
-      <c r="B112" t="s">
-        <v>99</v>
-      </c>
-      <c r="C112" t="s">
-        <v>100</v>
-      </c>
-      <c r="D112">
-        <v>55</v>
-      </c>
-      <c r="E112">
-        <v>560</v>
-      </c>
-      <c r="F112">
-        <v>510</v>
-      </c>
-      <c r="G112">
-        <v>360</v>
-      </c>
-      <c r="H112">
-        <v>360</v>
-      </c>
-      <c r="I112">
-        <v>600</v>
-      </c>
-      <c r="J112">
-        <v>200</v>
-      </c>
-      <c r="K112">
-        <v>400</v>
-      </c>
-      <c r="L112">
-        <v>350</v>
-      </c>
-      <c r="N112">
-        <v>82.5</v>
-      </c>
-      <c r="O112">
-        <v>14.8</v>
-      </c>
-      <c r="P112" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>98</v>
-      </c>
-      <c r="B113" t="s">
-        <v>99</v>
-      </c>
-      <c r="C113" t="s">
-        <v>102</v>
-      </c>
-      <c r="D113">
-        <v>75</v>
-      </c>
-      <c r="E113">
-        <v>630</v>
-      </c>
-      <c r="F113">
-        <v>580</v>
-      </c>
-      <c r="G113">
-        <v>410</v>
-      </c>
-      <c r="H113">
-        <v>410</v>
-      </c>
-      <c r="I113">
-        <v>700</v>
-      </c>
-      <c r="J113">
-        <v>200</v>
-      </c>
-      <c r="K113">
+      <c r="R114" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>211</v>
+      </c>
+      <c r="B115" t="s">
+        <v>220</v>
+      </c>
+      <c r="C115" t="s">
+        <v>232</v>
+      </c>
+      <c r="D115">
+        <v>550</v>
+      </c>
+      <c r="E115">
+        <v>1250</v>
+      </c>
+      <c r="F115">
+        <v>1150</v>
+      </c>
+      <c r="G115">
+        <v>920</v>
+      </c>
+      <c r="H115">
+        <v>920</v>
+      </c>
+      <c r="I115">
+        <v>1400</v>
+      </c>
+      <c r="J115">
         <v>450</v>
       </c>
-      <c r="L113">
-        <v>400</v>
-      </c>
-      <c r="N113">
-        <v>112.5</v>
-      </c>
-      <c r="O113">
-        <v>17.3</v>
-      </c>
-      <c r="P113" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>98</v>
-      </c>
-      <c r="B114" t="s">
-        <v>99</v>
-      </c>
-      <c r="C114" t="s">
-        <v>104</v>
-      </c>
-      <c r="D114">
-        <v>143</v>
-      </c>
-      <c r="E114">
-        <v>750</v>
-      </c>
-      <c r="F114">
-        <v>680</v>
-      </c>
-      <c r="G114">
-        <v>510</v>
-      </c>
-      <c r="H114">
-        <v>510</v>
-      </c>
-      <c r="I114">
-        <v>800</v>
-      </c>
-      <c r="J114">
-        <v>250</v>
-      </c>
-      <c r="K114">
-        <v>550</v>
-      </c>
-      <c r="L114">
-        <v>500</v>
-      </c>
-      <c r="N114">
-        <v>214.5</v>
-      </c>
-      <c r="O114">
-        <v>23.9</v>
-      </c>
-      <c r="P114" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>98</v>
-      </c>
-      <c r="B115" t="s">
-        <v>99</v>
-      </c>
-      <c r="C115" t="s">
-        <v>106</v>
-      </c>
-      <c r="D115">
-        <v>198</v>
-      </c>
-      <c r="E115">
-        <v>830</v>
-      </c>
-      <c r="F115">
-        <v>760</v>
-      </c>
-      <c r="G115">
-        <v>560</v>
-      </c>
-      <c r="H115">
-        <v>560</v>
-      </c>
-      <c r="I115">
-        <v>900</v>
-      </c>
-      <c r="J115">
-        <v>300</v>
-      </c>
       <c r="K115">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="L115">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="N115">
-        <v>297</v>
+        <v>825</v>
       </c>
       <c r="O115">
-        <v>28.1</v>
-      </c>
-      <c r="P115" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46.9</v>
+      </c>
+      <c r="R115" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="C116" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="D116">
-        <v>308</v>
+        <v>220</v>
       </c>
       <c r="E116">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="F116">
-        <v>840</v>
+        <v>810</v>
       </c>
       <c r="G116">
         <v>610</v>
@@ -6820,30 +6926,30 @@
         <v>700</v>
       </c>
       <c r="N116">
-        <v>462</v>
+        <v>330</v>
       </c>
       <c r="O116">
-        <v>35.1</v>
-      </c>
-      <c r="P116" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+        <v>29.7</v>
+      </c>
+      <c r="R116" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>236</v>
       </c>
       <c r="D117">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="E117">
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="F117">
         <v>950</v>
@@ -6858,7 +6964,7 @@
         <v>1200</v>
       </c>
       <c r="J117">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K117">
         <v>800</v>
@@ -6867,27 +6973,27 @@
         <v>800</v>
       </c>
       <c r="N117">
-        <v>577.5</v>
+        <v>525</v>
       </c>
       <c r="O117">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="P117" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+        <v>37.4</v>
+      </c>
+      <c r="R117" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="C118" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="D118">
-        <v>495</v>
+        <v>450</v>
       </c>
       <c r="E118">
         <v>1150</v>
@@ -6914,24 +7020,24 @@
         <v>900</v>
       </c>
       <c r="N118">
-        <v>742.5</v>
+        <v>675</v>
       </c>
       <c r="O118">
-        <v>44.5</v>
-      </c>
-      <c r="P118" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+        <v>42.4</v>
+      </c>
+      <c r="R118" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="B119" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="C119" t="s">
-        <v>113</v>
+        <v>240</v>
       </c>
       <c r="D119">
         <v>550</v>
@@ -6966,1215 +7072,1732 @@
       <c r="O119">
         <v>46.9</v>
       </c>
-      <c r="P119" t="s">
+      <c r="R119" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>211</v>
+      </c>
+      <c r="B120" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" t="s">
+        <v>243</v>
+      </c>
+      <c r="D120">
+        <v>240</v>
+      </c>
+      <c r="E120">
+        <v>900</v>
+      </c>
+      <c r="F120">
+        <v>830</v>
+      </c>
+      <c r="G120">
+        <v>610</v>
+      </c>
+      <c r="H120">
+        <v>610</v>
+      </c>
+      <c r="I120">
+        <v>1000</v>
+      </c>
+      <c r="J120">
+        <v>300</v>
+      </c>
+      <c r="K120">
+        <v>700</v>
+      </c>
+      <c r="L120">
+        <v>700</v>
+      </c>
+      <c r="N120">
+        <v>360</v>
+      </c>
+      <c r="O120">
+        <v>31</v>
+      </c>
+      <c r="R120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" t="s">
+        <v>242</v>
+      </c>
+      <c r="C121" t="s">
+        <v>244</v>
+      </c>
+      <c r="D121">
+        <v>350</v>
+      </c>
+      <c r="E121">
+        <v>1050</v>
+      </c>
+      <c r="F121">
+        <v>950</v>
+      </c>
+      <c r="G121">
+        <v>710</v>
+      </c>
+      <c r="H121">
+        <v>710</v>
+      </c>
+      <c r="I121">
+        <v>1200</v>
+      </c>
+      <c r="J121">
+        <v>400</v>
+      </c>
+      <c r="K121">
+        <v>800</v>
+      </c>
+      <c r="L121">
+        <v>800</v>
+      </c>
+      <c r="N121">
+        <v>525</v>
+      </c>
+      <c r="O121">
+        <v>37.4</v>
+      </c>
+      <c r="R121" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>211</v>
+      </c>
+      <c r="B122" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" t="s">
+        <v>245</v>
+      </c>
+      <c r="D122">
+        <v>460</v>
+      </c>
+      <c r="E122">
+        <v>1150</v>
+      </c>
+      <c r="F122">
+        <v>1050</v>
+      </c>
+      <c r="G122">
+        <v>820</v>
+      </c>
+      <c r="H122">
+        <v>820</v>
+      </c>
+      <c r="I122">
+        <v>1300</v>
+      </c>
+      <c r="J122">
+        <v>400</v>
+      </c>
+      <c r="K122">
+        <v>900</v>
+      </c>
+      <c r="L122">
+        <v>900</v>
+      </c>
+      <c r="N122">
+        <v>690</v>
+      </c>
+      <c r="O122">
+        <v>42.9</v>
+      </c>
+      <c r="R122" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>97</v>
+      </c>
+      <c r="B123" t="s">
+        <v>98</v>
+      </c>
+      <c r="C123" t="s">
+        <v>99</v>
+      </c>
+      <c r="D123">
+        <v>55</v>
+      </c>
+      <c r="E123">
+        <v>560</v>
+      </c>
+      <c r="F123">
+        <v>510</v>
+      </c>
+      <c r="G123">
+        <v>360</v>
+      </c>
+      <c r="H123">
+        <v>360</v>
+      </c>
+      <c r="I123">
+        <v>600</v>
+      </c>
+      <c r="J123">
+        <v>200</v>
+      </c>
+      <c r="K123">
+        <v>400</v>
+      </c>
+      <c r="L123">
+        <v>350</v>
+      </c>
+      <c r="N123">
+        <v>82.5</v>
+      </c>
+      <c r="O123">
+        <v>14.8</v>
+      </c>
+      <c r="R123" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" t="s">
+        <v>98</v>
+      </c>
+      <c r="C124" t="s">
+        <v>101</v>
+      </c>
+      <c r="D124">
         <v>75</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="E124">
+        <v>630</v>
+      </c>
+      <c r="F124">
+        <v>580</v>
+      </c>
+      <c r="G124">
+        <v>410</v>
+      </c>
+      <c r="H124">
+        <v>410</v>
+      </c>
+      <c r="I124">
+        <v>700</v>
+      </c>
+      <c r="J124">
+        <v>200</v>
+      </c>
+      <c r="K124">
+        <v>450</v>
+      </c>
+      <c r="L124">
+        <v>400</v>
+      </c>
+      <c r="N124">
+        <v>112.5</v>
+      </c>
+      <c r="O124">
+        <v>17.3</v>
+      </c>
+      <c r="R124" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>97</v>
+      </c>
+      <c r="B125" t="s">
         <v>98</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C125" t="s">
+        <v>103</v>
+      </c>
+      <c r="D125">
+        <v>143</v>
+      </c>
+      <c r="E125">
+        <v>750</v>
+      </c>
+      <c r="F125">
+        <v>680</v>
+      </c>
+      <c r="G125">
+        <v>510</v>
+      </c>
+      <c r="H125">
+        <v>510</v>
+      </c>
+      <c r="I125">
+        <v>800</v>
+      </c>
+      <c r="J125">
+        <v>250</v>
+      </c>
+      <c r="K125">
+        <v>550</v>
+      </c>
+      <c r="L125">
+        <v>500</v>
+      </c>
+      <c r="N125">
+        <v>214.5</v>
+      </c>
+      <c r="O125">
+        <v>23.9</v>
+      </c>
+      <c r="R125" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>97</v>
+      </c>
+      <c r="B126" t="s">
+        <v>98</v>
+      </c>
+      <c r="C126" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126">
+        <v>198</v>
+      </c>
+      <c r="E126">
+        <v>830</v>
+      </c>
+      <c r="F126">
+        <v>760</v>
+      </c>
+      <c r="G126">
+        <v>560</v>
+      </c>
+      <c r="H126">
+        <v>560</v>
+      </c>
+      <c r="I126">
+        <v>900</v>
+      </c>
+      <c r="J126">
+        <v>300</v>
+      </c>
+      <c r="K126">
+        <v>600</v>
+      </c>
+      <c r="L126">
+        <v>600</v>
+      </c>
+      <c r="N126">
+        <v>297</v>
+      </c>
+      <c r="O126">
+        <v>28.1</v>
+      </c>
+      <c r="R126" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>97</v>
+      </c>
+      <c r="B127" t="s">
+        <v>98</v>
+      </c>
+      <c r="C127" t="s">
+        <v>107</v>
+      </c>
+      <c r="D127">
+        <v>308</v>
+      </c>
+      <c r="E127">
+        <v>900</v>
+      </c>
+      <c r="F127">
+        <v>840</v>
+      </c>
+      <c r="G127">
+        <v>610</v>
+      </c>
+      <c r="H127">
+        <v>610</v>
+      </c>
+      <c r="I127">
+        <v>1000</v>
+      </c>
+      <c r="J127">
+        <v>300</v>
+      </c>
+      <c r="K127">
+        <v>700</v>
+      </c>
+      <c r="L127">
+        <v>700</v>
+      </c>
+      <c r="N127">
+        <v>462</v>
+      </c>
+      <c r="O127">
+        <v>35.1</v>
+      </c>
+      <c r="R127" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>97</v>
+      </c>
+      <c r="B128" t="s">
+        <v>98</v>
+      </c>
+      <c r="C128" t="s">
+        <v>108</v>
+      </c>
+      <c r="D128">
+        <v>385</v>
+      </c>
+      <c r="E128">
+        <v>1020</v>
+      </c>
+      <c r="F128">
+        <v>950</v>
+      </c>
+      <c r="G128">
+        <v>710</v>
+      </c>
+      <c r="H128">
+        <v>710</v>
+      </c>
+      <c r="I128">
+        <v>1200</v>
+      </c>
+      <c r="J128">
+        <v>350</v>
+      </c>
+      <c r="K128">
+        <v>800</v>
+      </c>
+      <c r="L128">
+        <v>800</v>
+      </c>
+      <c r="N128">
+        <v>577.5</v>
+      </c>
+      <c r="O128">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="R128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>97</v>
+      </c>
+      <c r="B129" t="s">
+        <v>98</v>
+      </c>
+      <c r="C129" t="s">
+        <v>110</v>
+      </c>
+      <c r="D129">
+        <v>495</v>
+      </c>
+      <c r="E129">
+        <v>1150</v>
+      </c>
+      <c r="F129">
+        <v>1050</v>
+      </c>
+      <c r="G129">
+        <v>820</v>
+      </c>
+      <c r="H129">
+        <v>820</v>
+      </c>
+      <c r="I129">
+        <v>1300</v>
+      </c>
+      <c r="J129">
+        <v>400</v>
+      </c>
+      <c r="K129">
+        <v>900</v>
+      </c>
+      <c r="L129">
+        <v>900</v>
+      </c>
+      <c r="N129">
+        <v>742.5</v>
+      </c>
+      <c r="O129">
+        <v>44.5</v>
+      </c>
+      <c r="R129" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>97</v>
+      </c>
+      <c r="B130" t="s">
+        <v>98</v>
+      </c>
+      <c r="C130" t="s">
+        <v>112</v>
+      </c>
+      <c r="D130">
+        <v>550</v>
+      </c>
+      <c r="E130">
+        <v>1250</v>
+      </c>
+      <c r="F130">
+        <v>1150</v>
+      </c>
+      <c r="G130">
+        <v>920</v>
+      </c>
+      <c r="H130">
+        <v>920</v>
+      </c>
+      <c r="I130">
+        <v>1400</v>
+      </c>
+      <c r="J130">
+        <v>450</v>
+      </c>
+      <c r="K130">
+        <v>1000</v>
+      </c>
+      <c r="L130">
+        <v>1000</v>
+      </c>
+      <c r="N130">
+        <v>825</v>
+      </c>
+      <c r="O130">
+        <v>46.9</v>
+      </c>
+      <c r="R130" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>97</v>
+      </c>
+      <c r="B131" t="s">
+        <v>113</v>
+      </c>
+      <c r="C131" t="s">
         <v>114</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D131">
+        <v>143</v>
+      </c>
+      <c r="E131">
+        <v>750</v>
+      </c>
+      <c r="F131">
+        <v>680</v>
+      </c>
+      <c r="G131">
+        <v>510</v>
+      </c>
+      <c r="H131">
+        <v>510</v>
+      </c>
+      <c r="I131">
+        <v>800</v>
+      </c>
+      <c r="J131">
+        <v>250</v>
+      </c>
+      <c r="K131">
+        <v>550</v>
+      </c>
+      <c r="L131">
+        <v>500</v>
+      </c>
+      <c r="N131">
+        <v>214.5</v>
+      </c>
+      <c r="O131">
+        <v>23.9</v>
+      </c>
+      <c r="R131" t="s">
         <v>115</v>
       </c>
-      <c r="D120">
-        <v>143</v>
-      </c>
-      <c r="E120">
-        <v>750</v>
-      </c>
-      <c r="F120">
-        <v>680</v>
-      </c>
-      <c r="G120">
-        <v>510</v>
-      </c>
-      <c r="H120">
-        <v>510</v>
-      </c>
-      <c r="I120">
-        <v>800</v>
-      </c>
-      <c r="J120">
-        <v>250</v>
-      </c>
-      <c r="K120">
-        <v>550</v>
-      </c>
-      <c r="L120">
-        <v>500</v>
-      </c>
-      <c r="N120">
-        <v>214.5</v>
-      </c>
-      <c r="O120">
-        <v>23.9</v>
-      </c>
-      <c r="P120" t="s">
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>97</v>
+      </c>
+      <c r="B132" t="s">
+        <v>113</v>
+      </c>
+      <c r="C132" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>98</v>
-      </c>
-      <c r="B121" t="s">
-        <v>114</v>
-      </c>
-      <c r="C121" t="s">
-        <v>117</v>
-      </c>
-      <c r="D121">
+      <c r="D132">
         <v>198</v>
       </c>
-      <c r="E121">
+      <c r="E132">
         <v>830</v>
       </c>
-      <c r="F121">
+      <c r="F132">
         <v>760</v>
       </c>
-      <c r="G121">
+      <c r="G132">
         <v>560</v>
       </c>
-      <c r="H121">
+      <c r="H132">
         <v>560</v>
       </c>
-      <c r="I121">
+      <c r="I132">
         <v>900</v>
-      </c>
-      <c r="J121">
-        <v>300</v>
-      </c>
-      <c r="K121">
-        <v>600</v>
-      </c>
-      <c r="L121">
-        <v>600</v>
-      </c>
-      <c r="N121">
-        <v>297</v>
-      </c>
-      <c r="O121">
-        <v>28.1</v>
-      </c>
-      <c r="P121" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>98</v>
-      </c>
-      <c r="B122" t="s">
-        <v>114</v>
-      </c>
-      <c r="C122" t="s">
-        <v>119</v>
-      </c>
-      <c r="D122">
-        <v>242</v>
-      </c>
-      <c r="E122">
-        <v>880</v>
-      </c>
-      <c r="F122">
-        <v>810</v>
-      </c>
-      <c r="G122">
-        <v>610</v>
-      </c>
-      <c r="H122">
-        <v>610</v>
-      </c>
-      <c r="I122">
-        <v>1000</v>
-      </c>
-      <c r="J122">
-        <v>300</v>
-      </c>
-      <c r="K122">
-        <v>700</v>
-      </c>
-      <c r="L122">
-        <v>700</v>
-      </c>
-      <c r="N122">
-        <v>363</v>
-      </c>
-      <c r="O122">
-        <v>31.1</v>
-      </c>
-      <c r="P122" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>98</v>
-      </c>
-      <c r="B123" t="s">
-        <v>114</v>
-      </c>
-      <c r="C123" t="s">
-        <v>121</v>
-      </c>
-      <c r="D123">
-        <v>308</v>
-      </c>
-      <c r="E123">
-        <v>950</v>
-      </c>
-      <c r="F123">
-        <v>850</v>
-      </c>
-      <c r="G123">
-        <v>660</v>
-      </c>
-      <c r="H123">
-        <v>660</v>
-      </c>
-      <c r="I123">
-        <v>1100</v>
-      </c>
-      <c r="J123">
-        <v>350</v>
-      </c>
-      <c r="K123">
-        <v>750</v>
-      </c>
-      <c r="L123">
-        <v>750</v>
-      </c>
-      <c r="N123">
-        <v>462</v>
-      </c>
-      <c r="O123">
-        <v>35.1</v>
-      </c>
-      <c r="P123" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>98</v>
-      </c>
-      <c r="B124" t="s">
-        <v>114</v>
-      </c>
-      <c r="C124" t="s">
-        <v>123</v>
-      </c>
-      <c r="D124">
-        <v>385</v>
-      </c>
-      <c r="E124">
-        <v>1050</v>
-      </c>
-      <c r="F124">
-        <v>950</v>
-      </c>
-      <c r="G124">
-        <v>710</v>
-      </c>
-      <c r="H124">
-        <v>710</v>
-      </c>
-      <c r="I124">
-        <v>1200</v>
-      </c>
-      <c r="J124">
-        <v>400</v>
-      </c>
-      <c r="K124">
-        <v>800</v>
-      </c>
-      <c r="L124">
-        <v>800</v>
-      </c>
-      <c r="N124">
-        <v>577.5</v>
-      </c>
-      <c r="O124">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="P124" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>98</v>
-      </c>
-      <c r="B125" t="s">
-        <v>125</v>
-      </c>
-      <c r="C125" t="s">
-        <v>126</v>
-      </c>
-      <c r="D125">
-        <v>33</v>
-      </c>
-      <c r="E125">
-        <v>450</v>
-      </c>
-      <c r="F125">
-        <v>420</v>
-      </c>
-      <c r="G125">
-        <v>300</v>
-      </c>
-      <c r="H125">
-        <v>300</v>
-      </c>
-      <c r="I125">
-        <v>500</v>
-      </c>
-      <c r="J125">
-        <v>150</v>
-      </c>
-      <c r="K125">
-        <v>300</v>
-      </c>
-      <c r="L125">
-        <v>300</v>
-      </c>
-      <c r="N125">
-        <v>49.5</v>
-      </c>
-      <c r="O125">
-        <v>11.5</v>
-      </c>
-      <c r="P125" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>98</v>
-      </c>
-      <c r="B126" t="s">
-        <v>125</v>
-      </c>
-      <c r="C126" t="s">
-        <v>128</v>
-      </c>
-      <c r="D126">
-        <v>55</v>
-      </c>
-      <c r="E126">
-        <v>560</v>
-      </c>
-      <c r="F126">
-        <v>510</v>
-      </c>
-      <c r="G126">
-        <v>360</v>
-      </c>
-      <c r="H126">
-        <v>360</v>
-      </c>
-      <c r="I126">
-        <v>600</v>
-      </c>
-      <c r="J126">
-        <v>200</v>
-      </c>
-      <c r="K126">
-        <v>400</v>
-      </c>
-      <c r="L126">
-        <v>350</v>
-      </c>
-      <c r="N126">
-        <v>82.5</v>
-      </c>
-      <c r="O126">
-        <v>14.8</v>
-      </c>
-      <c r="P126" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>98</v>
-      </c>
-      <c r="B127" t="s">
-        <v>125</v>
-      </c>
-      <c r="C127" t="s">
-        <v>130</v>
-      </c>
-      <c r="D127">
-        <v>75</v>
-      </c>
-      <c r="E127">
-        <v>630</v>
-      </c>
-      <c r="F127">
-        <v>580</v>
-      </c>
-      <c r="G127">
-        <v>410</v>
-      </c>
-      <c r="H127">
-        <v>410</v>
-      </c>
-      <c r="I127">
-        <v>700</v>
-      </c>
-      <c r="J127">
-        <v>200</v>
-      </c>
-      <c r="K127">
-        <v>450</v>
-      </c>
-      <c r="L127">
-        <v>400</v>
-      </c>
-      <c r="N127">
-        <v>112.5</v>
-      </c>
-      <c r="O127">
-        <v>17.3</v>
-      </c>
-      <c r="P127" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>98</v>
-      </c>
-      <c r="B128" t="s">
-        <v>125</v>
-      </c>
-      <c r="C128" t="s">
-        <v>132</v>
-      </c>
-      <c r="D128">
-        <v>143</v>
-      </c>
-      <c r="E128">
-        <v>750</v>
-      </c>
-      <c r="F128">
-        <v>680</v>
-      </c>
-      <c r="G128">
-        <v>510</v>
-      </c>
-      <c r="H128">
-        <v>510</v>
-      </c>
-      <c r="I128">
-        <v>800</v>
-      </c>
-      <c r="J128">
-        <v>250</v>
-      </c>
-      <c r="K128">
-        <v>550</v>
-      </c>
-      <c r="L128">
-        <v>500</v>
-      </c>
-      <c r="N128">
-        <v>214.5</v>
-      </c>
-      <c r="O128">
-        <v>23.9</v>
-      </c>
-      <c r="P128" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>98</v>
-      </c>
-      <c r="B129" t="s">
-        <v>125</v>
-      </c>
-      <c r="C129" t="s">
-        <v>133</v>
-      </c>
-      <c r="D129">
-        <v>198</v>
-      </c>
-      <c r="E129">
-        <v>830</v>
-      </c>
-      <c r="F129">
-        <v>760</v>
-      </c>
-      <c r="G129">
-        <v>560</v>
-      </c>
-      <c r="H129">
-        <v>560</v>
-      </c>
-      <c r="I129">
-        <v>900</v>
-      </c>
-      <c r="J129">
-        <v>300</v>
-      </c>
-      <c r="K129">
-        <v>600</v>
-      </c>
-      <c r="L129">
-        <v>600</v>
-      </c>
-      <c r="N129">
-        <v>297</v>
-      </c>
-      <c r="O129">
-        <v>28.1</v>
-      </c>
-      <c r="P129" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>98</v>
-      </c>
-      <c r="B130" t="s">
-        <v>125</v>
-      </c>
-      <c r="C130" t="s">
-        <v>135</v>
-      </c>
-      <c r="D130">
-        <v>308</v>
-      </c>
-      <c r="E130">
-        <v>900</v>
-      </c>
-      <c r="F130">
-        <v>840</v>
-      </c>
-      <c r="G130">
-        <v>610</v>
-      </c>
-      <c r="H130">
-        <v>610</v>
-      </c>
-      <c r="I130">
-        <v>1000</v>
-      </c>
-      <c r="J130">
-        <v>300</v>
-      </c>
-      <c r="K130">
-        <v>700</v>
-      </c>
-      <c r="L130">
-        <v>700</v>
-      </c>
-      <c r="N130">
-        <v>462</v>
-      </c>
-      <c r="O130">
-        <v>35.1</v>
-      </c>
-      <c r="P130" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>98</v>
-      </c>
-      <c r="B131" t="s">
-        <v>125</v>
-      </c>
-      <c r="C131" t="s">
-        <v>136</v>
-      </c>
-      <c r="D131">
-        <v>385</v>
-      </c>
-      <c r="E131">
-        <v>1020</v>
-      </c>
-      <c r="F131">
-        <v>950</v>
-      </c>
-      <c r="G131">
-        <v>710</v>
-      </c>
-      <c r="H131">
-        <v>710</v>
-      </c>
-      <c r="I131">
-        <v>1200</v>
-      </c>
-      <c r="J131">
-        <v>350</v>
-      </c>
-      <c r="K131">
-        <v>800</v>
-      </c>
-      <c r="L131">
-        <v>800</v>
-      </c>
-      <c r="N131">
-        <v>577.5</v>
-      </c>
-      <c r="O131">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="P131" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>98</v>
-      </c>
-      <c r="B132" t="s">
-        <v>138</v>
-      </c>
-      <c r="C132" t="s">
-        <v>139</v>
-      </c>
-      <c r="D132">
-        <v>220</v>
-      </c>
-      <c r="E132">
-        <v>880</v>
-      </c>
-      <c r="F132">
-        <v>810</v>
-      </c>
-      <c r="G132">
-        <v>610</v>
-      </c>
-      <c r="H132">
-        <v>610</v>
-      </c>
-      <c r="I132">
-        <v>1000</v>
       </c>
       <c r="J132">
         <v>300</v>
       </c>
       <c r="K132">
+        <v>600</v>
+      </c>
+      <c r="L132">
+        <v>600</v>
+      </c>
+      <c r="N132">
+        <v>297</v>
+      </c>
+      <c r="O132">
+        <v>28.1</v>
+      </c>
+      <c r="R132" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>97</v>
+      </c>
+      <c r="B133" t="s">
+        <v>113</v>
+      </c>
+      <c r="C133" t="s">
+        <v>118</v>
+      </c>
+      <c r="D133">
+        <v>242</v>
+      </c>
+      <c r="E133">
+        <v>880</v>
+      </c>
+      <c r="F133">
+        <v>810</v>
+      </c>
+      <c r="G133">
+        <v>610</v>
+      </c>
+      <c r="H133">
+        <v>610</v>
+      </c>
+      <c r="I133">
+        <v>1000</v>
+      </c>
+      <c r="J133">
+        <v>300</v>
+      </c>
+      <c r="K133">
         <v>700</v>
       </c>
-      <c r="L132">
+      <c r="L133">
         <v>700</v>
       </c>
-      <c r="N132">
+      <c r="N133">
+        <v>363</v>
+      </c>
+      <c r="O133">
+        <v>31.1</v>
+      </c>
+      <c r="R133" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>97</v>
+      </c>
+      <c r="B134" t="s">
+        <v>113</v>
+      </c>
+      <c r="C134" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134">
+        <v>308</v>
+      </c>
+      <c r="E134">
+        <v>950</v>
+      </c>
+      <c r="F134">
+        <v>850</v>
+      </c>
+      <c r="G134">
+        <v>660</v>
+      </c>
+      <c r="H134">
+        <v>660</v>
+      </c>
+      <c r="I134">
+        <v>1100</v>
+      </c>
+      <c r="J134">
+        <v>350</v>
+      </c>
+      <c r="K134">
+        <v>750</v>
+      </c>
+      <c r="L134">
+        <v>750</v>
+      </c>
+      <c r="N134">
+        <v>462</v>
+      </c>
+      <c r="O134">
+        <v>35.1</v>
+      </c>
+      <c r="R134" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>97</v>
+      </c>
+      <c r="B135" t="s">
+        <v>113</v>
+      </c>
+      <c r="C135" t="s">
+        <v>122</v>
+      </c>
+      <c r="D135">
+        <v>385</v>
+      </c>
+      <c r="E135">
+        <v>1050</v>
+      </c>
+      <c r="F135">
+        <v>950</v>
+      </c>
+      <c r="G135">
+        <v>710</v>
+      </c>
+      <c r="H135">
+        <v>710</v>
+      </c>
+      <c r="I135">
+        <v>1200</v>
+      </c>
+      <c r="J135">
+        <v>400</v>
+      </c>
+      <c r="K135">
+        <v>800</v>
+      </c>
+      <c r="L135">
+        <v>800</v>
+      </c>
+      <c r="N135">
+        <v>577.5</v>
+      </c>
+      <c r="O135">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="R135" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>97</v>
+      </c>
+      <c r="B136" t="s">
+        <v>124</v>
+      </c>
+      <c r="C136" t="s">
+        <v>125</v>
+      </c>
+      <c r="D136">
+        <v>33</v>
+      </c>
+      <c r="E136">
+        <v>450</v>
+      </c>
+      <c r="F136">
+        <v>420</v>
+      </c>
+      <c r="G136">
+        <v>300</v>
+      </c>
+      <c r="H136">
+        <v>300</v>
+      </c>
+      <c r="I136">
+        <v>500</v>
+      </c>
+      <c r="J136">
+        <v>150</v>
+      </c>
+      <c r="K136">
+        <v>300</v>
+      </c>
+      <c r="L136">
+        <v>300</v>
+      </c>
+      <c r="N136">
+        <v>49.5</v>
+      </c>
+      <c r="O136">
+        <v>11.5</v>
+      </c>
+      <c r="R136" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>97</v>
+      </c>
+      <c r="B137" t="s">
+        <v>124</v>
+      </c>
+      <c r="C137" t="s">
+        <v>127</v>
+      </c>
+      <c r="D137">
+        <v>55</v>
+      </c>
+      <c r="E137">
+        <v>560</v>
+      </c>
+      <c r="F137">
+        <v>510</v>
+      </c>
+      <c r="G137">
+        <v>360</v>
+      </c>
+      <c r="H137">
+        <v>360</v>
+      </c>
+      <c r="I137">
+        <v>600</v>
+      </c>
+      <c r="J137">
+        <v>200</v>
+      </c>
+      <c r="K137">
+        <v>400</v>
+      </c>
+      <c r="L137">
+        <v>350</v>
+      </c>
+      <c r="N137">
+        <v>82.5</v>
+      </c>
+      <c r="O137">
+        <v>14.8</v>
+      </c>
+      <c r="R137" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>97</v>
+      </c>
+      <c r="B138" t="s">
+        <v>124</v>
+      </c>
+      <c r="C138" t="s">
+        <v>129</v>
+      </c>
+      <c r="D138">
+        <v>75</v>
+      </c>
+      <c r="E138">
+        <v>630</v>
+      </c>
+      <c r="F138">
+        <v>580</v>
+      </c>
+      <c r="G138">
+        <v>410</v>
+      </c>
+      <c r="H138">
+        <v>410</v>
+      </c>
+      <c r="I138">
+        <v>700</v>
+      </c>
+      <c r="J138">
+        <v>200</v>
+      </c>
+      <c r="K138">
+        <v>450</v>
+      </c>
+      <c r="L138">
+        <v>400</v>
+      </c>
+      <c r="N138">
+        <v>112.5</v>
+      </c>
+      <c r="O138">
+        <v>17.3</v>
+      </c>
+      <c r="R138" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>97</v>
+      </c>
+      <c r="B139" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" t="s">
+        <v>131</v>
+      </c>
+      <c r="D139">
+        <v>143</v>
+      </c>
+      <c r="E139">
+        <v>750</v>
+      </c>
+      <c r="F139">
+        <v>680</v>
+      </c>
+      <c r="G139">
+        <v>510</v>
+      </c>
+      <c r="H139">
+        <v>510</v>
+      </c>
+      <c r="I139">
+        <v>800</v>
+      </c>
+      <c r="J139">
+        <v>250</v>
+      </c>
+      <c r="K139">
+        <v>550</v>
+      </c>
+      <c r="L139">
+        <v>500</v>
+      </c>
+      <c r="N139">
+        <v>214.5</v>
+      </c>
+      <c r="O139">
+        <v>23.9</v>
+      </c>
+      <c r="R139" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>97</v>
+      </c>
+      <c r="B140" t="s">
+        <v>124</v>
+      </c>
+      <c r="C140" t="s">
+        <v>132</v>
+      </c>
+      <c r="D140">
+        <v>198</v>
+      </c>
+      <c r="E140">
+        <v>830</v>
+      </c>
+      <c r="F140">
+        <v>760</v>
+      </c>
+      <c r="G140">
+        <v>560</v>
+      </c>
+      <c r="H140">
+        <v>560</v>
+      </c>
+      <c r="I140">
+        <v>900</v>
+      </c>
+      <c r="J140">
+        <v>300</v>
+      </c>
+      <c r="K140">
+        <v>600</v>
+      </c>
+      <c r="L140">
+        <v>600</v>
+      </c>
+      <c r="N140">
+        <v>297</v>
+      </c>
+      <c r="O140">
+        <v>28.1</v>
+      </c>
+      <c r="R140" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>97</v>
+      </c>
+      <c r="B141" t="s">
+        <v>124</v>
+      </c>
+      <c r="C141" t="s">
+        <v>134</v>
+      </c>
+      <c r="D141">
+        <v>308</v>
+      </c>
+      <c r="E141">
+        <v>900</v>
+      </c>
+      <c r="F141">
+        <v>840</v>
+      </c>
+      <c r="G141">
+        <v>610</v>
+      </c>
+      <c r="H141">
+        <v>610</v>
+      </c>
+      <c r="I141">
+        <v>1000</v>
+      </c>
+      <c r="J141">
+        <v>300</v>
+      </c>
+      <c r="K141">
+        <v>700</v>
+      </c>
+      <c r="L141">
+        <v>700</v>
+      </c>
+      <c r="N141">
+        <v>462</v>
+      </c>
+      <c r="O141">
+        <v>35.1</v>
+      </c>
+      <c r="R141" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>97</v>
+      </c>
+      <c r="B142" t="s">
+        <v>124</v>
+      </c>
+      <c r="C142" t="s">
+        <v>135</v>
+      </c>
+      <c r="D142">
+        <v>385</v>
+      </c>
+      <c r="E142">
+        <v>1020</v>
+      </c>
+      <c r="F142">
+        <v>950</v>
+      </c>
+      <c r="G142">
+        <v>710</v>
+      </c>
+      <c r="H142">
+        <v>710</v>
+      </c>
+      <c r="I142">
+        <v>1200</v>
+      </c>
+      <c r="J142">
+        <v>350</v>
+      </c>
+      <c r="K142">
+        <v>800</v>
+      </c>
+      <c r="L142">
+        <v>800</v>
+      </c>
+      <c r="N142">
+        <v>577.5</v>
+      </c>
+      <c r="O142">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="R142" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>97</v>
+      </c>
+      <c r="B143" t="s">
+        <v>137</v>
+      </c>
+      <c r="C143" t="s">
+        <v>138</v>
+      </c>
+      <c r="D143">
+        <v>220</v>
+      </c>
+      <c r="E143">
+        <v>880</v>
+      </c>
+      <c r="F143">
+        <v>810</v>
+      </c>
+      <c r="G143">
+        <v>610</v>
+      </c>
+      <c r="H143">
+        <v>610</v>
+      </c>
+      <c r="I143">
+        <v>1000</v>
+      </c>
+      <c r="J143">
+        <v>300</v>
+      </c>
+      <c r="K143">
+        <v>700</v>
+      </c>
+      <c r="L143">
+        <v>700</v>
+      </c>
+      <c r="N143">
         <v>330</v>
       </c>
-      <c r="O132">
+      <c r="O143">
         <v>29.7</v>
       </c>
-      <c r="P132" t="s">
+      <c r="R143" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>97</v>
+      </c>
+      <c r="B144" t="s">
+        <v>137</v>
+      </c>
+      <c r="C144" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>98</v>
-      </c>
-      <c r="B133" t="s">
-        <v>138</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="D144">
+        <v>350</v>
+      </c>
+      <c r="E144">
+        <v>1050</v>
+      </c>
+      <c r="F144">
+        <v>950</v>
+      </c>
+      <c r="G144">
+        <v>710</v>
+      </c>
+      <c r="H144">
+        <v>710</v>
+      </c>
+      <c r="I144">
+        <v>1200</v>
+      </c>
+      <c r="J144">
+        <v>400</v>
+      </c>
+      <c r="K144">
+        <v>800</v>
+      </c>
+      <c r="L144">
+        <v>800</v>
+      </c>
+      <c r="N144">
+        <v>525</v>
+      </c>
+      <c r="O144">
+        <v>37.4</v>
+      </c>
+      <c r="R144" t="s">
         <v>141</v>
       </c>
-      <c r="D133">
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>97</v>
+      </c>
+      <c r="B145" t="s">
+        <v>137</v>
+      </c>
+      <c r="C145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D145">
+        <v>450</v>
+      </c>
+      <c r="E145">
+        <v>1150</v>
+      </c>
+      <c r="F145">
+        <v>1050</v>
+      </c>
+      <c r="G145">
+        <v>820</v>
+      </c>
+      <c r="H145">
+        <v>820</v>
+      </c>
+      <c r="I145">
+        <v>1300</v>
+      </c>
+      <c r="J145">
+        <v>400</v>
+      </c>
+      <c r="K145">
+        <v>900</v>
+      </c>
+      <c r="L145">
+        <v>900</v>
+      </c>
+      <c r="N145">
+        <v>675</v>
+      </c>
+      <c r="O145">
+        <v>42.4</v>
+      </c>
+      <c r="R145" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>97</v>
+      </c>
+      <c r="B146" t="s">
+        <v>137</v>
+      </c>
+      <c r="C146" t="s">
+        <v>144</v>
+      </c>
+      <c r="D146">
+        <v>500</v>
+      </c>
+      <c r="E146">
+        <v>1250</v>
+      </c>
+      <c r="F146">
+        <v>1150</v>
+      </c>
+      <c r="G146">
+        <v>920</v>
+      </c>
+      <c r="H146">
+        <v>920</v>
+      </c>
+      <c r="I146">
+        <v>1400</v>
+      </c>
+      <c r="J146">
+        <v>450</v>
+      </c>
+      <c r="K146">
+        <v>1000</v>
+      </c>
+      <c r="L146">
+        <v>1000</v>
+      </c>
+      <c r="N146">
+        <v>750</v>
+      </c>
+      <c r="O146">
+        <v>44.7</v>
+      </c>
+      <c r="R146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>97</v>
+      </c>
+      <c r="B147" t="s">
+        <v>146</v>
+      </c>
+      <c r="C147" t="s">
+        <v>147</v>
+      </c>
+      <c r="D147">
+        <v>231</v>
+      </c>
+      <c r="E147">
+        <v>880</v>
+      </c>
+      <c r="F147">
+        <v>810</v>
+      </c>
+      <c r="G147">
+        <v>610</v>
+      </c>
+      <c r="H147">
+        <v>610</v>
+      </c>
+      <c r="I147">
+        <v>1000</v>
+      </c>
+      <c r="J147">
+        <v>300</v>
+      </c>
+      <c r="K147">
+        <v>700</v>
+      </c>
+      <c r="L147">
+        <v>700</v>
+      </c>
+      <c r="N147">
+        <v>346.5</v>
+      </c>
+      <c r="O147">
+        <v>30.4</v>
+      </c>
+      <c r="R147" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>97</v>
+      </c>
+      <c r="B148" t="s">
+        <v>146</v>
+      </c>
+      <c r="C148" t="s">
+        <v>149</v>
+      </c>
+      <c r="D148">
+        <v>308</v>
+      </c>
+      <c r="E148">
+        <v>950</v>
+      </c>
+      <c r="F148">
+        <v>850</v>
+      </c>
+      <c r="G148">
+        <v>660</v>
+      </c>
+      <c r="H148">
+        <v>660</v>
+      </c>
+      <c r="I148">
+        <v>1100</v>
+      </c>
+      <c r="J148">
         <v>350</v>
       </c>
-      <c r="E133">
+      <c r="K148">
+        <v>750</v>
+      </c>
+      <c r="L148">
+        <v>750</v>
+      </c>
+      <c r="N148">
+        <v>462</v>
+      </c>
+      <c r="O148">
+        <v>35.1</v>
+      </c>
+      <c r="R148" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>97</v>
+      </c>
+      <c r="B149" t="s">
+        <v>146</v>
+      </c>
+      <c r="C149" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149">
+        <v>385</v>
+      </c>
+      <c r="E149">
         <v>1050</v>
       </c>
-      <c r="F133">
+      <c r="F149">
         <v>950</v>
       </c>
-      <c r="G133">
+      <c r="G149">
         <v>710</v>
       </c>
-      <c r="H133">
+      <c r="H149">
         <v>710</v>
       </c>
-      <c r="I133">
+      <c r="I149">
         <v>1200</v>
       </c>
-      <c r="J133">
+      <c r="J149">
         <v>400</v>
       </c>
-      <c r="K133">
+      <c r="K149">
         <v>800</v>
       </c>
-      <c r="L133">
+      <c r="L149">
         <v>800</v>
       </c>
-      <c r="N133">
-        <v>525</v>
-      </c>
-      <c r="O133">
-        <v>37.4</v>
-      </c>
-      <c r="P133" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>98</v>
-      </c>
-      <c r="B134" t="s">
-        <v>138</v>
-      </c>
-      <c r="C134" t="s">
-        <v>143</v>
-      </c>
-      <c r="D134">
+      <c r="N149">
+        <v>577.5</v>
+      </c>
+      <c r="O149">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="R149" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>97</v>
+      </c>
+      <c r="B150" t="s">
+        <v>146</v>
+      </c>
+      <c r="C150" t="s">
+        <v>152</v>
+      </c>
+      <c r="D150">
+        <v>550</v>
+      </c>
+      <c r="E150">
+        <v>1250</v>
+      </c>
+      <c r="F150">
+        <v>1150</v>
+      </c>
+      <c r="G150">
+        <v>920</v>
+      </c>
+      <c r="H150">
+        <v>920</v>
+      </c>
+      <c r="I150">
+        <v>1400</v>
+      </c>
+      <c r="J150">
         <v>450</v>
       </c>
-      <c r="E134">
-        <v>1150</v>
-      </c>
-      <c r="F134">
-        <v>1050</v>
-      </c>
-      <c r="G134">
-        <v>820</v>
-      </c>
-      <c r="H134">
-        <v>820</v>
-      </c>
-      <c r="I134">
-        <v>1300</v>
-      </c>
-      <c r="J134">
+      <c r="K150">
+        <v>1000</v>
+      </c>
+      <c r="L150">
+        <v>1000</v>
+      </c>
+      <c r="N150">
+        <v>825</v>
+      </c>
+      <c r="O150">
+        <v>46.9</v>
+      </c>
+      <c r="R150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D151" s="2">
+        <v>100</v>
+      </c>
+      <c r="E151" s="2">
+        <v>650</v>
+      </c>
+      <c r="F151" s="2">
+        <v>600</v>
+      </c>
+      <c r="G151" s="2">
+        <v>460</v>
+      </c>
+      <c r="H151" s="2">
+        <v>410</v>
+      </c>
+      <c r="I151" s="2">
+        <v>800</v>
+      </c>
+      <c r="J151" s="2">
+        <v>150</v>
+      </c>
+      <c r="K151" s="2">
+        <v>450</v>
+      </c>
+      <c r="L151" s="2">
+        <v>350</v>
+      </c>
+      <c r="M151" s="2">
+        <v>150</v>
+      </c>
+      <c r="N151" s="2">
+        <v>202</v>
+      </c>
+      <c r="O151" s="2">
+        <v>40</v>
+      </c>
+      <c r="R151" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D152" s="2">
+        <v>130</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2">
+        <v>530</v>
+      </c>
+      <c r="H152" s="2">
+        <v>530</v>
+      </c>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2">
+        <v>150</v>
+      </c>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2">
         <v>400</v>
       </c>
-      <c r="K134">
-        <v>900</v>
-      </c>
-      <c r="L134">
-        <v>900</v>
-      </c>
-      <c r="N134">
-        <v>675</v>
-      </c>
-      <c r="O134">
-        <v>42.4</v>
-      </c>
-      <c r="P134" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>98</v>
-      </c>
-      <c r="B135" t="s">
-        <v>138</v>
-      </c>
-      <c r="C135" t="s">
-        <v>145</v>
-      </c>
-      <c r="D135">
+      <c r="M152" s="2">
+        <v>150</v>
+      </c>
+      <c r="N152" s="2">
+        <v>250</v>
+      </c>
+      <c r="O152" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="R152" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D153" s="2">
+        <v>180</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2">
+        <v>570</v>
+      </c>
+      <c r="H153" s="2">
+        <v>570</v>
+      </c>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2">
+        <v>150</v>
+      </c>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2">
+        <v>450</v>
+      </c>
+      <c r="M153" s="2">
+        <v>150</v>
+      </c>
+      <c r="N153" s="2">
+        <v>300</v>
+      </c>
+      <c r="O153" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="R153" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D154" s="2">
+        <v>220</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2">
+        <v>650</v>
+      </c>
+      <c r="H154" s="2">
+        <v>650</v>
+      </c>
+      <c r="I154" s="2"/>
+      <c r="J154" s="2">
+        <v>150</v>
+      </c>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2">
         <v>500</v>
       </c>
-      <c r="E135">
-        <v>1250</v>
-      </c>
-      <c r="F135">
-        <v>1150</v>
-      </c>
-      <c r="G135">
-        <v>920</v>
-      </c>
-      <c r="H135">
-        <v>920</v>
-      </c>
-      <c r="I135">
-        <v>1400</v>
-      </c>
-      <c r="J135">
-        <v>450</v>
-      </c>
-      <c r="K135">
-        <v>1000</v>
-      </c>
-      <c r="L135">
-        <v>1000</v>
-      </c>
-      <c r="N135">
-        <v>750</v>
-      </c>
-      <c r="O135">
-        <v>44.7</v>
-      </c>
-      <c r="P135" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>98</v>
-      </c>
-      <c r="B136" t="s">
-        <v>147</v>
-      </c>
-      <c r="C136" t="s">
-        <v>148</v>
-      </c>
-      <c r="D136">
-        <v>231</v>
-      </c>
-      <c r="E136">
-        <v>880</v>
-      </c>
-      <c r="F136">
-        <v>810</v>
-      </c>
-      <c r="G136">
-        <v>610</v>
-      </c>
-      <c r="H136">
-        <v>610</v>
-      </c>
-      <c r="I136">
-        <v>1000</v>
-      </c>
-      <c r="J136">
-        <v>300</v>
-      </c>
-      <c r="K136">
+      <c r="M154" s="2">
+        <v>150</v>
+      </c>
+      <c r="N154" s="2">
+        <v>350</v>
+      </c>
+      <c r="O154" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="R154" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D155" s="2">
+        <v>500</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2">
+        <v>830</v>
+      </c>
+      <c r="H155" s="2">
+        <v>830</v>
+      </c>
+      <c r="I155" s="2"/>
+      <c r="J155" s="2">
+        <v>150</v>
+      </c>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2">
         <v>700</v>
       </c>
-      <c r="L136">
-        <v>700</v>
-      </c>
-      <c r="N136">
-        <v>346.5</v>
-      </c>
-      <c r="O136">
-        <v>30.4</v>
-      </c>
-      <c r="P136" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>98</v>
-      </c>
-      <c r="B137" t="s">
-        <v>147</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="M155" s="2">
         <v>150</v>
       </c>
-      <c r="D137">
-        <v>308</v>
-      </c>
-      <c r="E137">
-        <v>950</v>
-      </c>
-      <c r="F137">
-        <v>850</v>
-      </c>
-      <c r="G137">
-        <v>660</v>
-      </c>
-      <c r="H137">
-        <v>660</v>
-      </c>
-      <c r="I137">
-        <v>1100</v>
-      </c>
-      <c r="J137">
-        <v>350</v>
-      </c>
-      <c r="K137">
-        <v>750</v>
-      </c>
-      <c r="L137">
-        <v>750</v>
-      </c>
-      <c r="N137">
-        <v>462</v>
-      </c>
-      <c r="O137">
-        <v>35.1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>98</v>
-      </c>
-      <c r="B138" t="s">
-        <v>147</v>
-      </c>
-      <c r="C138" t="s">
-        <v>152</v>
-      </c>
-      <c r="D138">
-        <v>385</v>
-      </c>
-      <c r="E138">
-        <v>1050</v>
-      </c>
-      <c r="F138">
-        <v>950</v>
-      </c>
-      <c r="G138">
-        <v>710</v>
-      </c>
-      <c r="H138">
-        <v>710</v>
-      </c>
-      <c r="I138">
-        <v>1200</v>
-      </c>
-      <c r="J138">
-        <v>400</v>
-      </c>
-      <c r="K138">
-        <v>800</v>
-      </c>
-      <c r="L138">
-        <v>800</v>
-      </c>
-      <c r="N138">
-        <v>577.5</v>
-      </c>
-      <c r="O138">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="P138" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>98</v>
-      </c>
-      <c r="B139" t="s">
-        <v>147</v>
-      </c>
-      <c r="C139" t="s">
-        <v>153</v>
-      </c>
-      <c r="D139">
-        <v>550</v>
-      </c>
-      <c r="E139">
-        <v>1250</v>
-      </c>
-      <c r="F139">
-        <v>1150</v>
-      </c>
-      <c r="G139">
-        <v>920</v>
-      </c>
-      <c r="H139">
-        <v>920</v>
-      </c>
-      <c r="I139">
-        <v>1400</v>
-      </c>
-      <c r="J139">
-        <v>450</v>
-      </c>
-      <c r="K139">
-        <v>1000</v>
-      </c>
-      <c r="L139">
-        <v>1000</v>
-      </c>
-      <c r="N139">
-        <v>825</v>
-      </c>
-      <c r="O139">
-        <v>46.9</v>
-      </c>
-      <c r="P139" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D140" s="2">
-        <v>100</v>
-      </c>
-      <c r="E140" s="2">
-        <v>650</v>
-      </c>
-      <c r="F140" s="2">
+      <c r="N155" s="2">
         <v>600</v>
       </c>
-      <c r="G140" s="2">
-        <v>460</v>
-      </c>
-      <c r="H140" s="2">
-        <v>410</v>
-      </c>
-      <c r="I140" s="2">
-        <v>800</v>
-      </c>
-      <c r="J140" s="2">
+      <c r="O155" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="R155" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D156" s="3">
+        <v>85</v>
+      </c>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3">
+        <v>470</v>
+      </c>
+      <c r="H156" s="3">
+        <v>420</v>
+      </c>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3">
         <v>150</v>
       </c>
-      <c r="K140" s="2">
-        <v>450</v>
-      </c>
-      <c r="L140" s="2">
-        <v>350</v>
-      </c>
-      <c r="M140" s="2">
+      <c r="K156" s="3"/>
+      <c r="L156" s="3">
+        <v>320</v>
+      </c>
+      <c r="M156" s="3">
         <v>150</v>
       </c>
-      <c r="N140" s="2">
-        <v>202</v>
-      </c>
-      <c r="O140" s="2">
-        <v>40</v>
-      </c>
-      <c r="P140" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D141" s="2">
-        <v>130</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2">
-        <v>530</v>
-      </c>
-      <c r="H141" s="2">
-        <v>530</v>
-      </c>
-      <c r="I141" s="2"/>
-      <c r="J141" s="2">
-        <v>150</v>
-      </c>
-      <c r="K141" s="2"/>
-      <c r="L141" s="2">
-        <v>400</v>
-      </c>
-      <c r="M141" s="2">
-        <v>150</v>
-      </c>
-      <c r="N141" s="2">
-        <v>250</v>
-      </c>
-      <c r="O141" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="P141" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D142" s="2">
-        <v>180</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2">
-        <v>570</v>
-      </c>
-      <c r="H142" s="2">
-        <v>570</v>
-      </c>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2">
-        <v>150</v>
-      </c>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2">
-        <v>450</v>
-      </c>
-      <c r="M142" s="2">
-        <v>150</v>
-      </c>
-      <c r="N142" s="2">
-        <v>300</v>
-      </c>
-      <c r="O142" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="P142" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D143" s="2">
-        <v>220</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2">
-        <v>650</v>
-      </c>
-      <c r="H143" s="2">
-        <v>650</v>
-      </c>
-      <c r="I143" s="2"/>
-      <c r="J143" s="2">
-        <v>150</v>
-      </c>
-      <c r="K143" s="2"/>
-      <c r="L143" s="2">
-        <v>500</v>
-      </c>
-      <c r="M143" s="2">
-        <v>150</v>
-      </c>
-      <c r="N143" s="2">
-        <v>350</v>
-      </c>
-      <c r="O143" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="P143" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D144" s="2">
-        <v>500</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2">
-        <v>830</v>
-      </c>
-      <c r="H144" s="2">
-        <v>830</v>
-      </c>
-      <c r="I144" s="2"/>
-      <c r="J144" s="2">
-        <v>150</v>
-      </c>
-      <c r="K144" s="2"/>
-      <c r="L144" s="2">
-        <v>700</v>
-      </c>
-      <c r="M144" s="2">
-        <v>150</v>
-      </c>
-      <c r="N144" s="2">
-        <v>600</v>
-      </c>
-      <c r="O144" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="P144" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D145" s="3">
-        <v>85</v>
-      </c>
-      <c r="E145" s="3"/>
-      <c r="F145" s="3"/>
-      <c r="G145" s="3">
-        <v>470</v>
-      </c>
-      <c r="H145" s="3">
-        <v>420</v>
-      </c>
-      <c r="I145" s="3"/>
-      <c r="J145" s="3">
-        <v>150</v>
-      </c>
-      <c r="K145" s="3"/>
-      <c r="L145" s="3">
-        <v>320</v>
-      </c>
-      <c r="M145" s="3">
-        <v>150</v>
-      </c>
-      <c r="N145" s="3">
+      <c r="N156" s="3">
         <v>23</v>
       </c>
-      <c r="O145" s="3">
+      <c r="O156" s="3">
         <v>20</v>
       </c>
-      <c r="P145" s="3"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
+      <c r="R156" s="3"/>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O139">
-    <sortCondition ref="A2:A139"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O150">
+    <sortCondition ref="A2:A150"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC512D8A-979E-43CD-AECA-E5D11896EDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DAA7E3-18C0-4D05-B62B-CF79A71808F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="315">
   <si>
     <t>OEM</t>
   </si>
@@ -932,7 +933,52 @@
     <t>Mold Weight Moving Platen Max (kg)</t>
   </si>
   <si>
-    <t>Screw Stroke (mm)</t>
+    <t>Opening Stroke (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mold_length</t>
+  </si>
+  <si>
+    <t>value=636</t>
+  </si>
+  <si>
+    <t>mold_width</t>
+  </si>
+  <si>
+    <t>value=396</t>
+  </si>
+  <si>
+    <t>mold_height</t>
+  </si>
+  <si>
+    <t>value=458</t>
+  </si>
+  <si>
+    <t>clamp_min</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>value=50</t>
+  </si>
+  <si>
+    <t>clamp_max</t>
+  </si>
+  <si>
+    <t>value=200</t>
+  </si>
+  <si>
+    <t>shot_weight</t>
+  </si>
+  <si>
+    <t>value=15</t>
+  </si>
+  <si>
+    <t>safety_clearance = mold_height * 0.1 + 20</t>
+  </si>
+  <si>
+    <t>To add stroke/part depth</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1369,7 @@
     <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -4036,284 +4082,239 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>156</v>
+        <v>272</v>
       </c>
       <c r="D57">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E57">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F57">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G57">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="H57">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="I57">
         <v>800</v>
       </c>
       <c r="J57">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K57">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="L57">
-        <v>500</v>
+        <v>350</v>
+      </c>
+      <c r="M57">
+        <v>150</v>
       </c>
       <c r="N57">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="O57">
-        <v>22.8</v>
+        <v>40</v>
       </c>
       <c r="R57" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="D58">
-        <v>180</v>
-      </c>
-      <c r="E58">
-        <v>850</v>
-      </c>
-      <c r="F58">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="G58">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="H58">
-        <v>580</v>
-      </c>
-      <c r="I58">
-        <v>900</v>
+        <v>530</v>
       </c>
       <c r="J58">
-        <v>300</v>
-      </c>
-      <c r="K58">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="L58">
-        <v>600</v>
+        <v>400</v>
+      </c>
+      <c r="M58">
+        <v>150</v>
       </c>
       <c r="N58">
-        <v>270</v>
-      </c>
-      <c r="O58">
-        <v>26.8</v>
+        <v>250</v>
+      </c>
+      <c r="O58" t="s">
+        <v>275</v>
       </c>
       <c r="R58" t="s">
-        <v>159</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C59" t="s">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="D59">
-        <v>220</v>
-      </c>
-      <c r="E59">
-        <v>900</v>
-      </c>
-      <c r="F59">
-        <v>850</v>
+        <v>180</v>
       </c>
       <c r="G59">
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="H59">
-        <v>610</v>
-      </c>
-      <c r="I59">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="J59">
+        <v>150</v>
+      </c>
+      <c r="L59">
+        <v>450</v>
+      </c>
+      <c r="M59">
+        <v>150</v>
+      </c>
+      <c r="N59">
         <v>300</v>
       </c>
-      <c r="K59">
-        <v>700</v>
-      </c>
-      <c r="L59">
-        <v>650</v>
-      </c>
-      <c r="N59">
-        <v>330</v>
-      </c>
-      <c r="O59">
-        <v>29.7</v>
+      <c r="O59" t="s">
+        <v>278</v>
       </c>
       <c r="R59" t="s">
-        <v>161</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C60" t="s">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="D60">
-        <v>280</v>
-      </c>
-      <c r="E60">
-        <v>950</v>
-      </c>
-      <c r="F60">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="G60">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="H60">
-        <v>660</v>
-      </c>
-      <c r="I60">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="J60">
+        <v>150</v>
+      </c>
+      <c r="L60">
+        <v>500</v>
+      </c>
+      <c r="M60">
+        <v>150</v>
+      </c>
+      <c r="N60">
         <v>350</v>
       </c>
-      <c r="K60">
-        <v>750</v>
-      </c>
-      <c r="L60">
-        <v>700</v>
-      </c>
-      <c r="N60">
-        <v>420</v>
-      </c>
-      <c r="O60">
-        <v>33.5</v>
+      <c r="O60" t="s">
+        <v>281</v>
       </c>
       <c r="R60" t="s">
-        <v>163</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C61" t="s">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="D61">
-        <v>350</v>
-      </c>
-      <c r="E61">
-        <v>1050</v>
-      </c>
-      <c r="F61">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="G61">
-        <v>710</v>
+        <v>830</v>
       </c>
       <c r="H61">
-        <v>710</v>
-      </c>
-      <c r="I61">
-        <v>1200</v>
+        <v>830</v>
       </c>
       <c r="J61">
-        <v>400</v>
-      </c>
-      <c r="K61">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="L61">
-        <v>800</v>
+        <v>700</v>
+      </c>
+      <c r="M61">
+        <v>150</v>
       </c>
       <c r="N61">
-        <v>525</v>
-      </c>
-      <c r="O61">
-        <v>37.4</v>
+        <v>600</v>
+      </c>
+      <c r="O61" t="s">
+        <v>284</v>
       </c>
       <c r="R61" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="D62">
+        <v>85</v>
+      </c>
+      <c r="G62">
+        <v>470</v>
+      </c>
+      <c r="H62">
         <v>420</v>
       </c>
-      <c r="E62">
-        <v>1150</v>
-      </c>
-      <c r="F62">
-        <v>1050</v>
-      </c>
-      <c r="G62">
-        <v>820</v>
-      </c>
-      <c r="H62">
-        <v>820</v>
-      </c>
-      <c r="I62">
-        <v>1300</v>
-      </c>
       <c r="J62">
-        <v>400</v>
-      </c>
-      <c r="K62">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="L62">
-        <v>900</v>
+        <v>320</v>
+      </c>
+      <c r="M62">
+        <v>150</v>
       </c>
       <c r="N62">
-        <v>630</v>
+        <v>23</v>
       </c>
       <c r="O62">
-        <v>41</v>
-      </c>
-      <c r="R62" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -4324,43 +4325,43 @@
         <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D63">
-        <v>520</v>
+        <v>130</v>
       </c>
       <c r="E63">
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="F63">
-        <v>1150</v>
+        <v>700</v>
       </c>
       <c r="G63">
-        <v>920</v>
+        <v>500</v>
       </c>
       <c r="H63">
-        <v>920</v>
+        <v>500</v>
       </c>
       <c r="I63">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="J63">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="K63">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="L63">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N63">
-        <v>780</v>
+        <v>195</v>
       </c>
       <c r="O63">
-        <v>45.6</v>
+        <v>22.8</v>
       </c>
       <c r="R63" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -4371,43 +4372,43 @@
         <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D64">
+        <v>180</v>
+      </c>
+      <c r="E64">
+        <v>850</v>
+      </c>
+      <c r="F64">
+        <v>800</v>
+      </c>
+      <c r="G64">
+        <v>580</v>
+      </c>
+      <c r="H64">
+        <v>580</v>
+      </c>
+      <c r="I64">
+        <v>900</v>
+      </c>
+      <c r="J64">
+        <v>300</v>
+      </c>
+      <c r="K64">
         <v>600</v>
       </c>
-      <c r="E64">
-        <v>1350</v>
-      </c>
-      <c r="F64">
-        <v>1250</v>
-      </c>
-      <c r="G64">
-        <v>1020</v>
-      </c>
-      <c r="H64">
-        <v>1020</v>
-      </c>
-      <c r="I64">
-        <v>1500</v>
-      </c>
-      <c r="J64">
-        <v>500</v>
-      </c>
-      <c r="K64">
-        <v>1100</v>
-      </c>
       <c r="L64">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="N64">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="O64">
-        <v>49</v>
+        <v>26.8</v>
       </c>
       <c r="R64" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4415,46 +4416,46 @@
         <v>154</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D65">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="E65">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="F65">
+        <v>850</v>
+      </c>
+      <c r="G65">
+        <v>610</v>
+      </c>
+      <c r="H65">
+        <v>610</v>
+      </c>
+      <c r="I65">
+        <v>1000</v>
+      </c>
+      <c r="J65">
+        <v>300</v>
+      </c>
+      <c r="K65">
         <v>700</v>
       </c>
-      <c r="G65">
-        <v>500</v>
-      </c>
-      <c r="H65">
-        <v>500</v>
-      </c>
-      <c r="I65">
-        <v>800</v>
-      </c>
-      <c r="J65">
-        <v>250</v>
-      </c>
-      <c r="K65">
-        <v>550</v>
-      </c>
       <c r="L65">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="N65">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="O65">
-        <v>22.8</v>
+        <v>29.7</v>
       </c>
       <c r="R65" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -4462,46 +4463,46 @@
         <v>154</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C66" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D66">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="E66">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="F66">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G66">
-        <v>580</v>
+        <v>660</v>
       </c>
       <c r="H66">
-        <v>580</v>
+        <v>660</v>
       </c>
       <c r="I66">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="J66">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K66">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="L66">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N66">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="O66">
-        <v>26.8</v>
+        <v>33.5</v>
       </c>
       <c r="R66" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -4509,46 +4510,46 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D67">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="E67">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="F67">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="G67">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="H67">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="I67">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="J67">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K67">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L67">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="N67">
-        <v>330</v>
+        <v>525</v>
       </c>
       <c r="O67">
-        <v>29.7</v>
+        <v>37.4</v>
       </c>
       <c r="R67" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -4556,46 +4557,46 @@
         <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C68" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D68">
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="E68">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="F68">
+        <v>1050</v>
+      </c>
+      <c r="G68">
+        <v>820</v>
+      </c>
+      <c r="H68">
+        <v>820</v>
+      </c>
+      <c r="I68">
+        <v>1300</v>
+      </c>
+      <c r="J68">
+        <v>400</v>
+      </c>
+      <c r="K68">
         <v>900</v>
       </c>
-      <c r="G68">
-        <v>660</v>
-      </c>
-      <c r="H68">
-        <v>660</v>
-      </c>
-      <c r="I68">
-        <v>1100</v>
-      </c>
-      <c r="J68">
-        <v>350</v>
-      </c>
-      <c r="K68">
-        <v>750</v>
-      </c>
       <c r="L68">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="N68">
-        <v>420</v>
+        <v>630</v>
       </c>
       <c r="O68">
-        <v>33.5</v>
+        <v>41</v>
       </c>
       <c r="R68" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -4603,46 +4604,46 @@
         <v>154</v>
       </c>
       <c r="B69" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D69">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="E69">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="F69">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="G69">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="H69">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="I69">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J69">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K69">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="L69">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="N69">
-        <v>525</v>
+        <v>780</v>
       </c>
       <c r="O69">
-        <v>37.4</v>
+        <v>45.6</v>
       </c>
       <c r="R69" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -4650,46 +4651,46 @@
         <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="D70">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="E70">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="F70">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="G70">
-        <v>820</v>
+        <v>1020</v>
       </c>
       <c r="H70">
-        <v>820</v>
+        <v>1020</v>
       </c>
       <c r="I70">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="J70">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K70">
+        <v>1100</v>
+      </c>
+      <c r="L70">
+        <v>1100</v>
+      </c>
+      <c r="N70">
         <v>900</v>
       </c>
-      <c r="L70">
-        <v>900</v>
-      </c>
-      <c r="N70">
-        <v>630</v>
-      </c>
       <c r="O70">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="R70" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -4697,10 +4698,10 @@
         <v>154</v>
       </c>
       <c r="B71" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D71">
         <v>130</v>
@@ -4736,7 +4737,7 @@
         <v>22.8</v>
       </c>
       <c r="R71" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -4744,10 +4745,10 @@
         <v>154</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D72">
         <v>180</v>
@@ -4783,7 +4784,7 @@
         <v>26.8</v>
       </c>
       <c r="R72" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -4791,10 +4792,10 @@
         <v>154</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D73">
         <v>220</v>
@@ -4830,7 +4831,7 @@
         <v>29.7</v>
       </c>
       <c r="R73" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -4838,46 +4839,46 @@
         <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D74">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E74">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="F74">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="G74">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="H74">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I74">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="J74">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="K74">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="L74">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="N74">
-        <v>375</v>
+        <v>420</v>
       </c>
       <c r="O74">
-        <v>31.6</v>
+        <v>33.5</v>
       </c>
       <c r="R74" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -4885,46 +4886,46 @@
         <v>154</v>
       </c>
       <c r="B75" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D75">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E75">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="F75">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="G75">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="H75">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="I75">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J75">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K75">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="L75">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N75">
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="O75">
-        <v>34.6</v>
+        <v>37.4</v>
       </c>
       <c r="R75" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -4932,46 +4933,46 @@
         <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D76">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="E76">
+        <v>1150</v>
+      </c>
+      <c r="F76">
         <v>1050</v>
       </c>
-      <c r="F76">
-        <v>950</v>
-      </c>
       <c r="G76">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="H76">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="I76">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J76">
         <v>400</v>
       </c>
       <c r="K76">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L76">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N76">
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="O76">
-        <v>37.4</v>
+        <v>41</v>
       </c>
       <c r="R76" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -4982,43 +4983,43 @@
         <v>184</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D77">
-        <v>400</v>
+        <v>130</v>
       </c>
       <c r="E77">
-        <v>1100</v>
+        <v>750</v>
       </c>
       <c r="F77">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="G77">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="H77">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="I77">
-        <v>1250</v>
+        <v>800</v>
       </c>
       <c r="J77">
-        <v>420</v>
+        <v>250</v>
       </c>
       <c r="K77">
-        <v>850</v>
+        <v>550</v>
       </c>
       <c r="L77">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="N77">
-        <v>600</v>
+        <v>195</v>
       </c>
       <c r="O77">
-        <v>40</v>
+        <v>22.8</v>
       </c>
       <c r="R77" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -5029,43 +5030,43 @@
         <v>184</v>
       </c>
       <c r="C78" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D78">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="E78">
-        <v>1200</v>
+        <v>850</v>
       </c>
       <c r="F78">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="G78">
-        <v>820</v>
+        <v>580</v>
       </c>
       <c r="H78">
-        <v>820</v>
+        <v>580</v>
       </c>
       <c r="I78">
-        <v>1350</v>
+        <v>900</v>
       </c>
       <c r="J78">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="K78">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="L78">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="N78">
-        <v>750</v>
+        <v>270</v>
       </c>
       <c r="O78">
-        <v>44.7</v>
+        <v>26.8</v>
       </c>
       <c r="R78" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -5073,46 +5074,46 @@
         <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="E79">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="F79">
+        <v>850</v>
+      </c>
+      <c r="G79">
+        <v>610</v>
+      </c>
+      <c r="H79">
+        <v>610</v>
+      </c>
+      <c r="I79">
+        <v>1000</v>
+      </c>
+      <c r="J79">
         <v>300</v>
       </c>
-      <c r="G79">
-        <v>200</v>
-      </c>
-      <c r="H79">
-        <v>200</v>
-      </c>
-      <c r="I79">
-        <v>400</v>
-      </c>
-      <c r="J79">
-        <v>120</v>
-      </c>
       <c r="K79">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="L79">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="N79">
-        <v>19.5</v>
+        <v>330</v>
       </c>
       <c r="O79">
-        <v>7.2</v>
+        <v>29.7</v>
       </c>
       <c r="R79" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -5120,46 +5121,46 @@
         <v>154</v>
       </c>
       <c r="B80" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D80">
-        <v>33</v>
+        <v>250</v>
       </c>
       <c r="E80">
-        <v>450</v>
+        <v>930</v>
       </c>
       <c r="F80">
-        <v>420</v>
+        <v>880</v>
       </c>
       <c r="G80">
-        <v>280</v>
+        <v>640</v>
       </c>
       <c r="H80">
-        <v>280</v>
+        <v>640</v>
       </c>
       <c r="I80">
-        <v>500</v>
+        <v>1050</v>
       </c>
       <c r="J80">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="K80">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="L80">
-        <v>300</v>
+        <v>680</v>
       </c>
       <c r="N80">
-        <v>49.5</v>
+        <v>375</v>
       </c>
       <c r="O80">
-        <v>11.5</v>
+        <v>31.6</v>
       </c>
       <c r="R80" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -5167,46 +5168,46 @@
         <v>154</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D81">
-        <v>66</v>
+        <v>300</v>
       </c>
       <c r="E81">
-        <v>550</v>
+        <v>980</v>
       </c>
       <c r="F81">
-        <v>500</v>
+        <v>930</v>
       </c>
       <c r="G81">
+        <v>680</v>
+      </c>
+      <c r="H81">
+        <v>680</v>
+      </c>
+      <c r="I81">
+        <v>1100</v>
+      </c>
+      <c r="J81">
         <v>350</v>
       </c>
-      <c r="H81">
-        <v>350</v>
-      </c>
-      <c r="I81">
-        <v>600</v>
-      </c>
-      <c r="J81">
-        <v>200</v>
-      </c>
       <c r="K81">
-        <v>400</v>
+        <v>760</v>
       </c>
       <c r="L81">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="N81">
-        <v>99</v>
+        <v>450</v>
       </c>
       <c r="O81">
-        <v>16.2</v>
+        <v>34.6</v>
       </c>
       <c r="R81" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -5214,46 +5215,46 @@
         <v>154</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D82">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E82">
-        <v>650</v>
+        <v>1050</v>
       </c>
       <c r="F82">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="G82">
-        <v>420</v>
+        <v>710</v>
       </c>
       <c r="H82">
-        <v>420</v>
+        <v>710</v>
       </c>
       <c r="I82">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J82">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K82">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="L82">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="N82">
-        <v>150</v>
+        <v>525</v>
       </c>
       <c r="O82">
-        <v>20</v>
+        <v>37.4</v>
       </c>
       <c r="R82" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -5261,46 +5262,46 @@
         <v>154</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C83" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D83">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E83">
+        <v>1100</v>
+      </c>
+      <c r="F83">
+        <v>1000</v>
+      </c>
+      <c r="G83">
         <v>750</v>
       </c>
-      <c r="F83">
-        <v>680</v>
-      </c>
-      <c r="G83">
-        <v>500</v>
-      </c>
       <c r="H83">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="I83">
-        <v>800</v>
+        <v>1250</v>
       </c>
       <c r="J83">
-        <v>250</v>
+        <v>420</v>
       </c>
       <c r="K83">
-        <v>550</v>
+        <v>850</v>
       </c>
       <c r="L83">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="N83">
-        <v>225</v>
+        <v>600</v>
       </c>
       <c r="O83">
-        <v>24.5</v>
+        <v>40</v>
       </c>
       <c r="R83" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
@@ -5308,364 +5309,328 @@
         <v>154</v>
       </c>
       <c r="B84" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D84">
+        <v>500</v>
+      </c>
+      <c r="E84">
+        <v>1200</v>
+      </c>
+      <c r="F84">
+        <v>1100</v>
+      </c>
+      <c r="G84">
+        <v>820</v>
+      </c>
+      <c r="H84">
+        <v>820</v>
+      </c>
+      <c r="I84">
+        <v>1350</v>
+      </c>
+      <c r="J84">
+        <v>450</v>
+      </c>
+      <c r="K84">
+        <v>950</v>
+      </c>
+      <c r="L84">
+        <v>900</v>
+      </c>
+      <c r="N84">
+        <v>750</v>
+      </c>
+      <c r="O84">
+        <v>44.7</v>
+      </c>
+      <c r="R84" t="s">
         <v>200</v>
-      </c>
-      <c r="E84">
-        <v>830</v>
-      </c>
-      <c r="F84">
-        <v>760</v>
-      </c>
-      <c r="G84">
-        <v>560</v>
-      </c>
-      <c r="H84">
-        <v>560</v>
-      </c>
-      <c r="I84">
-        <v>900</v>
-      </c>
-      <c r="J84">
-        <v>300</v>
-      </c>
-      <c r="K84">
-        <v>600</v>
-      </c>
-      <c r="L84">
-        <v>600</v>
-      </c>
-      <c r="N84">
-        <v>300</v>
-      </c>
-      <c r="O84">
-        <v>28.3</v>
-      </c>
-      <c r="R84" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B85" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D85">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E85">
-        <v>520</v>
+        <v>350</v>
       </c>
       <c r="F85">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="G85">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="H85">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I85">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="J85">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="K85">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L85">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N85">
-        <v>82.5</v>
+        <v>19.5</v>
       </c>
       <c r="O85">
-        <v>14.8</v>
+        <v>7.2</v>
       </c>
       <c r="R85" t="s">
-        <v>214</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D86">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E86">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="F86">
+        <v>420</v>
+      </c>
+      <c r="G86">
+        <v>280</v>
+      </c>
+      <c r="H86">
+        <v>280</v>
+      </c>
+      <c r="I86">
         <v>500</v>
       </c>
-      <c r="G86">
-        <v>340</v>
-      </c>
-      <c r="H86">
-        <v>340</v>
-      </c>
-      <c r="I86">
-        <v>600</v>
-      </c>
       <c r="J86">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="K86">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="L86">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="N86">
-        <v>97.5</v>
+        <v>49.5</v>
       </c>
       <c r="O86">
-        <v>16.100000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="R86" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B87" t="s">
-        <v>212</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>268</v>
+        <v>201</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="D87">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E87">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="F87">
-        <v>621</v>
+        <v>500</v>
       </c>
       <c r="G87">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="H87">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="I87">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="J87">
         <v>200</v>
       </c>
       <c r="K87">
-        <v>500</v>
-      </c>
-      <c r="L87">
-        <v>100</v>
-      </c>
-      <c r="M87">
-        <v>200</v>
+        <v>400</v>
+      </c>
+      <c r="L87" s="3">
+        <v>350</v>
       </c>
       <c r="N87">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="O87">
-        <v>16</v>
-      </c>
-      <c r="P87" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q87" s="3">
-        <v>704</v>
+        <v>16.2</v>
       </c>
       <c r="R87" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>268</v>
+        <v>201</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="D88" s="3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E88" s="3">
         <v>650</v>
       </c>
       <c r="F88" s="3">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="G88" s="3">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="H88" s="3">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="I88" s="3">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="J88" s="3">
         <v>200</v>
       </c>
       <c r="K88" s="3">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="L88" s="3">
-        <v>100</v>
-      </c>
-      <c r="M88" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N88" s="3">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="O88" s="3">
-        <v>18</v>
-      </c>
-      <c r="P88" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q88" s="3">
-        <v>704</v>
+        <v>20</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>268</v>
+        <v>201</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="D89" s="3">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="E89" s="3">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="F89" s="3">
-        <v>621</v>
+        <v>680</v>
       </c>
       <c r="G89" s="3">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="H89" s="3">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="I89" s="3">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="J89" s="3">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K89" s="3">
+        <v>550</v>
+      </c>
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
-        <v>100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>200</v>
-      </c>
       <c r="N89" s="3">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="O89" s="3">
-        <v>20</v>
-      </c>
-      <c r="P89" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>704</v>
+        <v>24.5</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>268</v>
+        <v>201</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="D90" s="3">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="E90" s="3">
-        <v>650</v>
+        <v>830</v>
       </c>
       <c r="F90" s="3">
-        <v>621</v>
+        <v>760</v>
       </c>
       <c r="G90" s="3">
-        <v>410</v>
+        <v>560</v>
       </c>
       <c r="H90" s="3">
-        <v>410</v>
+        <v>560</v>
       </c>
       <c r="I90" s="3">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="J90" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K90" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L90" s="3">
-        <v>100</v>
-      </c>
-      <c r="M90" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="N90" s="3">
-        <v>47</v>
+        <v>300</v>
       </c>
       <c r="O90" s="3">
-        <v>25</v>
-      </c>
-      <c r="P90" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q90" s="3">
-        <v>704</v>
+        <v>28.3</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
@@ -5675,50 +5640,41 @@
       <c r="B91" t="s">
         <v>212</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>269</v>
+      <c r="C91" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="D91">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E91">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="F91">
-        <v>621</v>
+        <v>480</v>
       </c>
       <c r="G91">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="H91">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="I91">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="J91" s="3">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="K91" s="3">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="L91">
-        <v>350</v>
-      </c>
-      <c r="M91">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N91">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="O91">
-        <v>18</v>
-      </c>
-      <c r="P91" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>704</v>
+        <v>14.8</v>
       </c>
       <c r="R91" t="s">
         <v>214</v>
@@ -5731,53 +5687,44 @@
       <c r="B92" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C92" s="5" t="s">
-        <v>269</v>
+      <c r="C92" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="D92" s="3">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E92" s="3">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="F92" s="3">
-        <v>621</v>
+        <v>500</v>
       </c>
       <c r="G92" s="3">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="H92" s="3">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="I92" s="3">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="J92" s="3">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="K92" s="3">
-        <v>700</v>
+        <v>380</v>
       </c>
       <c r="L92" s="3">
-        <v>350</v>
-      </c>
-      <c r="M92" s="3">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="N92" s="3">
-        <v>77</v>
+        <v>97.5</v>
       </c>
       <c r="O92" s="3">
-        <v>18</v>
-      </c>
-      <c r="P92" s="3">
-        <v>1174</v>
-      </c>
-      <c r="Q92" s="3">
-        <v>704</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
@@ -5788,7 +5735,7 @@
         <v>212</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D93">
         <v>85</v>
@@ -5809,22 +5756,22 @@
         <v>650</v>
       </c>
       <c r="J93" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K93" s="3">
-        <v>700</v>
-      </c>
-      <c r="L93">
-        <v>127</v>
+        <v>500</v>
+      </c>
+      <c r="L93" s="3">
+        <v>350</v>
       </c>
       <c r="M93">
         <v>200</v>
       </c>
       <c r="N93">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="O93">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P93" s="3">
         <v>1174</v>
@@ -5844,7 +5791,7 @@
         <v>212</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D94" s="3">
         <v>85</v>
@@ -5865,22 +5812,22 @@
         <v>650</v>
       </c>
       <c r="J94" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K94" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L94" s="3">
-        <v>127</v>
+        <v>350</v>
       </c>
       <c r="M94" s="3">
         <v>200</v>
       </c>
       <c r="N94" s="3">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="O94" s="3">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="P94" s="3">
         <v>1174</v>
@@ -5900,7 +5847,7 @@
         <v>212</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D95" s="3">
         <v>85</v>
@@ -5921,22 +5868,22 @@
         <v>650</v>
       </c>
       <c r="J95" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K95" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L95" s="3">
-        <v>127</v>
+        <v>350</v>
       </c>
       <c r="M95" s="3">
         <v>200</v>
       </c>
       <c r="N95" s="3">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="O95" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P95" s="3">
         <v>1174</v>
@@ -5955,44 +5902,53 @@
       <c r="B96" t="s">
         <v>212</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>287</v>
+      <c r="C96" s="4" t="s">
+        <v>268</v>
       </c>
       <c r="D96">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="E96">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F96">
-        <v>700</v>
+        <v>621</v>
       </c>
       <c r="G96">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="H96" s="3">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="I96">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="J96">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K96">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="L96">
-        <v>500</v>
+        <v>350</v>
+      </c>
+      <c r="M96">
+        <v>200</v>
       </c>
       <c r="N96">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="O96">
-        <v>22.8</v>
+        <v>25</v>
+      </c>
+      <c r="P96" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>704</v>
       </c>
       <c r="R96" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6003,43 +5959,52 @@
         <v>212</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="D97" s="3">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="E97" s="3">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F97" s="3">
+        <v>621</v>
+      </c>
+      <c r="G97" s="3">
+        <v>410</v>
+      </c>
+      <c r="H97" s="3">
+        <v>410</v>
+      </c>
+      <c r="I97" s="3">
+        <v>650</v>
+      </c>
+      <c r="J97" s="3">
+        <v>400</v>
+      </c>
+      <c r="K97" s="3">
         <v>700</v>
       </c>
-      <c r="G97" s="3">
-        <v>510</v>
-      </c>
-      <c r="H97" s="3">
-        <v>510</v>
-      </c>
-      <c r="I97" s="3">
-        <v>800</v>
-      </c>
-      <c r="J97" s="3">
-        <v>250</v>
-      </c>
-      <c r="K97" s="3">
-        <v>550</v>
-      </c>
       <c r="L97" s="3">
-        <v>500</v>
+        <v>350</v>
+      </c>
+      <c r="M97" s="3">
+        <v>200</v>
       </c>
       <c r="N97" s="3">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="O97" s="3">
-        <v>22.8</v>
+        <v>18</v>
+      </c>
+      <c r="P97" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>704</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
@@ -6050,43 +6015,52 @@
         <v>212</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="D98">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="E98">
-        <v>820</v>
+        <v>650</v>
       </c>
       <c r="F98">
-        <v>760</v>
+        <v>621</v>
       </c>
       <c r="G98">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="H98">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="I98">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="J98">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K98">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L98">
-        <v>600</v>
+        <v>350</v>
+      </c>
+      <c r="M98">
+        <v>200</v>
       </c>
       <c r="N98" s="3">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="O98">
-        <v>27.6</v>
+        <v>18</v>
+      </c>
+      <c r="P98" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>704</v>
       </c>
       <c r="R98" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6096,44 +6070,53 @@
       <c r="B99" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>290</v>
+      <c r="C99" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="D99" s="3">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="E99" s="3">
-        <v>820</v>
+        <v>650</v>
       </c>
       <c r="F99" s="3">
-        <v>760</v>
+        <v>621</v>
       </c>
       <c r="G99" s="3">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="H99" s="3">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="I99" s="3">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="J99" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K99" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L99" s="3">
-        <v>600</v>
+        <v>350</v>
+      </c>
+      <c r="M99" s="3">
+        <v>200</v>
       </c>
       <c r="N99" s="3">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="O99" s="3">
-        <v>27.6</v>
+        <v>33</v>
+      </c>
+      <c r="P99" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>704</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="100" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6143,44 +6126,53 @@
       <c r="B100" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>291</v>
+      <c r="C100" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="D100" s="3">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="E100" s="3">
-        <v>820</v>
+        <v>650</v>
       </c>
       <c r="F100" s="3">
-        <v>760</v>
+        <v>621</v>
       </c>
       <c r="G100" s="3">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="H100" s="3">
-        <v>560</v>
+        <v>410</v>
       </c>
       <c r="I100" s="3">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="J100" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K100" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L100" s="3">
-        <v>600</v>
+        <v>350</v>
+      </c>
+      <c r="M100" s="3">
+        <v>200</v>
       </c>
       <c r="N100" s="3">
-        <v>579</v>
+        <v>113</v>
       </c>
       <c r="O100" s="3">
-        <v>27.6</v>
+        <v>36</v>
+      </c>
+      <c r="P100" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>704</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
@@ -6190,44 +6182,53 @@
       <c r="B101" t="s">
         <v>212</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>292</v>
+      <c r="C101" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="D101">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="E101">
-        <v>900</v>
+        <v>650</v>
       </c>
       <c r="F101">
-        <v>830</v>
+        <v>621</v>
       </c>
       <c r="G101">
-        <v>670</v>
+        <v>410</v>
       </c>
       <c r="H101">
-        <v>620</v>
+        <v>410</v>
       </c>
       <c r="I101">
-        <v>1000</v>
+        <v>650</v>
       </c>
       <c r="J101">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K101">
         <v>700</v>
       </c>
       <c r="L101">
-        <v>700</v>
+        <v>350</v>
+      </c>
+      <c r="M101">
+        <v>200</v>
       </c>
       <c r="N101" s="3">
         <v>154</v>
       </c>
       <c r="O101">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1174</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>704</v>
       </c>
       <c r="R101" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
     </row>
     <row r="102" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6238,43 +6239,43 @@
         <v>212</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D102" s="3">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="E102" s="3">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F102" s="3">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="G102" s="3">
-        <v>670</v>
+        <v>510</v>
       </c>
       <c r="H102" s="3">
-        <v>620</v>
+        <v>510</v>
       </c>
       <c r="I102" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J102" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K102" s="3">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L102" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N102" s="3">
-        <v>301</v>
+        <v>154</v>
       </c>
       <c r="O102" s="3">
-        <v>31</v>
+        <v>22.8</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6285,43 +6286,43 @@
         <v>212</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D103" s="3">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="E103" s="3">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="F103" s="3">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="G103" s="3">
-        <v>670</v>
+        <v>510</v>
       </c>
       <c r="H103" s="3">
-        <v>620</v>
+        <v>510</v>
       </c>
       <c r="I103" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J103" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K103" s="3">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="L103" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N103" s="3">
-        <v>579</v>
+        <v>301</v>
       </c>
       <c r="O103" s="3">
-        <v>31</v>
+        <v>22.8</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -6332,43 +6333,43 @@
         <v>212</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D104">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="E104">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="F104">
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="G104">
-        <v>720</v>
+        <v>560</v>
       </c>
       <c r="H104">
-        <v>670</v>
+        <v>560</v>
       </c>
       <c r="I104">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J104">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K104">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L104">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="N104" s="3">
-        <v>301</v>
+        <v>154</v>
       </c>
       <c r="O104">
-        <v>35.200000000000003</v>
+        <v>27.6</v>
       </c>
       <c r="R104" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6379,43 +6380,43 @@
         <v>212</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D105" s="3">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="E105" s="3">
-        <v>950</v>
+        <v>820</v>
       </c>
       <c r="F105" s="3">
-        <v>880</v>
+        <v>760</v>
       </c>
       <c r="G105" s="3">
-        <v>720</v>
+        <v>560</v>
       </c>
       <c r="H105" s="3">
-        <v>670</v>
+        <v>560</v>
       </c>
       <c r="I105" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J105" s="3">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="K105" s="3">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L105" s="3">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="N105" s="3">
-        <v>579</v>
+        <v>301</v>
       </c>
       <c r="O105" s="3">
-        <v>35.200000000000003</v>
+        <v>27.6</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -6425,44 +6426,44 @@
       <c r="B106" t="s">
         <v>212</v>
       </c>
-      <c r="C106" t="s">
-        <v>217</v>
+      <c r="C106" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="D106">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="E106">
-        <v>1050</v>
+        <v>820</v>
       </c>
       <c r="F106">
-        <v>950</v>
+        <v>760</v>
       </c>
       <c r="G106">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="H106">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="I106">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J106">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K106">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="L106">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N106">
-        <v>525</v>
+        <v>579</v>
       </c>
       <c r="O106">
-        <v>37.4</v>
+        <v>27.6</v>
       </c>
       <c r="R106" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
@@ -6472,44 +6473,44 @@
       <c r="B107" t="s">
         <v>212</v>
       </c>
-      <c r="C107" t="s">
-        <v>218</v>
+      <c r="C107" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="D107">
-        <v>460</v>
+        <v>240</v>
       </c>
       <c r="E107">
-        <v>1150</v>
+        <v>900</v>
       </c>
       <c r="F107">
-        <v>1050</v>
+        <v>830</v>
       </c>
       <c r="G107">
-        <v>820</v>
+        <v>670</v>
       </c>
       <c r="H107">
-        <v>820</v>
+        <v>620</v>
       </c>
       <c r="I107">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J107">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K107">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L107">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N107">
-        <v>690</v>
+        <v>154</v>
       </c>
       <c r="O107">
-        <v>42.9</v>
+        <v>31</v>
       </c>
       <c r="R107" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
@@ -6519,44 +6520,44 @@
       <c r="B108" t="s">
         <v>212</v>
       </c>
-      <c r="C108" t="s">
-        <v>219</v>
+      <c r="C108" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="D108">
-        <v>550</v>
+        <v>240</v>
       </c>
       <c r="E108">
-        <v>1250</v>
+        <v>900</v>
       </c>
       <c r="F108">
-        <v>1150</v>
+        <v>830</v>
       </c>
       <c r="G108">
-        <v>920</v>
+        <v>670</v>
       </c>
       <c r="H108">
-        <v>920</v>
+        <v>620</v>
       </c>
       <c r="I108">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="J108">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="K108">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L108">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N108">
-        <v>825</v>
+        <v>301</v>
       </c>
       <c r="O108">
-        <v>46.9</v>
+        <v>31</v>
       </c>
       <c r="R108" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
@@ -6564,46 +6565,46 @@
         <v>211</v>
       </c>
       <c r="B109" t="s">
-        <v>220</v>
-      </c>
-      <c r="C109" t="s">
-        <v>221</v>
+        <v>212</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="D109">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="E109">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="F109">
+        <v>830</v>
+      </c>
+      <c r="G109">
+        <v>670</v>
+      </c>
+      <c r="H109">
+        <v>620</v>
+      </c>
+      <c r="I109">
+        <v>1000</v>
+      </c>
+      <c r="J109">
+        <v>300</v>
+      </c>
+      <c r="K109">
         <v>700</v>
       </c>
-      <c r="G109">
-        <v>500</v>
-      </c>
-      <c r="H109">
-        <v>500</v>
-      </c>
-      <c r="I109">
-        <v>800</v>
-      </c>
-      <c r="J109">
-        <v>250</v>
-      </c>
-      <c r="K109">
-        <v>550</v>
-      </c>
       <c r="L109">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N109">
-        <v>195</v>
+        <v>579</v>
       </c>
       <c r="O109">
-        <v>22.8</v>
+        <v>31</v>
       </c>
       <c r="R109" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
@@ -6611,46 +6612,46 @@
         <v>211</v>
       </c>
       <c r="B110" t="s">
-        <v>220</v>
-      </c>
-      <c r="C110" t="s">
-        <v>223</v>
+        <v>212</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>295</v>
       </c>
       <c r="D110">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="E110">
-        <v>820</v>
+        <v>950</v>
       </c>
       <c r="F110">
-        <v>760</v>
+        <v>880</v>
       </c>
       <c r="G110">
-        <v>560</v>
+        <v>720</v>
       </c>
       <c r="H110">
-        <v>560</v>
+        <v>670</v>
       </c>
       <c r="I110">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="J110">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K110">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="L110">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="N110">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="O110">
-        <v>27.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="R110" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
@@ -6658,46 +6659,46 @@
         <v>211</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
-      </c>
-      <c r="C111" t="s">
-        <v>225</v>
+        <v>212</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>296</v>
       </c>
       <c r="D111">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="E111">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="F111">
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="G111">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="H111">
-        <v>610</v>
+        <v>670</v>
       </c>
       <c r="I111">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J111">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K111">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="L111">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="N111">
-        <v>360</v>
+        <v>579</v>
       </c>
       <c r="O111">
-        <v>31</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="R111" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
@@ -6705,46 +6706,46 @@
         <v>211</v>
       </c>
       <c r="B112" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C112" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D112">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="E112">
+        <v>1050</v>
+      </c>
+      <c r="F112">
         <v>950</v>
       </c>
-      <c r="F112">
-        <v>880</v>
-      </c>
       <c r="G112">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="H112">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="I112">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J112">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K112">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="L112">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="N112">
-        <v>465</v>
+        <v>525</v>
       </c>
       <c r="O112">
-        <v>35.200000000000003</v>
+        <v>37.4</v>
       </c>
       <c r="R112" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
@@ -6752,46 +6753,46 @@
         <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C113" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D113">
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="E113">
+        <v>1150</v>
+      </c>
+      <c r="F113">
         <v>1050</v>
       </c>
-      <c r="F113">
-        <v>950</v>
-      </c>
       <c r="G113">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="H113">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="I113">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J113">
         <v>400</v>
       </c>
       <c r="K113">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L113">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N113">
-        <v>525</v>
+        <v>690</v>
       </c>
       <c r="O113">
-        <v>37.4</v>
+        <v>42.9</v>
       </c>
       <c r="R113" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
@@ -6799,46 +6800,46 @@
         <v>211</v>
       </c>
       <c r="B114" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C114" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D114">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="E114">
+        <v>1250</v>
+      </c>
+      <c r="F114">
         <v>1150</v>
       </c>
-      <c r="F114">
-        <v>1050</v>
-      </c>
       <c r="G114">
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="H114">
-        <v>820</v>
+        <v>920</v>
       </c>
       <c r="I114">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="J114">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K114">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L114">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="N114">
-        <v>690</v>
+        <v>825</v>
       </c>
       <c r="O114">
-        <v>42.9</v>
+        <v>46.9</v>
       </c>
       <c r="R114" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
@@ -6849,43 +6850,43 @@
         <v>220</v>
       </c>
       <c r="C115" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D115">
+        <v>130</v>
+      </c>
+      <c r="E115">
+        <v>750</v>
+      </c>
+      <c r="F115">
+        <v>700</v>
+      </c>
+      <c r="G115">
+        <v>500</v>
+      </c>
+      <c r="H115">
+        <v>500</v>
+      </c>
+      <c r="I115">
+        <v>800</v>
+      </c>
+      <c r="J115">
+        <v>250</v>
+      </c>
+      <c r="K115">
         <v>550</v>
       </c>
-      <c r="E115">
-        <v>1250</v>
-      </c>
-      <c r="F115">
-        <v>1150</v>
-      </c>
-      <c r="G115">
-        <v>920</v>
-      </c>
-      <c r="H115">
-        <v>920</v>
-      </c>
-      <c r="I115">
-        <v>1400</v>
-      </c>
-      <c r="J115">
-        <v>450</v>
-      </c>
-      <c r="K115">
-        <v>1000</v>
-      </c>
       <c r="L115">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N115">
-        <v>825</v>
+        <v>195</v>
       </c>
       <c r="O115">
-        <v>46.9</v>
+        <v>22.8</v>
       </c>
       <c r="R115" t="s">
-        <v>87</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
@@ -6893,46 +6894,46 @@
         <v>211</v>
       </c>
       <c r="B116" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D116">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="E116">
-        <v>880</v>
+        <v>820</v>
       </c>
       <c r="F116">
-        <v>810</v>
+        <v>760</v>
       </c>
       <c r="G116">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="H116">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="I116">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="J116">
         <v>300</v>
       </c>
       <c r="K116">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L116">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N116">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="O116">
-        <v>29.7</v>
+        <v>27.6</v>
       </c>
       <c r="R116" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
@@ -6940,46 +6941,46 @@
         <v>211</v>
       </c>
       <c r="B117" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D117">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="E117">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="F117">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="G117">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H117">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I117">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J117">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K117">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L117">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N117">
-        <v>525</v>
+        <v>360</v>
       </c>
       <c r="O117">
-        <v>37.4</v>
+        <v>31</v>
       </c>
       <c r="R117" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
@@ -6987,46 +6988,46 @@
         <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C118" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D118">
-        <v>450</v>
+        <v>310</v>
       </c>
       <c r="E118">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="F118">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="G118">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="H118">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="I118">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="J118">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="K118">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="L118">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="N118">
-        <v>675</v>
+        <v>465</v>
       </c>
       <c r="O118">
-        <v>42.4</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="R118" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -7034,46 +7035,46 @@
         <v>211</v>
       </c>
       <c r="B119" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C119" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D119">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E119">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F119">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G119">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H119">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I119">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J119">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K119">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L119">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N119">
-        <v>825</v>
+        <v>525</v>
       </c>
       <c r="O119">
-        <v>46.9</v>
+        <v>37.4</v>
       </c>
       <c r="R119" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
@@ -7081,46 +7082,46 @@
         <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C120" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D120">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="E120">
+        <v>1150</v>
+      </c>
+      <c r="F120">
+        <v>1050</v>
+      </c>
+      <c r="G120">
+        <v>820</v>
+      </c>
+      <c r="H120">
+        <v>820</v>
+      </c>
+      <c r="I120">
+        <v>1300</v>
+      </c>
+      <c r="J120">
+        <v>400</v>
+      </c>
+      <c r="K120">
         <v>900</v>
       </c>
-      <c r="F120">
-        <v>830</v>
-      </c>
-      <c r="G120">
-        <v>610</v>
-      </c>
-      <c r="H120">
-        <v>610</v>
-      </c>
-      <c r="I120">
-        <v>1000</v>
-      </c>
-      <c r="J120">
-        <v>300</v>
-      </c>
-      <c r="K120">
-        <v>700</v>
-      </c>
       <c r="L120">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="N120">
-        <v>360</v>
+        <v>690</v>
       </c>
       <c r="O120">
-        <v>31</v>
+        <v>42.9</v>
       </c>
       <c r="R120" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
@@ -7128,46 +7129,46 @@
         <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C121" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D121">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="E121">
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="F121">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="G121">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="H121">
-        <v>710</v>
+        <v>920</v>
       </c>
       <c r="I121">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J121">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K121">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="L121">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="N121">
-        <v>525</v>
+        <v>825</v>
       </c>
       <c r="O121">
-        <v>37.4</v>
+        <v>46.9</v>
       </c>
       <c r="R121" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -7175,328 +7176,328 @@
         <v>211</v>
       </c>
       <c r="B122" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C122" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D122">
-        <v>460</v>
+        <v>220</v>
       </c>
       <c r="E122">
-        <v>1150</v>
+        <v>880</v>
       </c>
       <c r="F122">
-        <v>1050</v>
+        <v>810</v>
       </c>
       <c r="G122">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="H122">
-        <v>820</v>
+        <v>610</v>
       </c>
       <c r="I122">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J122">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K122">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L122">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="N122">
-        <v>690</v>
+        <v>330</v>
       </c>
       <c r="O122">
-        <v>42.9</v>
+        <v>29.7</v>
       </c>
       <c r="R122" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B123" t="s">
-        <v>98</v>
+        <v>233</v>
       </c>
       <c r="C123" t="s">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="D123">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="E123">
-        <v>560</v>
+        <v>1050</v>
       </c>
       <c r="F123">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="G123">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="H123">
-        <v>360</v>
+        <v>710</v>
       </c>
       <c r="I123">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="J123">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K123">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="L123">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="N123">
-        <v>82.5</v>
+        <v>525</v>
       </c>
       <c r="O123">
-        <v>14.8</v>
+        <v>37.4</v>
       </c>
       <c r="R123" t="s">
-        <v>100</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B124" t="s">
-        <v>98</v>
+        <v>233</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="D124">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="E124">
-        <v>630</v>
+        <v>1150</v>
       </c>
       <c r="F124">
-        <v>580</v>
+        <v>1050</v>
       </c>
       <c r="G124">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="H124">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="I124">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="J124">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K124">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="L124">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="N124">
-        <v>112.5</v>
+        <v>675</v>
       </c>
       <c r="O124">
-        <v>17.3</v>
+        <v>42.4</v>
       </c>
       <c r="R124" t="s">
-        <v>102</v>
+        <v>239</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B125" t="s">
-        <v>98</v>
+        <v>233</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="D125">
-        <v>143</v>
+        <v>550</v>
       </c>
       <c r="E125">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="F125">
-        <v>680</v>
+        <v>1150</v>
       </c>
       <c r="G125">
-        <v>510</v>
+        <v>920</v>
       </c>
       <c r="H125">
-        <v>510</v>
+        <v>920</v>
       </c>
       <c r="I125">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="J125">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="K125">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="L125">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N125">
-        <v>214.5</v>
+        <v>825</v>
       </c>
       <c r="O125">
-        <v>23.9</v>
+        <v>46.9</v>
       </c>
       <c r="R125" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B126" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="C126" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="D126">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="E126">
+        <v>900</v>
+      </c>
+      <c r="F126">
         <v>830</v>
       </c>
-      <c r="F126">
-        <v>760</v>
-      </c>
       <c r="G126">
-        <v>560</v>
+        <v>610</v>
       </c>
       <c r="H126">
-        <v>560</v>
+        <v>610</v>
       </c>
       <c r="I126">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J126">
         <v>300</v>
       </c>
       <c r="K126">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L126">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N126">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="O126">
-        <v>28.1</v>
+        <v>31</v>
       </c>
       <c r="R126" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B127" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="D127">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="E127">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="F127">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="G127">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="H127">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="I127">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="J127">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K127">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L127">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N127">
-        <v>462</v>
+        <v>525</v>
       </c>
       <c r="O127">
-        <v>35.1</v>
+        <v>37.4</v>
       </c>
       <c r="R127" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="B128" t="s">
-        <v>98</v>
+        <v>242</v>
       </c>
       <c r="C128" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="D128">
-        <v>385</v>
+        <v>460</v>
       </c>
       <c r="E128">
-        <v>1020</v>
+        <v>1150</v>
       </c>
       <c r="F128">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="G128">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="H128">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="I128">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J128">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="K128">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L128">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N128">
-        <v>577.5</v>
+        <v>690</v>
       </c>
       <c r="O128">
-        <v>39.200000000000003</v>
+        <v>42.9</v>
       </c>
       <c r="R128" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
@@ -7507,43 +7508,43 @@
         <v>98</v>
       </c>
       <c r="C129" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D129">
-        <v>495</v>
+        <v>55</v>
       </c>
       <c r="E129">
-        <v>1150</v>
+        <v>560</v>
       </c>
       <c r="F129">
-        <v>1050</v>
+        <v>510</v>
       </c>
       <c r="G129">
-        <v>820</v>
+        <v>360</v>
       </c>
       <c r="H129">
-        <v>820</v>
+        <v>360</v>
       </c>
       <c r="I129">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="J129">
+        <v>200</v>
+      </c>
+      <c r="K129">
         <v>400</v>
       </c>
-      <c r="K129">
-        <v>900</v>
-      </c>
       <c r="L129">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="N129">
-        <v>742.5</v>
+        <v>82.5</v>
       </c>
       <c r="O129">
-        <v>44.5</v>
+        <v>14.8</v>
       </c>
       <c r="R129" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
@@ -7554,43 +7555,43 @@
         <v>98</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D130">
-        <v>550</v>
+        <v>75</v>
       </c>
       <c r="E130">
-        <v>1250</v>
+        <v>630</v>
       </c>
       <c r="F130">
-        <v>1150</v>
+        <v>580</v>
       </c>
       <c r="G130">
-        <v>920</v>
+        <v>410</v>
       </c>
       <c r="H130">
-        <v>920</v>
+        <v>410</v>
       </c>
       <c r="I130">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="J130">
+        <v>200</v>
+      </c>
+      <c r="K130">
         <v>450</v>
       </c>
-      <c r="K130">
-        <v>1000</v>
-      </c>
       <c r="L130">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="N130">
-        <v>825</v>
+        <v>112.5</v>
       </c>
       <c r="O130">
-        <v>46.9</v>
+        <v>17.3</v>
       </c>
       <c r="R130" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
@@ -7598,10 +7599,10 @@
         <v>97</v>
       </c>
       <c r="B131" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C131" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D131">
         <v>143</v>
@@ -7637,7 +7638,7 @@
         <v>23.9</v>
       </c>
       <c r="R131" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
@@ -7645,10 +7646,10 @@
         <v>97</v>
       </c>
       <c r="B132" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D132">
         <v>198</v>
@@ -7684,7 +7685,7 @@
         <v>28.1</v>
       </c>
       <c r="R132" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
@@ -7692,19 +7693,19 @@
         <v>97</v>
       </c>
       <c r="B133" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C133" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D133">
-        <v>242</v>
+        <v>308</v>
       </c>
       <c r="E133">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="F133">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="G133">
         <v>610</v>
@@ -7725,13 +7726,13 @@
         <v>700</v>
       </c>
       <c r="N133">
-        <v>363</v>
+        <v>462</v>
       </c>
       <c r="O133">
-        <v>31.1</v>
+        <v>35.1</v>
       </c>
       <c r="R133" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
@@ -7739,46 +7740,46 @@
         <v>97</v>
       </c>
       <c r="B134" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D134">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="E134">
+        <v>1020</v>
+      </c>
+      <c r="F134">
         <v>950</v>
       </c>
-      <c r="F134">
-        <v>850</v>
-      </c>
       <c r="G134">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="H134">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="I134">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J134">
         <v>350</v>
       </c>
       <c r="K134">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="L134">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="N134">
-        <v>462</v>
+        <v>577.5</v>
       </c>
       <c r="O134">
-        <v>35.1</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="R134" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
@@ -7786,46 +7787,46 @@
         <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D135">
-        <v>385</v>
+        <v>495</v>
       </c>
       <c r="E135">
+        <v>1150</v>
+      </c>
+      <c r="F135">
         <v>1050</v>
       </c>
-      <c r="F135">
-        <v>950</v>
-      </c>
       <c r="G135">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="H135">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="I135">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="J135">
         <v>400</v>
       </c>
       <c r="K135">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="L135">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N135">
-        <v>577.5</v>
+        <v>742.5</v>
       </c>
       <c r="O135">
-        <v>39.200000000000003</v>
+        <v>44.5</v>
       </c>
       <c r="R135" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
@@ -7833,46 +7834,46 @@
         <v>97</v>
       </c>
       <c r="B136" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D136">
-        <v>33</v>
+        <v>550</v>
       </c>
       <c r="E136">
+        <v>1250</v>
+      </c>
+      <c r="F136">
+        <v>1150</v>
+      </c>
+      <c r="G136">
+        <v>920</v>
+      </c>
+      <c r="H136">
+        <v>920</v>
+      </c>
+      <c r="I136">
+        <v>1400</v>
+      </c>
+      <c r="J136">
         <v>450</v>
       </c>
-      <c r="F136">
-        <v>420</v>
-      </c>
-      <c r="G136">
-        <v>300</v>
-      </c>
-      <c r="H136">
-        <v>300</v>
-      </c>
-      <c r="I136">
-        <v>500</v>
-      </c>
-      <c r="J136">
-        <v>150</v>
-      </c>
       <c r="K136">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="L136">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="N136">
-        <v>49.5</v>
+        <v>825</v>
       </c>
       <c r="O136">
-        <v>11.5</v>
+        <v>46.9</v>
       </c>
       <c r="R136" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
@@ -7880,46 +7881,46 @@
         <v>97</v>
       </c>
       <c r="B137" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C137" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D137">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="E137">
-        <v>560</v>
+        <v>750</v>
       </c>
       <c r="F137">
+        <v>680</v>
+      </c>
+      <c r="G137">
         <v>510</v>
       </c>
-      <c r="G137">
-        <v>360</v>
-      </c>
       <c r="H137">
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="I137">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="J137">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K137">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="L137">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="N137">
-        <v>82.5</v>
+        <v>214.5</v>
       </c>
       <c r="O137">
-        <v>14.8</v>
+        <v>23.9</v>
       </c>
       <c r="R137" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
@@ -7927,46 +7928,46 @@
         <v>97</v>
       </c>
       <c r="B138" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D138">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="E138">
-        <v>630</v>
+        <v>830</v>
       </c>
       <c r="F138">
-        <v>580</v>
+        <v>760</v>
       </c>
       <c r="G138">
-        <v>410</v>
+        <v>560</v>
       </c>
       <c r="H138">
-        <v>410</v>
+        <v>560</v>
       </c>
       <c r="I138">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="J138">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K138">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="L138">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N138">
-        <v>112.5</v>
+        <v>297</v>
       </c>
       <c r="O138">
-        <v>17.3</v>
+        <v>28.1</v>
       </c>
       <c r="R138" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
@@ -7974,46 +7975,46 @@
         <v>97</v>
       </c>
       <c r="B139" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C139" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D139">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="E139">
-        <v>750</v>
+        <v>880</v>
       </c>
       <c r="F139">
-        <v>680</v>
+        <v>810</v>
       </c>
       <c r="G139">
-        <v>510</v>
+        <v>610</v>
       </c>
       <c r="H139">
-        <v>510</v>
+        <v>610</v>
       </c>
       <c r="I139">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J139">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="K139">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="L139">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N139">
-        <v>214.5</v>
+        <v>363</v>
       </c>
       <c r="O139">
-        <v>23.9</v>
+        <v>31.1</v>
       </c>
       <c r="R139" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
@@ -8021,46 +8022,46 @@
         <v>97</v>
       </c>
       <c r="B140" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C140" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D140">
-        <v>198</v>
+        <v>308</v>
       </c>
       <c r="E140">
-        <v>830</v>
+        <v>950</v>
       </c>
       <c r="F140">
-        <v>760</v>
+        <v>850</v>
       </c>
       <c r="G140">
-        <v>560</v>
+        <v>660</v>
       </c>
       <c r="H140">
-        <v>560</v>
+        <v>660</v>
       </c>
       <c r="I140">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="J140">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K140">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="L140">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="N140">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="O140">
-        <v>28.1</v>
+        <v>35.1</v>
       </c>
       <c r="R140" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.25">
@@ -8068,46 +8069,46 @@
         <v>97</v>
       </c>
       <c r="B141" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C141" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D141">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="E141">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="F141">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="G141">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="H141">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="I141">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="J141">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K141">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="L141">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N141">
-        <v>462</v>
+        <v>577.5</v>
       </c>
       <c r="O141">
-        <v>35.1</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="R141" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -8118,43 +8119,43 @@
         <v>124</v>
       </c>
       <c r="C142" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D142">
-        <v>385</v>
+        <v>33</v>
       </c>
       <c r="E142">
-        <v>1020</v>
+        <v>450</v>
       </c>
       <c r="F142">
-        <v>950</v>
+        <v>420</v>
       </c>
       <c r="G142">
-        <v>710</v>
+        <v>300</v>
       </c>
       <c r="H142">
-        <v>710</v>
+        <v>300</v>
       </c>
       <c r="I142">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="J142">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="K142">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="L142">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="N142">
-        <v>577.5</v>
+        <v>49.5</v>
       </c>
       <c r="O142">
-        <v>39.200000000000003</v>
+        <v>11.5</v>
       </c>
       <c r="R142" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
@@ -8162,46 +8163,46 @@
         <v>97</v>
       </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C143" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D143">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="E143">
-        <v>880</v>
+        <v>560</v>
       </c>
       <c r="F143">
-        <v>810</v>
+        <v>510</v>
       </c>
       <c r="G143">
-        <v>610</v>
+        <v>360</v>
       </c>
       <c r="H143">
-        <v>610</v>
+        <v>360</v>
       </c>
       <c r="I143">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="J143">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K143">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="L143">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="N143">
-        <v>330</v>
+        <v>82.5</v>
       </c>
       <c r="O143">
-        <v>29.7</v>
+        <v>14.8</v>
       </c>
       <c r="R143" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
@@ -8209,46 +8210,46 @@
         <v>97</v>
       </c>
       <c r="B144" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C144" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D144">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="E144">
-        <v>1050</v>
+        <v>630</v>
       </c>
       <c r="F144">
-        <v>950</v>
+        <v>580</v>
       </c>
       <c r="G144">
-        <v>710</v>
+        <v>410</v>
       </c>
       <c r="H144">
-        <v>710</v>
+        <v>410</v>
       </c>
       <c r="I144">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="J144">
+        <v>200</v>
+      </c>
+      <c r="K144">
+        <v>450</v>
+      </c>
+      <c r="L144">
         <v>400</v>
       </c>
-      <c r="K144">
-        <v>800</v>
-      </c>
-      <c r="L144">
-        <v>800</v>
-      </c>
       <c r="N144">
-        <v>525</v>
+        <v>112.5</v>
       </c>
       <c r="O144">
-        <v>37.4</v>
+        <v>17.3</v>
       </c>
       <c r="R144" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
@@ -8256,46 +8257,46 @@
         <v>97</v>
       </c>
       <c r="B145" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C145" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D145">
-        <v>450</v>
+        <v>143</v>
       </c>
       <c r="E145">
-        <v>1150</v>
+        <v>750</v>
       </c>
       <c r="F145">
-        <v>1050</v>
+        <v>680</v>
       </c>
       <c r="G145">
-        <v>820</v>
+        <v>510</v>
       </c>
       <c r="H145">
-        <v>820</v>
+        <v>510</v>
       </c>
       <c r="I145">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="J145">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="K145">
-        <v>900</v>
+        <v>550</v>
       </c>
       <c r="L145">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="N145">
-        <v>675</v>
+        <v>214.5</v>
       </c>
       <c r="O145">
-        <v>42.4</v>
+        <v>23.9</v>
       </c>
       <c r="R145" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.25">
@@ -8303,46 +8304,46 @@
         <v>97</v>
       </c>
       <c r="B146" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C146" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D146">
-        <v>500</v>
+        <v>198</v>
       </c>
       <c r="E146">
-        <v>1250</v>
+        <v>830</v>
       </c>
       <c r="F146">
-        <v>1150</v>
+        <v>760</v>
       </c>
       <c r="G146">
-        <v>920</v>
+        <v>560</v>
       </c>
       <c r="H146">
-        <v>920</v>
+        <v>560</v>
       </c>
       <c r="I146">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="J146">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="K146">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="L146">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="N146">
-        <v>750</v>
+        <v>297</v>
       </c>
       <c r="O146">
-        <v>44.7</v>
+        <v>28.1</v>
       </c>
       <c r="R146" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.25">
@@ -8350,19 +8351,19 @@
         <v>97</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C147" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D147">
-        <v>231</v>
+        <v>308</v>
       </c>
       <c r="E147">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="F147">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="G147">
         <v>610</v>
@@ -8383,13 +8384,13 @@
         <v>700</v>
       </c>
       <c r="N147">
-        <v>346.5</v>
+        <v>462</v>
       </c>
       <c r="O147">
-        <v>30.4</v>
+        <v>35.1</v>
       </c>
       <c r="R147" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.25">
@@ -8397,46 +8398,46 @@
         <v>97</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C148" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D148">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="E148">
+        <v>1020</v>
+      </c>
+      <c r="F148">
         <v>950</v>
       </c>
-      <c r="F148">
-        <v>850</v>
-      </c>
       <c r="G148">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="H148">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="I148">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J148">
         <v>350</v>
       </c>
       <c r="K148">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="L148">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="N148">
-        <v>462</v>
+        <v>577.5</v>
       </c>
       <c r="O148">
-        <v>35.1</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="R148" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.25">
@@ -8444,46 +8445,46 @@
         <v>97</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C149" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D149">
-        <v>385</v>
+        <v>220</v>
       </c>
       <c r="E149">
-        <v>1050</v>
+        <v>880</v>
       </c>
       <c r="F149">
-        <v>950</v>
+        <v>810</v>
       </c>
       <c r="G149">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="H149">
-        <v>710</v>
+        <v>610</v>
       </c>
       <c r="I149">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="J149">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K149">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L149">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N149">
-        <v>577.5</v>
+        <v>330</v>
       </c>
       <c r="O149">
-        <v>39.200000000000003</v>
+        <v>29.7</v>
       </c>
       <c r="R149" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
@@ -8491,316 +8492,421 @@
         <v>97</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C150" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D150">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E150">
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="F150">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="G150">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="H150">
-        <v>920</v>
+        <v>710</v>
       </c>
       <c r="I150">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="J150">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K150">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="L150">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N150">
-        <v>825</v>
+        <v>525</v>
       </c>
       <c r="O150">
-        <v>46.9</v>
+        <v>37.4</v>
       </c>
       <c r="R150" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="D151" s="2">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="E151" s="2">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F151" s="2">
-        <v>600</v>
+        <v>1050</v>
       </c>
       <c r="G151" s="2">
-        <v>460</v>
+        <v>820</v>
       </c>
       <c r="H151" s="2">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="I151" s="2">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="J151" s="2">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="K151" s="2">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="L151" s="2">
-        <v>350</v>
-      </c>
-      <c r="M151" s="2">
-        <v>150</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="M151" s="2"/>
       <c r="N151" s="2">
-        <v>202</v>
+        <v>675</v>
       </c>
       <c r="O151" s="2">
-        <v>40</v>
+        <v>42.4</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>273</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="D152" s="2">
-        <v>130</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="E152" s="2">
+        <v>1250</v>
+      </c>
+      <c r="F152" s="2">
+        <v>1150</v>
+      </c>
       <c r="G152" s="2">
-        <v>530</v>
+        <v>920</v>
       </c>
       <c r="H152" s="2">
-        <v>530</v>
-      </c>
-      <c r="I152" s="2"/>
+        <v>920</v>
+      </c>
+      <c r="I152" s="2">
+        <v>1400</v>
+      </c>
       <c r="J152" s="2">
-        <v>150</v>
-      </c>
-      <c r="K152" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="K152" s="2">
+        <v>1000</v>
+      </c>
       <c r="L152" s="2">
-        <v>400</v>
-      </c>
-      <c r="M152" s="2">
-        <v>150</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="M152" s="2"/>
       <c r="N152" s="2">
-        <v>250</v>
-      </c>
-      <c r="O152" s="2" t="s">
-        <v>275</v>
+        <v>750</v>
+      </c>
+      <c r="O152" s="2">
+        <v>44.7</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>276</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>277</v>
+        <v>147</v>
       </c>
       <c r="D153" s="2">
-        <v>180</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="E153" s="2">
+        <v>880</v>
+      </c>
+      <c r="F153" s="2">
+        <v>810</v>
+      </c>
       <c r="G153" s="2">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="H153" s="2">
-        <v>570</v>
-      </c>
-      <c r="I153" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="I153" s="2">
+        <v>1000</v>
+      </c>
       <c r="J153" s="2">
-        <v>150</v>
-      </c>
-      <c r="K153" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="K153" s="2">
+        <v>700</v>
+      </c>
       <c r="L153" s="2">
-        <v>450</v>
-      </c>
-      <c r="M153" s="2">
-        <v>150</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="M153" s="2"/>
       <c r="N153" s="2">
-        <v>300</v>
-      </c>
-      <c r="O153" s="2" t="s">
-        <v>278</v>
+        <v>346.5</v>
+      </c>
+      <c r="O153" s="2">
+        <v>30.4</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>279</v>
+        <v>148</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>280</v>
+        <v>149</v>
       </c>
       <c r="D154" s="2">
-        <v>220</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="E154" s="2">
+        <v>950</v>
+      </c>
+      <c r="F154" s="2">
+        <v>850</v>
+      </c>
       <c r="G154" s="2">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="H154" s="2">
-        <v>650</v>
-      </c>
-      <c r="I154" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="I154" s="2">
+        <v>1100</v>
+      </c>
       <c r="J154" s="2">
+        <v>350</v>
+      </c>
+      <c r="K154" s="2">
+        <v>750</v>
+      </c>
+      <c r="L154" s="2">
+        <v>750</v>
+      </c>
+      <c r="M154" s="2"/>
+      <c r="N154" s="2">
+        <v>462</v>
+      </c>
+      <c r="O154" s="2">
+        <v>35.1</v>
+      </c>
+      <c r="R154" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="K154" s="2"/>
-      <c r="L154" s="2">
-        <v>500</v>
-      </c>
-      <c r="M154" s="2">
-        <v>150</v>
-      </c>
-      <c r="N154" s="2">
-        <v>350</v>
-      </c>
-      <c r="O154" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="R154" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>283</v>
+        <v>151</v>
       </c>
       <c r="D155" s="2">
-        <v>500</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="E155" s="2">
+        <v>1050</v>
+      </c>
+      <c r="F155" s="2">
+        <v>950</v>
+      </c>
       <c r="G155" s="2">
-        <v>830</v>
+        <v>710</v>
       </c>
       <c r="H155" s="2">
-        <v>830</v>
-      </c>
-      <c r="I155" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="I155" s="2">
+        <v>1200</v>
+      </c>
       <c r="J155" s="2">
-        <v>150</v>
-      </c>
-      <c r="K155" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="K155" s="2">
+        <v>800</v>
+      </c>
       <c r="L155" s="2">
-        <v>700</v>
-      </c>
-      <c r="M155" s="2">
-        <v>150</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="M155" s="2"/>
       <c r="N155" s="2">
-        <v>600</v>
-      </c>
-      <c r="O155" s="2" t="s">
-        <v>284</v>
+        <v>577.5</v>
+      </c>
+      <c r="O155" s="2">
+        <v>39.200000000000003</v>
       </c>
       <c r="R155" s="2" t="s">
-        <v>285</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>286</v>
+        <v>152</v>
       </c>
       <c r="D156" s="3">
-        <v>85</v>
-      </c>
-      <c r="E156" s="3"/>
-      <c r="F156" s="3"/>
+        <v>550</v>
+      </c>
+      <c r="E156" s="3">
+        <v>1250</v>
+      </c>
+      <c r="F156" s="3">
+        <v>1150</v>
+      </c>
       <c r="G156" s="3">
-        <v>470</v>
+        <v>920</v>
       </c>
       <c r="H156" s="3">
-        <v>420</v>
-      </c>
-      <c r="I156" s="3"/>
+        <v>920</v>
+      </c>
+      <c r="I156" s="3">
+        <v>1400</v>
+      </c>
       <c r="J156" s="3">
-        <v>150</v>
-      </c>
-      <c r="K156" s="3"/>
+        <v>450</v>
+      </c>
+      <c r="K156" s="3">
+        <v>1000</v>
+      </c>
       <c r="L156" s="3">
-        <v>320</v>
-      </c>
-      <c r="M156" s="3">
-        <v>150</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="M156" s="3"/>
       <c r="N156" s="3">
-        <v>23</v>
+        <v>825</v>
       </c>
       <c r="O156" s="3">
-        <v>20</v>
-      </c>
-      <c r="R156" s="3"/>
+        <v>46.9</v>
+      </c>
+      <c r="R156" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G159" s="3"/>
       <c r="H159" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O150">
-    <sortCondition ref="A2:A150"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R159">
+    <sortCondition ref="A2:A159"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6CEE4A-7CCF-4455-857B-32193F671A1E}">
+  <dimension ref="B1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4705E771-A28A-46B2-8B5D-7C05A62E1415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFDDFD3-691F-40E0-B2BA-753C613C1ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="359">
   <si>
     <t>OEM</t>
   </si>
@@ -1093,6 +1093,24 @@
   </si>
   <si>
     <t>320 C-170</t>
+  </si>
+  <si>
+    <t>SHIBAURA</t>
+  </si>
+  <si>
+    <t>ECSXIII</t>
+  </si>
+  <si>
+    <t>EC30SXII</t>
+  </si>
+  <si>
+    <t>EC250SXIII-U48-8Y</t>
+  </si>
+  <si>
+    <t>EC200SXIII-U48-8Y</t>
+  </si>
+  <si>
+    <t>all-electric</t>
   </si>
 </sst>
 </file>
@@ -9290,9 +9308,86 @@
         <v>153</v>
       </c>
     </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>353</v>
+      </c>
+      <c r="B163" t="s">
+        <v>354</v>
+      </c>
+      <c r="C163" t="s">
+        <v>355</v>
+      </c>
+      <c r="D163">
+        <v>33</v>
+      </c>
+      <c r="T163" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D164">
+        <v>198</v>
+      </c>
+      <c r="F164">
+        <v>790</v>
+      </c>
+      <c r="G164">
+        <v>740</v>
+      </c>
+      <c r="H164">
+        <v>560</v>
+      </c>
+      <c r="I164">
+        <v>510</v>
+      </c>
+      <c r="J164">
+        <v>1050</v>
+      </c>
+      <c r="K164">
+        <v>200</v>
+      </c>
+      <c r="L164">
+        <v>600</v>
+      </c>
+      <c r="M164">
+        <v>450</v>
+      </c>
+      <c r="O164">
+        <v>292</v>
+      </c>
+      <c r="P164">
+        <v>45</v>
+      </c>
+      <c r="S164" s="2">
+        <v>130</v>
+      </c>
+      <c r="T164" t="s">
+        <v>358</v>
+      </c>
+    </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H165" s="2"/>
-      <c r="I165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C165" t="s">
+        <v>356</v>
+      </c>
+      <c r="T165" s="2" t="s">
+        <v>358</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T165">

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFDDFD3-691F-40E0-B2BA-753C613C1ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5284095C-0E1E-4EF6-8979-969B6065ACF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="362">
   <si>
     <t>OEM</t>
   </si>
@@ -1111,6 +1111,15 @@
   </si>
   <si>
     <t>all-electric</t>
+  </si>
+  <si>
+    <t>YIZUMI's</t>
+  </si>
+  <si>
+    <t>FF300 </t>
+  </si>
+  <si>
+    <t>FF300-IU670</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T165"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1615,6 +1624,10 @@
       <c r="D2">
         <v>60</v>
       </c>
+      <c r="E2" s="2">
+        <f>D2*10</f>
+        <v>600</v>
+      </c>
       <c r="F2">
         <v>450</v>
       </c>
@@ -1666,6 +1679,10 @@
       <c r="D3">
         <v>100</v>
       </c>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E66" si="0">D3*10</f>
+        <v>1000</v>
+      </c>
       <c r="F3">
         <v>500</v>
       </c>
@@ -1714,6 +1731,7 @@
         <v>50</v>
       </c>
       <c r="E4" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F4" s="2">
@@ -1767,6 +1785,7 @@
         <v>50</v>
       </c>
       <c r="E5" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F5" s="2">
@@ -1820,6 +1839,7 @@
         <v>50</v>
       </c>
       <c r="E6" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F6" s="2">
@@ -1873,6 +1893,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F7" s="2">
@@ -1926,6 +1947,7 @@
         <v>50</v>
       </c>
       <c r="E8" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F8" s="2">
@@ -1979,6 +2001,7 @@
         <v>50</v>
       </c>
       <c r="E9" s="2">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="F9" s="2">
@@ -2031,6 +2054,10 @@
       <c r="D10">
         <v>60</v>
       </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
       <c r="F10">
         <v>570</v>
       </c>
@@ -2078,6 +2105,10 @@
       <c r="D11">
         <v>150</v>
       </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
       <c r="F11">
         <v>570</v>
       </c>
@@ -2125,6 +2156,10 @@
       <c r="D12">
         <v>290</v>
       </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
       <c r="F12">
         <v>770</v>
       </c>
@@ -2172,6 +2207,10 @@
       <c r="D13">
         <v>150</v>
       </c>
+      <c r="E13" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
       <c r="F13">
         <v>770</v>
       </c>
@@ -2219,6 +2258,10 @@
       <c r="D14">
         <v>350</v>
       </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
       <c r="F14">
         <v>850</v>
       </c>
@@ -2266,6 +2309,10 @@
       <c r="D15">
         <v>400</v>
       </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
       <c r="F15">
         <v>900</v>
       </c>
@@ -2313,6 +2360,10 @@
       <c r="D16">
         <v>800</v>
       </c>
+      <c r="E16" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F16">
         <v>1000</v>
       </c>
@@ -2360,6 +2411,10 @@
       <c r="D17">
         <v>800</v>
       </c>
+      <c r="E17" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F17">
         <v>1100</v>
       </c>
@@ -2407,6 +2462,10 @@
       <c r="D18">
         <v>1300</v>
       </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
       <c r="F18">
         <v>1300</v>
       </c>
@@ -2454,6 +2513,10 @@
       <c r="D19">
         <v>2100</v>
       </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>21000</v>
+      </c>
       <c r="F19">
         <v>1500</v>
       </c>
@@ -2501,6 +2564,10 @@
       <c r="D20">
         <v>100</v>
       </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
       <c r="F20">
         <v>500</v>
       </c>
@@ -2548,6 +2615,10 @@
       <c r="D21">
         <v>150</v>
       </c>
+      <c r="E21" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
       <c r="F21">
         <v>570</v>
       </c>
@@ -2595,6 +2666,10 @@
       <c r="D22">
         <v>290</v>
       </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>2900</v>
+      </c>
       <c r="F22">
         <v>770</v>
       </c>
@@ -2642,6 +2717,10 @@
       <c r="D23">
         <v>150</v>
       </c>
+      <c r="E23" s="2">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
       <c r="F23">
         <v>770</v>
       </c>
@@ -2689,6 +2768,10 @@
       <c r="D24">
         <v>350</v>
       </c>
+      <c r="E24" s="2">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
       <c r="F24">
         <v>850</v>
       </c>
@@ -2736,6 +2819,10 @@
       <c r="D25">
         <v>400</v>
       </c>
+      <c r="E25" s="2">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
       <c r="F25">
         <v>900</v>
       </c>
@@ -2783,6 +2870,10 @@
       <c r="D26">
         <v>800</v>
       </c>
+      <c r="E26" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F26">
         <v>1000</v>
       </c>
@@ -2830,6 +2921,10 @@
       <c r="D27">
         <v>800</v>
       </c>
+      <c r="E27" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F27">
         <v>1100</v>
       </c>
@@ -2877,6 +2972,10 @@
       <c r="D28">
         <v>1300</v>
       </c>
+      <c r="E28" s="2">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
       <c r="F28">
         <v>1300</v>
       </c>
@@ -2924,6 +3023,10 @@
       <c r="D29">
         <v>290</v>
       </c>
+      <c r="E29" s="2">
+        <f>D29*10</f>
+        <v>2900</v>
+      </c>
       <c r="F29">
         <v>770</v>
       </c>
@@ -2971,6 +3074,10 @@
       <c r="D30">
         <v>350</v>
       </c>
+      <c r="E30" s="2">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
       <c r="F30">
         <v>850</v>
       </c>
@@ -3018,6 +3125,10 @@
       <c r="D31">
         <v>400</v>
       </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
       <c r="F31">
         <v>900</v>
       </c>
@@ -3065,6 +3176,10 @@
       <c r="D32">
         <v>800</v>
       </c>
+      <c r="E32" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F32">
         <v>1000</v>
       </c>
@@ -3112,6 +3227,10 @@
       <c r="D33">
         <v>800</v>
       </c>
+      <c r="E33" s="2">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
       <c r="F33">
         <v>1100</v>
       </c>
@@ -3159,6 +3278,10 @@
       <c r="D34">
         <v>1300</v>
       </c>
+      <c r="E34" s="2">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
       <c r="F34">
         <v>1300</v>
       </c>
@@ -3206,6 +3329,10 @@
       <c r="D35">
         <v>2100</v>
       </c>
+      <c r="E35" s="2">
+        <f t="shared" si="0"/>
+        <v>21000</v>
+      </c>
       <c r="F35">
         <v>1500</v>
       </c>
@@ -3253,6 +3380,10 @@
       <c r="D36">
         <v>30</v>
       </c>
+      <c r="E36" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
       <c r="F36">
         <v>350</v>
       </c>
@@ -3300,6 +3431,10 @@
       <c r="D37">
         <v>60</v>
       </c>
+      <c r="E37" s="2">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
       <c r="F37">
         <v>450</v>
       </c>
@@ -3347,6 +3482,10 @@
       <c r="D38">
         <v>100</v>
       </c>
+      <c r="E38" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
       <c r="F38">
         <v>500</v>
       </c>
@@ -3394,6 +3533,10 @@
       <c r="D39">
         <v>1100</v>
       </c>
+      <c r="E39" s="2">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
       <c r="F39">
         <v>2000</v>
       </c>
@@ -3444,6 +3587,10 @@
       <c r="D40">
         <v>100</v>
       </c>
+      <c r="E40" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
       <c r="F40">
         <v>650</v>
       </c>
@@ -3494,6 +3641,10 @@
       <c r="D41">
         <v>500</v>
       </c>
+      <c r="E41" s="2">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
       <c r="F41">
         <v>1200</v>
       </c>
@@ -3544,6 +3695,10 @@
       <c r="D42">
         <v>60</v>
       </c>
+      <c r="E42" s="2">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
       <c r="F42">
         <v>650</v>
       </c>
@@ -3594,6 +3749,10 @@
       <c r="D43">
         <v>380</v>
       </c>
+      <c r="E43" s="2">
+        <f t="shared" si="0"/>
+        <v>3800</v>
+      </c>
       <c r="F43">
         <v>1050</v>
       </c>
@@ -3629,6 +3788,10 @@
       <c r="D44">
         <v>40</v>
       </c>
+      <c r="E44" s="2">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
       <c r="F44">
         <v>442</v>
       </c>
@@ -3679,6 +3842,10 @@
       <c r="D45">
         <v>50</v>
       </c>
+      <c r="E45" s="2">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
       <c r="F45">
         <v>494</v>
       </c>
@@ -3729,6 +3896,10 @@
       <c r="D46">
         <v>80</v>
       </c>
+      <c r="E46" s="2">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
       <c r="F46">
         <v>626</v>
       </c>
@@ -3779,6 +3950,10 @@
       <c r="D47">
         <v>100</v>
       </c>
+      <c r="E47" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
       <c r="F47">
         <v>700</v>
       </c>
@@ -3829,6 +4004,10 @@
       <c r="D48">
         <v>130</v>
       </c>
+      <c r="E48" s="2">
+        <f>D48*10</f>
+        <v>1300</v>
+      </c>
       <c r="F48">
         <v>798</v>
       </c>
@@ -3879,6 +4058,10 @@
       <c r="D49">
         <v>160</v>
       </c>
+      <c r="E49" s="2">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
       <c r="F49">
         <v>885</v>
       </c>
@@ -3929,6 +4112,10 @@
       <c r="D50">
         <v>180</v>
       </c>
+      <c r="E50" s="2">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
       <c r="F50">
         <v>939</v>
       </c>
@@ -3979,6 +4166,10 @@
       <c r="D51">
         <v>200</v>
       </c>
+      <c r="E51" s="2">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
       <c r="F51">
         <v>989</v>
       </c>
@@ -4029,6 +4220,10 @@
       <c r="D52">
         <v>220</v>
       </c>
+      <c r="E52" s="2">
+        <f t="shared" si="0"/>
+        <v>2200</v>
+      </c>
       <c r="F52">
         <v>1038</v>
       </c>
@@ -4079,6 +4274,10 @@
       <c r="D53">
         <v>280</v>
       </c>
+      <c r="E53" s="2">
+        <f t="shared" si="0"/>
+        <v>2800</v>
+      </c>
       <c r="F53">
         <v>1171</v>
       </c>
@@ -4129,6 +4328,10 @@
       <c r="D54">
         <v>380</v>
       </c>
+      <c r="E54" s="2">
+        <f t="shared" si="0"/>
+        <v>3800</v>
+      </c>
       <c r="F54">
         <v>1364</v>
       </c>
@@ -4179,6 +4382,10 @@
       <c r="D55">
         <v>450</v>
       </c>
+      <c r="E55" s="2">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
       <c r="F55">
         <v>1484</v>
       </c>
@@ -4229,6 +4436,10 @@
       <c r="D56">
         <v>550</v>
       </c>
+      <c r="E56" s="2">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
       <c r="F56">
         <v>1641</v>
       </c>
@@ -4279,6 +4490,10 @@
       <c r="D57">
         <v>700</v>
       </c>
+      <c r="E57" s="2">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
       <c r="F57">
         <v>1852</v>
       </c>
@@ -4329,6 +4544,10 @@
       <c r="D58">
         <v>900</v>
       </c>
+      <c r="E58" s="2">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
       <c r="F58">
         <v>2100</v>
       </c>
@@ -4379,6 +4598,10 @@
       <c r="D59">
         <v>1100</v>
       </c>
+      <c r="E59" s="2">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
       <c r="F59">
         <v>2321</v>
       </c>
@@ -4429,6 +4652,10 @@
       <c r="D60">
         <v>1500</v>
       </c>
+      <c r="E60" s="2">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
       <c r="F60">
         <v>2711</v>
       </c>
@@ -4479,6 +4706,10 @@
       <c r="D61">
         <v>2000</v>
       </c>
+      <c r="E61" s="2">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
       <c r="F61">
         <v>3130</v>
       </c>
@@ -4529,6 +4760,10 @@
       <c r="D62">
         <v>3000</v>
       </c>
+      <c r="E62" s="2">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
       <c r="F62">
         <v>3834</v>
       </c>
@@ -4579,6 +4814,10 @@
       <c r="D63">
         <v>100</v>
       </c>
+      <c r="E63" s="2">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
       <c r="F63">
         <v>650</v>
       </c>
@@ -4629,6 +4868,10 @@
       <c r="D64">
         <v>130</v>
       </c>
+      <c r="E64" s="2">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
       <c r="H64">
         <v>530</v>
       </c>
@@ -4667,6 +4910,10 @@
       <c r="D65">
         <v>180</v>
       </c>
+      <c r="E65" s="2">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
       <c r="H65">
         <v>570</v>
       </c>
@@ -4705,6 +4952,10 @@
       <c r="D66">
         <v>220</v>
       </c>
+      <c r="E66" s="2">
+        <f t="shared" si="0"/>
+        <v>2200</v>
+      </c>
       <c r="H66">
         <v>650</v>
       </c>
@@ -4743,6 +4994,10 @@
       <c r="D67">
         <v>500</v>
       </c>
+      <c r="E67" s="2">
+        <f t="shared" ref="E67:E69" si="1">D67*10</f>
+        <v>5000</v>
+      </c>
       <c r="H67">
         <v>830</v>
       </c>
@@ -4781,6 +5036,10 @@
       <c r="D68">
         <v>85</v>
       </c>
+      <c r="E68" s="2">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
       <c r="H68">
         <v>470</v>
       </c>
@@ -4816,6 +5075,10 @@
       <c r="D69">
         <v>130</v>
       </c>
+      <c r="E69" s="2">
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
       <c r="F69">
         <v>750</v>
       </c>
@@ -4863,6 +5126,10 @@
       <c r="D70">
         <v>180</v>
       </c>
+      <c r="E70" s="2">
+        <f>D70*10</f>
+        <v>1800</v>
+      </c>
       <c r="F70">
         <v>850</v>
       </c>
@@ -4910,6 +5177,10 @@
       <c r="D71">
         <v>220</v>
       </c>
+      <c r="E71" s="2">
+        <f t="shared" ref="E71:E89" si="2">D71*10</f>
+        <v>2200</v>
+      </c>
       <c r="F71">
         <v>900</v>
       </c>
@@ -4957,6 +5228,10 @@
       <c r="D72">
         <v>280</v>
       </c>
+      <c r="E72" s="2">
+        <f t="shared" si="2"/>
+        <v>2800</v>
+      </c>
       <c r="F72">
         <v>950</v>
       </c>
@@ -5004,6 +5279,10 @@
       <c r="D73">
         <v>350</v>
       </c>
+      <c r="E73" s="2">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
       <c r="F73">
         <v>1050</v>
       </c>
@@ -5051,6 +5330,10 @@
       <c r="D74">
         <v>420</v>
       </c>
+      <c r="E74" s="2">
+        <f t="shared" si="2"/>
+        <v>4200</v>
+      </c>
       <c r="F74">
         <v>1150</v>
       </c>
@@ -5098,6 +5381,10 @@
       <c r="D75">
         <v>520</v>
       </c>
+      <c r="E75" s="2">
+        <f t="shared" si="2"/>
+        <v>5200</v>
+      </c>
       <c r="F75">
         <v>1250</v>
       </c>
@@ -5145,6 +5432,10 @@
       <c r="D76">
         <v>600</v>
       </c>
+      <c r="E76" s="2">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
       <c r="F76">
         <v>1350</v>
       </c>
@@ -5192,6 +5483,10 @@
       <c r="D77">
         <v>130</v>
       </c>
+      <c r="E77" s="2">
+        <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
       <c r="F77">
         <v>750</v>
       </c>
@@ -5239,6 +5534,10 @@
       <c r="D78">
         <v>180</v>
       </c>
+      <c r="E78" s="2">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
       <c r="F78">
         <v>850</v>
       </c>
@@ -5286,6 +5585,10 @@
       <c r="D79">
         <v>220</v>
       </c>
+      <c r="E79" s="2">
+        <f t="shared" si="2"/>
+        <v>2200</v>
+      </c>
       <c r="F79">
         <v>900</v>
       </c>
@@ -5333,6 +5636,10 @@
       <c r="D80">
         <v>280</v>
       </c>
+      <c r="E80" s="2">
+        <f t="shared" si="2"/>
+        <v>2800</v>
+      </c>
       <c r="F80">
         <v>950</v>
       </c>
@@ -5380,6 +5687,10 @@
       <c r="D81">
         <v>350</v>
       </c>
+      <c r="E81" s="2">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
       <c r="F81">
         <v>1050</v>
       </c>
@@ -5427,6 +5738,10 @@
       <c r="D82">
         <v>420</v>
       </c>
+      <c r="E82" s="2">
+        <f t="shared" si="2"/>
+        <v>4200</v>
+      </c>
       <c r="F82">
         <v>1150</v>
       </c>
@@ -5474,6 +5789,10 @@
       <c r="D83">
         <v>130</v>
       </c>
+      <c r="E83" s="2">
+        <f t="shared" si="2"/>
+        <v>1300</v>
+      </c>
       <c r="F83">
         <v>750</v>
       </c>
@@ -5521,6 +5840,10 @@
       <c r="D84">
         <v>180</v>
       </c>
+      <c r="E84" s="2">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
       <c r="F84">
         <v>850</v>
       </c>
@@ -5568,6 +5891,10 @@
       <c r="D85">
         <v>220</v>
       </c>
+      <c r="E85" s="2">
+        <f t="shared" si="2"/>
+        <v>2200</v>
+      </c>
       <c r="F85">
         <v>900</v>
       </c>
@@ -5615,6 +5942,10 @@
       <c r="D86">
         <v>250</v>
       </c>
+      <c r="E86" s="2">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
       <c r="F86">
         <v>930</v>
       </c>
@@ -5662,6 +5993,10 @@
       <c r="D87">
         <v>300</v>
       </c>
+      <c r="E87" s="2">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
       <c r="F87">
         <v>980</v>
       </c>
@@ -5709,6 +6044,10 @@
       <c r="D88">
         <v>350</v>
       </c>
+      <c r="E88" s="2">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
       <c r="F88">
         <v>1050</v>
       </c>
@@ -5756,6 +6095,10 @@
       <c r="D89">
         <v>400</v>
       </c>
+      <c r="E89" s="2">
+        <f t="shared" si="2"/>
+        <v>4000</v>
+      </c>
       <c r="F89">
         <v>1100</v>
       </c>
@@ -5803,6 +6146,10 @@
       <c r="D90">
         <v>500</v>
       </c>
+      <c r="E90" s="2">
+        <f>D90*10</f>
+        <v>5000</v>
+      </c>
       <c r="F90">
         <v>1200</v>
       </c>
@@ -5850,6 +6197,10 @@
       <c r="D91">
         <v>13</v>
       </c>
+      <c r="E91" s="2">
+        <f t="shared" ref="E91:E108" si="3">D91*10</f>
+        <v>130</v>
+      </c>
       <c r="F91">
         <v>350</v>
       </c>
@@ -5897,6 +6248,10 @@
       <c r="D92">
         <v>33</v>
       </c>
+      <c r="E92" s="2">
+        <f t="shared" si="3"/>
+        <v>330</v>
+      </c>
       <c r="F92">
         <v>450</v>
       </c>
@@ -5944,6 +6299,10 @@
       <c r="D93">
         <v>66</v>
       </c>
+      <c r="E93" s="2">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
       <c r="F93">
         <v>550</v>
       </c>
@@ -5991,6 +6350,10 @@
       <c r="D94" s="2">
         <v>100</v>
       </c>
+      <c r="E94" s="2">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
       <c r="F94" s="2">
         <v>650</v>
       </c>
@@ -6038,6 +6401,10 @@
       <c r="D95" s="2">
         <v>150</v>
       </c>
+      <c r="E95" s="2">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
       <c r="F95" s="2">
         <v>750</v>
       </c>
@@ -6085,6 +6452,10 @@
       <c r="D96" s="2">
         <v>200</v>
       </c>
+      <c r="E96" s="2">
+        <f t="shared" si="3"/>
+        <v>2000</v>
+      </c>
       <c r="F96" s="2">
         <v>830</v>
       </c>
@@ -6132,6 +6503,10 @@
       <c r="D97">
         <v>55</v>
       </c>
+      <c r="E97" s="2">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
       <c r="F97">
         <v>520</v>
       </c>
@@ -6179,6 +6554,10 @@
       <c r="D98" s="2">
         <v>65</v>
       </c>
+      <c r="E98" s="2">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
       <c r="F98" s="2">
         <v>550</v>
       </c>
@@ -6226,6 +6605,10 @@
       <c r="D99">
         <v>85</v>
       </c>
+      <c r="E99" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F99">
         <v>650</v>
       </c>
@@ -6282,6 +6665,10 @@
       <c r="D100" s="2">
         <v>85</v>
       </c>
+      <c r="E100" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F100" s="2">
         <v>650</v>
       </c>
@@ -6338,6 +6725,10 @@
       <c r="D101" s="2">
         <v>85</v>
       </c>
+      <c r="E101" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F101" s="2">
         <v>650</v>
       </c>
@@ -6394,6 +6785,10 @@
       <c r="D102">
         <v>85</v>
       </c>
+      <c r="E102" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F102">
         <v>650</v>
       </c>
@@ -6450,6 +6845,10 @@
       <c r="D103" s="2">
         <v>85</v>
       </c>
+      <c r="E103" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F103" s="2">
         <v>650</v>
       </c>
@@ -6506,6 +6905,10 @@
       <c r="D104">
         <v>85</v>
       </c>
+      <c r="E104" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F104">
         <v>650</v>
       </c>
@@ -6562,6 +6965,10 @@
       <c r="D105" s="2">
         <v>85</v>
       </c>
+      <c r="E105" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F105" s="2">
         <v>650</v>
       </c>
@@ -6618,6 +7025,10 @@
       <c r="D106" s="2">
         <v>85</v>
       </c>
+      <c r="E106" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F106" s="2">
         <v>650</v>
       </c>
@@ -6674,6 +7085,10 @@
       <c r="D107">
         <v>85</v>
       </c>
+      <c r="E107" s="2">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
       <c r="F107">
         <v>650</v>
       </c>
@@ -6730,6 +7145,10 @@
       <c r="D108" s="2">
         <v>130</v>
       </c>
+      <c r="E108" s="2">
+        <f t="shared" si="3"/>
+        <v>1300</v>
+      </c>
       <c r="F108" s="2">
         <v>750</v>
       </c>
@@ -6777,6 +7196,10 @@
       <c r="D109" s="2">
         <v>130</v>
       </c>
+      <c r="E109" s="2">
+        <f>D109*10</f>
+        <v>1300</v>
+      </c>
       <c r="F109" s="2">
         <v>750</v>
       </c>
@@ -6824,6 +7247,10 @@
       <c r="D110">
         <v>190</v>
       </c>
+      <c r="E110" s="2">
+        <f t="shared" ref="E110:E127" si="4">D110*10</f>
+        <v>1900</v>
+      </c>
       <c r="F110">
         <v>820</v>
       </c>
@@ -6871,6 +7298,10 @@
       <c r="D111" s="2">
         <v>190</v>
       </c>
+      <c r="E111" s="2">
+        <f t="shared" si="4"/>
+        <v>1900</v>
+      </c>
       <c r="F111" s="2">
         <v>820</v>
       </c>
@@ -6918,6 +7349,10 @@
       <c r="D112">
         <v>190</v>
       </c>
+      <c r="E112" s="2">
+        <f t="shared" si="4"/>
+        <v>1900</v>
+      </c>
       <c r="F112">
         <v>820</v>
       </c>
@@ -6965,6 +7400,10 @@
       <c r="D113">
         <v>240</v>
       </c>
+      <c r="E113" s="2">
+        <f t="shared" si="4"/>
+        <v>2400</v>
+      </c>
       <c r="F113">
         <v>900</v>
       </c>
@@ -7012,6 +7451,10 @@
       <c r="D114">
         <v>240</v>
       </c>
+      <c r="E114" s="2">
+        <f t="shared" si="4"/>
+        <v>2400</v>
+      </c>
       <c r="F114">
         <v>900</v>
       </c>
@@ -7059,6 +7502,10 @@
       <c r="D115">
         <v>240</v>
       </c>
+      <c r="E115" s="2">
+        <f t="shared" si="4"/>
+        <v>2400</v>
+      </c>
       <c r="F115">
         <v>900</v>
       </c>
@@ -7106,6 +7553,10 @@
       <c r="D116">
         <v>310</v>
       </c>
+      <c r="E116" s="2">
+        <f t="shared" si="4"/>
+        <v>3100</v>
+      </c>
       <c r="F116">
         <v>950</v>
       </c>
@@ -7153,6 +7604,10 @@
       <c r="D117">
         <v>310</v>
       </c>
+      <c r="E117" s="2">
+        <f t="shared" si="4"/>
+        <v>3100</v>
+      </c>
       <c r="F117">
         <v>950</v>
       </c>
@@ -7200,6 +7655,10 @@
       <c r="D118">
         <v>350</v>
       </c>
+      <c r="E118" s="2">
+        <f t="shared" si="4"/>
+        <v>3500</v>
+      </c>
       <c r="F118">
         <v>1050</v>
       </c>
@@ -7247,6 +7706,10 @@
       <c r="D119">
         <v>460</v>
       </c>
+      <c r="E119" s="2">
+        <f t="shared" si="4"/>
+        <v>4600</v>
+      </c>
       <c r="F119">
         <v>1150</v>
       </c>
@@ -7294,6 +7757,10 @@
       <c r="D120">
         <v>550</v>
       </c>
+      <c r="E120" s="2">
+        <f t="shared" si="4"/>
+        <v>5500</v>
+      </c>
       <c r="F120">
         <v>1250</v>
       </c>
@@ -7341,6 +7808,10 @@
       <c r="D121">
         <v>130</v>
       </c>
+      <c r="E121" s="2">
+        <f t="shared" si="4"/>
+        <v>1300</v>
+      </c>
       <c r="F121">
         <v>750</v>
       </c>
@@ -7388,6 +7859,10 @@
       <c r="D122">
         <v>190</v>
       </c>
+      <c r="E122" s="2">
+        <f t="shared" si="4"/>
+        <v>1900</v>
+      </c>
       <c r="F122">
         <v>820</v>
       </c>
@@ -7435,6 +7910,10 @@
       <c r="D123">
         <v>240</v>
       </c>
+      <c r="E123" s="2">
+        <f t="shared" si="4"/>
+        <v>2400</v>
+      </c>
       <c r="F123">
         <v>900</v>
       </c>
@@ -7482,6 +7961,10 @@
       <c r="D124">
         <v>310</v>
       </c>
+      <c r="E124" s="2">
+        <f t="shared" si="4"/>
+        <v>3100</v>
+      </c>
       <c r="F124">
         <v>950</v>
       </c>
@@ -7529,6 +8012,10 @@
       <c r="D125">
         <v>350</v>
       </c>
+      <c r="E125" s="2">
+        <f t="shared" si="4"/>
+        <v>3500</v>
+      </c>
       <c r="F125">
         <v>1050</v>
       </c>
@@ -7576,6 +8063,10 @@
       <c r="D126">
         <v>460</v>
       </c>
+      <c r="E126" s="2">
+        <f t="shared" si="4"/>
+        <v>4600</v>
+      </c>
       <c r="F126">
         <v>1150</v>
       </c>
@@ -7623,6 +8114,10 @@
       <c r="D127">
         <v>550</v>
       </c>
+      <c r="E127" s="2">
+        <f t="shared" si="4"/>
+        <v>5500</v>
+      </c>
       <c r="F127">
         <v>1250</v>
       </c>
@@ -7670,6 +8165,10 @@
       <c r="D128">
         <v>220</v>
       </c>
+      <c r="E128" s="2">
+        <f>D128*10</f>
+        <v>2200</v>
+      </c>
       <c r="F128">
         <v>880</v>
       </c>
@@ -7717,6 +8216,10 @@
       <c r="D129">
         <v>350</v>
       </c>
+      <c r="E129" s="2">
+        <f t="shared" ref="E129:E145" si="5">D129*10</f>
+        <v>3500</v>
+      </c>
       <c r="F129">
         <v>1050</v>
       </c>
@@ -7764,6 +8267,10 @@
       <c r="D130">
         <v>450</v>
       </c>
+      <c r="E130" s="2">
+        <f t="shared" si="5"/>
+        <v>4500</v>
+      </c>
       <c r="F130">
         <v>1150</v>
       </c>
@@ -7811,6 +8318,10 @@
       <c r="D131">
         <v>550</v>
       </c>
+      <c r="E131" s="2">
+        <f t="shared" si="5"/>
+        <v>5500</v>
+      </c>
       <c r="F131">
         <v>1250</v>
       </c>
@@ -7858,6 +8369,10 @@
       <c r="D132">
         <v>240</v>
       </c>
+      <c r="E132" s="2">
+        <f t="shared" si="5"/>
+        <v>2400</v>
+      </c>
       <c r="F132">
         <v>900</v>
       </c>
@@ -7905,6 +8420,10 @@
       <c r="D133">
         <v>350</v>
       </c>
+      <c r="E133" s="2">
+        <f t="shared" si="5"/>
+        <v>3500</v>
+      </c>
       <c r="F133">
         <v>1050</v>
       </c>
@@ -7952,6 +8471,10 @@
       <c r="D134">
         <v>460</v>
       </c>
+      <c r="E134" s="2">
+        <f t="shared" si="5"/>
+        <v>4600</v>
+      </c>
       <c r="F134">
         <v>1150</v>
       </c>
@@ -7999,6 +8522,10 @@
       <c r="D135">
         <v>55</v>
       </c>
+      <c r="E135" s="2">
+        <f t="shared" si="5"/>
+        <v>550</v>
+      </c>
       <c r="F135">
         <v>560</v>
       </c>
@@ -8046,6 +8573,10 @@
       <c r="D136">
         <v>75</v>
       </c>
+      <c r="E136" s="2">
+        <f t="shared" si="5"/>
+        <v>750</v>
+      </c>
       <c r="F136">
         <v>630</v>
       </c>
@@ -8093,6 +8624,10 @@
       <c r="D137">
         <v>143</v>
       </c>
+      <c r="E137" s="2">
+        <f t="shared" si="5"/>
+        <v>1430</v>
+      </c>
       <c r="F137">
         <v>750</v>
       </c>
@@ -8140,6 +8675,10 @@
       <c r="D138">
         <v>198</v>
       </c>
+      <c r="E138" s="2">
+        <f t="shared" si="5"/>
+        <v>1980</v>
+      </c>
       <c r="F138">
         <v>830</v>
       </c>
@@ -8187,6 +8726,10 @@
       <c r="D139">
         <v>308</v>
       </c>
+      <c r="E139" s="2">
+        <f t="shared" si="5"/>
+        <v>3080</v>
+      </c>
       <c r="F139">
         <v>900</v>
       </c>
@@ -8234,6 +8777,10 @@
       <c r="D140">
         <v>385</v>
       </c>
+      <c r="E140" s="2">
+        <f t="shared" si="5"/>
+        <v>3850</v>
+      </c>
       <c r="F140">
         <v>1020</v>
       </c>
@@ -8281,6 +8828,10 @@
       <c r="D141">
         <v>495</v>
       </c>
+      <c r="E141" s="2">
+        <f t="shared" si="5"/>
+        <v>4950</v>
+      </c>
       <c r="F141">
         <v>1150</v>
       </c>
@@ -8328,6 +8879,10 @@
       <c r="D142">
         <v>550</v>
       </c>
+      <c r="E142" s="2">
+        <f t="shared" si="5"/>
+        <v>5500</v>
+      </c>
       <c r="F142">
         <v>1250</v>
       </c>
@@ -8375,6 +8930,10 @@
       <c r="D143">
         <v>143</v>
       </c>
+      <c r="E143" s="2">
+        <f t="shared" si="5"/>
+        <v>1430</v>
+      </c>
       <c r="F143">
         <v>750</v>
       </c>
@@ -8422,6 +8981,10 @@
       <c r="D144">
         <v>198</v>
       </c>
+      <c r="E144" s="2">
+        <f t="shared" si="5"/>
+        <v>1980</v>
+      </c>
       <c r="F144">
         <v>830</v>
       </c>
@@ -8469,6 +9032,10 @@
       <c r="D145">
         <v>242</v>
       </c>
+      <c r="E145" s="2">
+        <f t="shared" si="5"/>
+        <v>2420</v>
+      </c>
       <c r="F145">
         <v>880</v>
       </c>
@@ -8516,6 +9083,10 @@
       <c r="D146">
         <v>308</v>
       </c>
+      <c r="E146" s="2">
+        <f>D146*10</f>
+        <v>3080</v>
+      </c>
       <c r="F146">
         <v>950</v>
       </c>
@@ -8563,6 +9134,10 @@
       <c r="D147">
         <v>385</v>
       </c>
+      <c r="E147" s="2">
+        <f t="shared" ref="E147:E164" si="6">D147*10</f>
+        <v>3850</v>
+      </c>
       <c r="F147">
         <v>1050</v>
       </c>
@@ -8610,6 +9185,10 @@
       <c r="D148">
         <v>33</v>
       </c>
+      <c r="E148" s="2">
+        <f t="shared" si="6"/>
+        <v>330</v>
+      </c>
       <c r="F148">
         <v>450</v>
       </c>
@@ -8657,6 +9236,10 @@
       <c r="D149">
         <v>55</v>
       </c>
+      <c r="E149" s="2">
+        <f t="shared" si="6"/>
+        <v>550</v>
+      </c>
       <c r="F149">
         <v>560</v>
       </c>
@@ -8704,6 +9287,10 @@
       <c r="D150">
         <v>75</v>
       </c>
+      <c r="E150" s="2">
+        <f t="shared" si="6"/>
+        <v>750</v>
+      </c>
       <c r="F150">
         <v>630</v>
       </c>
@@ -8751,6 +9338,10 @@
       <c r="D151">
         <v>143</v>
       </c>
+      <c r="E151" s="2">
+        <f t="shared" si="6"/>
+        <v>1430</v>
+      </c>
       <c r="F151">
         <v>750</v>
       </c>
@@ -8798,6 +9389,10 @@
       <c r="D152">
         <v>198</v>
       </c>
+      <c r="E152" s="2">
+        <f t="shared" si="6"/>
+        <v>1980</v>
+      </c>
       <c r="F152">
         <v>830</v>
       </c>
@@ -8845,6 +9440,10 @@
       <c r="D153">
         <v>308</v>
       </c>
+      <c r="E153" s="2">
+        <f t="shared" si="6"/>
+        <v>3080</v>
+      </c>
       <c r="F153">
         <v>900</v>
       </c>
@@ -8892,6 +9491,10 @@
       <c r="D154">
         <v>385</v>
       </c>
+      <c r="E154" s="2">
+        <f t="shared" si="6"/>
+        <v>3850</v>
+      </c>
       <c r="F154">
         <v>1020</v>
       </c>
@@ -8939,6 +9542,10 @@
       <c r="D155">
         <v>220</v>
       </c>
+      <c r="E155" s="2">
+        <f t="shared" si="6"/>
+        <v>2200</v>
+      </c>
       <c r="F155">
         <v>880</v>
       </c>
@@ -8986,6 +9593,10 @@
       <c r="D156">
         <v>350</v>
       </c>
+      <c r="E156" s="2">
+        <f t="shared" si="6"/>
+        <v>3500</v>
+      </c>
       <c r="F156">
         <v>1050</v>
       </c>
@@ -9033,6 +9644,10 @@
       <c r="D157" s="1">
         <v>450</v>
       </c>
+      <c r="E157" s="2">
+        <f t="shared" si="6"/>
+        <v>4500</v>
+      </c>
       <c r="F157" s="1">
         <v>1150</v>
       </c>
@@ -9081,6 +9696,10 @@
       <c r="D158" s="1">
         <v>500</v>
       </c>
+      <c r="E158" s="2">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
       <c r="F158" s="1">
         <v>1250</v>
       </c>
@@ -9129,6 +9748,10 @@
       <c r="D159" s="1">
         <v>231</v>
       </c>
+      <c r="E159" s="2">
+        <f t="shared" si="6"/>
+        <v>2310</v>
+      </c>
       <c r="F159" s="1">
         <v>880</v>
       </c>
@@ -9177,6 +9800,10 @@
       <c r="D160" s="1">
         <v>308</v>
       </c>
+      <c r="E160" s="2">
+        <f t="shared" si="6"/>
+        <v>3080</v>
+      </c>
       <c r="F160" s="1">
         <v>950</v>
       </c>
@@ -9225,6 +9852,10 @@
       <c r="D161" s="1">
         <v>385</v>
       </c>
+      <c r="E161" s="2">
+        <f t="shared" si="6"/>
+        <v>3850</v>
+      </c>
       <c r="F161" s="1">
         <v>1050</v>
       </c>
@@ -9273,6 +9904,10 @@
       <c r="D162" s="2">
         <v>550</v>
       </c>
+      <c r="E162" s="2">
+        <f t="shared" si="6"/>
+        <v>5500</v>
+      </c>
       <c r="F162" s="2">
         <v>1250</v>
       </c>
@@ -9321,6 +9956,10 @@
       <c r="D163">
         <v>33</v>
       </c>
+      <c r="E163" s="2">
+        <f t="shared" si="6"/>
+        <v>330</v>
+      </c>
       <c r="T163" s="2" t="s">
         <v>358</v>
       </c>
@@ -9332,11 +9971,15 @@
       <c r="B164" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D164">
         <v>198</v>
+      </c>
+      <c r="E164" s="2">
+        <f t="shared" si="6"/>
+        <v>1980</v>
       </c>
       <c r="F164">
         <v>790</v>
@@ -9385,8 +10028,65 @@
       <c r="C165" t="s">
         <v>356</v>
       </c>
+      <c r="D165">
+        <v>254</v>
+      </c>
+      <c r="E165" s="2">
+        <f>D165*10</f>
+        <v>2540</v>
+      </c>
       <c r="T165" s="2" t="s">
         <v>358</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>359</v>
+      </c>
+      <c r="B166" t="s">
+        <v>360</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D166">
+        <v>300</v>
+      </c>
+      <c r="E166" s="2">
+        <v>3000</v>
+      </c>
+      <c r="F166">
+        <v>970</v>
+      </c>
+      <c r="G166">
+        <v>970</v>
+      </c>
+      <c r="H166">
+        <v>720</v>
+      </c>
+      <c r="I166" s="2">
+        <v>720</v>
+      </c>
+      <c r="J166">
+        <v>900</v>
+      </c>
+      <c r="K166">
+        <v>250</v>
+      </c>
+      <c r="L166">
+        <v>650</v>
+      </c>
+      <c r="M166">
+        <v>610</v>
+      </c>
+      <c r="O166">
+        <v>341</v>
+      </c>
+      <c r="P166">
+        <v>48</v>
+      </c>
+      <c r="S166" s="2">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuehu\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a41c63436a2eeaa/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{5284095C-0E1E-4EF6-8979-969B6065ACF7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C278EC3-4754-44D4-B210-FD0CA02850E8}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{FF8D5F3C-F02A-4C00-9DC1-BC784B402D4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12F447D-8F49-42EF-8D1F-4C9967467F76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
   <si>
     <t>OEM</t>
   </si>
@@ -276,6 +276,57 @@
   </si>
   <si>
     <t>FF300-IU670</t>
+  </si>
+  <si>
+    <t>ENGEL</t>
+  </si>
+  <si>
+    <t>e-mac</t>
+  </si>
+  <si>
+    <t>e-mac 100</t>
+  </si>
+  <si>
+    <t>Validated spec</t>
+  </si>
+  <si>
+    <t>e-mac 130</t>
+  </si>
+  <si>
+    <t>30-45</t>
+  </si>
+  <si>
+    <t>Tie-bar confirmed</t>
+  </si>
+  <si>
+    <t>e-mac 180</t>
+  </si>
+  <si>
+    <t>35-50</t>
+  </si>
+  <si>
+    <t>Common config</t>
+  </si>
+  <si>
+    <t>e-mac 220</t>
+  </si>
+  <si>
+    <t>40-55</t>
+  </si>
+  <si>
+    <t>Estimated larger class</t>
+  </si>
+  <si>
+    <t>e-mac 500</t>
+  </si>
+  <si>
+    <t>55-80</t>
+  </si>
+  <si>
+    <t>Max class</t>
+  </si>
+  <si>
+    <t>e-mac 85</t>
   </si>
 </sst>
 </file>
@@ -680,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -1613,6 +1664,267 @@
         <v>150</v>
       </c>
     </row>
+    <row r="17" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="1">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" ref="E17:E22" si="3">D17*10</f>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="1">
+        <v>650</v>
+      </c>
+      <c r="G17" s="1">
+        <v>600</v>
+      </c>
+      <c r="H17" s="1">
+        <v>460</v>
+      </c>
+      <c r="I17" s="1">
+        <v>410</v>
+      </c>
+      <c r="J17" s="1">
+        <v>800</v>
+      </c>
+      <c r="K17" s="1">
+        <v>150</v>
+      </c>
+      <c r="L17" s="1">
+        <v>450</v>
+      </c>
+      <c r="M17" s="1">
+        <v>350</v>
+      </c>
+      <c r="N17" s="1">
+        <v>150</v>
+      </c>
+      <c r="O17" s="1">
+        <v>202</v>
+      </c>
+      <c r="P17" s="1">
+        <v>40</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="1">
+        <v>130</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="3"/>
+        <v>1300</v>
+      </c>
+      <c r="H18" s="1">
+        <v>530</v>
+      </c>
+      <c r="I18" s="1">
+        <v>530</v>
+      </c>
+      <c r="K18" s="1">
+        <v>150</v>
+      </c>
+      <c r="M18" s="1">
+        <v>400</v>
+      </c>
+      <c r="N18" s="1">
+        <v>150</v>
+      </c>
+      <c r="O18" s="1">
+        <v>250</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="1">
+        <v>180</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="3"/>
+        <v>1800</v>
+      </c>
+      <c r="H19" s="1">
+        <v>570</v>
+      </c>
+      <c r="I19" s="1">
+        <v>570</v>
+      </c>
+      <c r="K19" s="1">
+        <v>150</v>
+      </c>
+      <c r="M19" s="1">
+        <v>450</v>
+      </c>
+      <c r="N19" s="1">
+        <v>150</v>
+      </c>
+      <c r="O19" s="1">
+        <v>300</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="1">
+        <v>220</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="3"/>
+        <v>2200</v>
+      </c>
+      <c r="H20" s="1">
+        <v>650</v>
+      </c>
+      <c r="I20" s="1">
+        <v>650</v>
+      </c>
+      <c r="K20" s="1">
+        <v>150</v>
+      </c>
+      <c r="M20" s="1">
+        <v>500</v>
+      </c>
+      <c r="N20" s="1">
+        <v>150</v>
+      </c>
+      <c r="O20" s="1">
+        <v>350</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="1">
+        <v>500</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="H21" s="1">
+        <v>830</v>
+      </c>
+      <c r="I21" s="1">
+        <v>830</v>
+      </c>
+      <c r="K21" s="1">
+        <v>150</v>
+      </c>
+      <c r="M21" s="1">
+        <v>700</v>
+      </c>
+      <c r="N21" s="1">
+        <v>150</v>
+      </c>
+      <c r="O21" s="1">
+        <v>600</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="1">
+        <v>85</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
+      <c r="H22" s="1">
+        <v>470</v>
+      </c>
+      <c r="I22" s="1">
+        <v>420</v>
+      </c>
+      <c r="K22" s="1">
+        <v>150</v>
+      </c>
+      <c r="M22" s="1">
+        <v>320</v>
+      </c>
+      <c r="N22" s="1">
+        <v>150</v>
+      </c>
+      <c r="O22" s="1">
+        <v>23</v>
+      </c>
+      <c r="P22" s="1">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:T15">
     <sortCondition ref="A2:A15"/>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a41c63436a2eeaa/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huanger9\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{FF8D5F3C-F02A-4C00-9DC1-BC784B402D4E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12F447D-8F49-42EF-8D1F-4C9967467F76}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A0181-C88C-4DB3-A633-A713913DE625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="106">
   <si>
     <t>OEM</t>
   </si>
@@ -327,6 +340,18 @@
   </si>
   <si>
     <t>e-mac 85</t>
+  </si>
+  <si>
+    <t>SUMITOMO</t>
+  </si>
+  <si>
+    <t>SE-EV-S-HD</t>
+  </si>
+  <si>
+    <t>SE-450EV-C2200</t>
+  </si>
+  <si>
+    <t>SE-450EV-C3000</t>
   </si>
 </sst>
 </file>
@@ -345,6 +370,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -731,30 +757,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19.28515625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -816,7 +842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -870,7 +896,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -924,7 +950,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -978,7 +1004,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1032,7 +1058,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1086,7 +1112,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1140,7 +1166,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1200,7 +1226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1260,7 +1286,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1320,7 +1346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1380,7 +1406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1440,7 +1466,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1500,7 +1526,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1560,7 +1586,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>78</v>
       </c>
@@ -1614,7 +1640,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1664,7 +1690,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>85</v>
       </c>
@@ -1678,7 +1704,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" ref="E17:E22" si="3">D17*10</f>
+        <f t="shared" ref="E17:E24" si="3">D17*10</f>
         <v>1000</v>
       </c>
       <c r="F17" s="1">
@@ -1718,7 +1744,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>85</v>
       </c>
@@ -1760,7 +1786,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>85</v>
       </c>
@@ -1802,7 +1828,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>85</v>
       </c>
@@ -1844,7 +1870,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1912,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>85</v>
       </c>
@@ -1925,8 +1951,128 @@
         <v>20</v>
       </c>
     </row>
+    <row r="23" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="1">
+        <v>450</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="3"/>
+        <v>4500</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H23" s="1">
+        <v>920</v>
+      </c>
+      <c r="I23" s="1">
+        <v>920</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1625</v>
+      </c>
+      <c r="K23" s="1">
+        <v>350</v>
+      </c>
+      <c r="L23" s="1">
+        <v>800</v>
+      </c>
+      <c r="M23" s="1">
+        <v>825</v>
+      </c>
+      <c r="O23" s="1">
+        <v>390</v>
+      </c>
+      <c r="P23" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>7500</v>
+      </c>
+      <c r="R23" s="1">
+        <v>5000</v>
+      </c>
+      <c r="S23" s="1">
+        <v>220</v>
+      </c>
+      <c r="T23" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="1">
+        <v>450</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="3"/>
+        <v>4500</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H24" s="1">
+        <v>920</v>
+      </c>
+      <c r="I24" s="1">
+        <v>920</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1625</v>
+      </c>
+      <c r="K24" s="1">
+        <v>350</v>
+      </c>
+      <c r="L24" s="1">
+        <v>800</v>
+      </c>
+      <c r="M24" s="1">
+        <v>825</v>
+      </c>
+      <c r="O24" s="1">
+        <v>1390</v>
+      </c>
+      <c r="P24" s="1">
+        <v>80</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>7500</v>
+      </c>
+      <c r="R24" s="1">
+        <v>5000</v>
+      </c>
+      <c r="S24" s="1">
+        <v>220</v>
+      </c>
+      <c r="T24" s="1">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:T15">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T15">
     <sortCondition ref="A2:A15"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1937,15 +2083,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6CEE4A-7CCF-4455-857B-32193F671A1E}">
   <dimension ref="B1:E59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="33.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>69</v>
       </c>
@@ -1959,7 +2105,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +2113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +2121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
@@ -1983,7 +2129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
@@ -1991,7 +2137,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
@@ -1999,7 +2145,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
@@ -2007,7 +2153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>38</v>
       </c>
@@ -2015,12 +2161,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>41</v>
       </c>
@@ -2031,7 +2177,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
@@ -2042,7 +2188,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -2050,7 +2196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
@@ -2058,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
@@ -2069,7 +2215,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>47</v>
       </c>
@@ -2077,7 +2223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
@@ -2085,7 +2231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>49</v>
       </c>
@@ -2093,7 +2239,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>70</v>
       </c>
@@ -2101,7 +2247,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>72</v>
       </c>
@@ -2109,7 +2255,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>63</v>
       </c>
@@ -2117,98 +2263,98 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
     </row>
-    <row r="37" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
     </row>
-    <row r="38" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
     </row>
-    <row r="39" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
     </row>
-    <row r="40" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
     </row>
-    <row r="41" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
     </row>
-    <row r="42" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
     </row>
-    <row r="43" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
     </row>
-    <row r="44" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
     </row>
-    <row r="46" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
     </row>
-    <row r="47" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>62</v>
       </c>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huanger9\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990A0181-C88C-4DB3-A633-A713913DE625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F5110E-6DD2-4A5B-A462-B92C9B16E192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
   <si>
     <t>OEM</t>
   </si>
@@ -352,6 +352,87 @@
   </si>
   <si>
     <t>SE-450EV-C3000</t>
+  </si>
+  <si>
+    <t>220 S 250-60</t>
+  </si>
+  <si>
+    <t>Small hydraulic</t>
+  </si>
+  <si>
+    <t>270 S 250-70-18</t>
+  </si>
+  <si>
+    <t>Compact machine</t>
+  </si>
+  <si>
+    <t>270 S 250-70-22</t>
+  </si>
+  <si>
+    <t>270 S 250-70-25</t>
+  </si>
+  <si>
+    <t>270 S 250-100-18</t>
+  </si>
+  <si>
+    <t>270 S 250-100-22</t>
+  </si>
+  <si>
+    <t>270 S 250-100-25</t>
+  </si>
+  <si>
+    <t>270 S 350-70-18</t>
+  </si>
+  <si>
+    <t>270 S 350-70-22</t>
+  </si>
+  <si>
+    <t>270 S 350-70-25</t>
+  </si>
+  <si>
+    <t>270 S 350-100-20</t>
+  </si>
+  <si>
+    <t>270 S 350-100-25</t>
+  </si>
+  <si>
+    <t>270 S 350-100-30</t>
+  </si>
+  <si>
+    <t>270 S 350-170-25</t>
+  </si>
+  <si>
+    <t>270 S 350-170-30</t>
+  </si>
+  <si>
+    <t>270 S 350-170-35</t>
+  </si>
+  <si>
+    <t>262 S 400-70-18</t>
+  </si>
+  <si>
+    <t>263 S 400-70-22</t>
+  </si>
+  <si>
+    <t>264 S 400-70-25</t>
+  </si>
+  <si>
+    <t>265 S 400-100-20</t>
+  </si>
+  <si>
+    <t>266 S 400-100-25</t>
+  </si>
+  <si>
+    <t>267 S 400-100-30</t>
+  </si>
+  <si>
+    <t>268 S 400-170-25</t>
+  </si>
+  <si>
+    <t>269 S 400-170-30</t>
+  </si>
+  <si>
+    <t>270 S 400-170-35</t>
   </si>
 </sst>
 </file>
@@ -393,7 +474,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +484,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,7 +541,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -842,328 +929,364 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="1">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>85</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" ref="E2:E7" si="0">D2*10</f>
+        <f t="shared" ref="E2:E8" si="0">D2*10</f>
+        <v>850</v>
+      </c>
+      <c r="F2">
+        <v>650</v>
+      </c>
+      <c r="G2">
+        <v>621</v>
+      </c>
+      <c r="H2">
+        <v>410</v>
+      </c>
+      <c r="I2">
+        <v>410</v>
+      </c>
+      <c r="J2">
+        <v>650</v>
+      </c>
+      <c r="K2" s="1">
+        <v>200</v>
+      </c>
+      <c r="L2" s="1">
         <v>500</v>
-      </c>
-      <c r="F2" s="1">
-        <v>446</v>
-      </c>
-      <c r="G2" s="1">
-        <v>446</v>
-      </c>
-      <c r="H2" s="1">
-        <v>320</v>
-      </c>
-      <c r="I2" s="1">
-        <v>320</v>
-      </c>
-      <c r="J2" s="1">
-        <v>550</v>
-      </c>
-      <c r="K2" s="1">
-        <v>200</v>
       </c>
       <c r="M2" s="1">
         <v>350</v>
       </c>
-      <c r="O2" s="1">
-        <v>29</v>
-      </c>
-      <c r="P2" s="1">
-        <v>20</v>
+      <c r="N2">
+        <v>200</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1174</v>
       </c>
       <c r="R2" s="1">
-        <v>180</v>
-      </c>
-      <c r="S2" s="1">
-        <v>125</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>73</v>
+        <v>704</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="F3" s="1">
+        <v>650</v>
+      </c>
+      <c r="G3" s="1">
+        <v>621</v>
+      </c>
+      <c r="H3" s="1">
+        <v>410</v>
+      </c>
+      <c r="I3" s="1">
+        <v>410</v>
+      </c>
+      <c r="J3" s="1">
+        <v>650</v>
+      </c>
+      <c r="K3" s="1">
+        <v>200</v>
+      </c>
+      <c r="L3" s="1">
         <v>500</v>
-      </c>
-      <c r="F3" s="1">
-        <v>446</v>
-      </c>
-      <c r="G3" s="1">
-        <v>446</v>
-      </c>
-      <c r="H3" s="1">
-        <v>320</v>
-      </c>
-      <c r="I3" s="1">
-        <v>320</v>
-      </c>
-      <c r="J3" s="1">
-        <v>550</v>
-      </c>
-      <c r="K3" s="1">
-        <v>200</v>
       </c>
       <c r="M3" s="1">
         <v>350</v>
       </c>
-      <c r="O3" s="9">
-        <v>45</v>
-      </c>
-      <c r="P3" s="9">
-        <v>25</v>
+      <c r="N3" s="1">
+        <v>200</v>
+      </c>
+      <c r="O3" s="1">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1174</v>
       </c>
       <c r="R3" s="1">
-        <v>180</v>
-      </c>
-      <c r="S3" s="1">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="F4" s="1">
+        <v>650</v>
+      </c>
+      <c r="G4" s="1">
+        <v>621</v>
+      </c>
+      <c r="H4" s="1">
+        <v>410</v>
+      </c>
+      <c r="I4" s="1">
+        <v>410</v>
+      </c>
+      <c r="J4" s="1">
+        <v>650</v>
+      </c>
+      <c r="K4" s="1">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1">
         <v>500</v>
-      </c>
-      <c r="F4" s="1">
-        <v>446</v>
-      </c>
-      <c r="G4" s="1">
-        <v>446</v>
-      </c>
-      <c r="H4" s="1">
-        <v>320</v>
-      </c>
-      <c r="I4" s="1">
-        <v>320</v>
-      </c>
-      <c r="J4" s="1">
-        <v>550</v>
-      </c>
-      <c r="K4" s="1">
-        <v>200</v>
       </c>
       <c r="M4" s="1">
         <v>350</v>
       </c>
-      <c r="O4" s="9">
-        <v>65</v>
-      </c>
-      <c r="P4" s="9">
+      <c r="N4" s="1">
+        <v>200</v>
+      </c>
+      <c r="O4" s="1">
         <v>30</v>
       </c>
+      <c r="P4" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1174</v>
+      </c>
       <c r="R4" s="1">
-        <v>180</v>
-      </c>
-      <c r="S4" s="1">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="1">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>85</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="F5">
+        <v>650</v>
+      </c>
+      <c r="G5">
+        <v>621</v>
+      </c>
+      <c r="H5">
+        <v>410</v>
+      </c>
+      <c r="I5" s="1">
+        <v>410</v>
+      </c>
+      <c r="J5">
+        <v>650</v>
+      </c>
+      <c r="K5">
+        <v>200</v>
+      </c>
+      <c r="L5">
         <v>500</v>
       </c>
-      <c r="F5" s="1">
-        <v>446</v>
-      </c>
-      <c r="G5" s="1">
-        <v>446</v>
-      </c>
-      <c r="H5" s="1">
-        <v>320</v>
-      </c>
-      <c r="I5" s="1">
-        <v>320</v>
-      </c>
-      <c r="J5" s="1">
-        <v>550</v>
-      </c>
-      <c r="K5" s="1">
-        <v>200</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="M5">
         <v>350</v>
       </c>
-      <c r="O5" s="9">
-        <v>54</v>
-      </c>
-      <c r="P5" s="9">
+      <c r="N5">
+        <v>200</v>
+      </c>
+      <c r="O5">
+        <v>47</v>
+      </c>
+      <c r="P5">
         <v>25</v>
       </c>
+      <c r="Q5" s="1">
+        <v>1174</v>
+      </c>
       <c r="R5" s="1">
-        <v>180</v>
-      </c>
-      <c r="S5" s="1">
-        <v>125</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>73</v>
+        <v>704</v>
+      </c>
+      <c r="T5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="F6" s="1">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="G6" s="1">
-        <v>446</v>
+        <v>621</v>
       </c>
       <c r="H6" s="1">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="I6" s="1">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="J6" s="1">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="K6" s="1">
-        <v>200</v>
+        <v>400</v>
+      </c>
+      <c r="L6" s="1">
+        <v>700</v>
       </c>
       <c r="M6" s="1">
         <v>350</v>
       </c>
-      <c r="O6" s="9">
-        <v>77</v>
-      </c>
-      <c r="P6" s="9">
-        <v>30</v>
+      <c r="N6" s="1">
+        <v>200</v>
+      </c>
+      <c r="O6" s="1">
+        <v>85</v>
+      </c>
+      <c r="P6" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1174</v>
       </c>
       <c r="R6" s="1">
-        <v>180</v>
-      </c>
-      <c r="S6" s="1">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="F7" s="1">
-        <v>446</v>
+        <v>650</v>
       </c>
       <c r="G7" s="1">
-        <v>446</v>
+        <v>621</v>
       </c>
       <c r="H7" s="1">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="I7" s="1">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="J7" s="1">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="K7" s="1">
-        <v>200</v>
+        <v>400</v>
+      </c>
+      <c r="L7" s="1">
+        <v>700</v>
       </c>
       <c r="M7" s="1">
         <v>350</v>
       </c>
-      <c r="O7" s="9">
-        <v>105</v>
-      </c>
-      <c r="P7" s="9">
-        <v>35</v>
+      <c r="N7" s="1">
+        <v>200</v>
+      </c>
+      <c r="O7" s="1">
+        <v>113</v>
+      </c>
+      <c r="P7" s="1">
+        <v>36</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1174</v>
       </c>
       <c r="R7" s="1">
-        <v>180</v>
-      </c>
-      <c r="S7" s="1">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -1174,13 +1297,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>85</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" ref="E8:E14" si="1">D8*10</f>
+        <f t="shared" si="0"/>
         <v>850</v>
       </c>
       <c r="F8">
@@ -1198,23 +1321,23 @@
       <c r="J8">
         <v>650</v>
       </c>
-      <c r="K8" s="1">
-        <v>200</v>
-      </c>
-      <c r="L8" s="1">
-        <v>500</v>
-      </c>
-      <c r="M8" s="1">
+      <c r="K8">
+        <v>400</v>
+      </c>
+      <c r="L8">
+        <v>700</v>
+      </c>
+      <c r="M8">
         <v>350</v>
       </c>
       <c r="N8">
         <v>200</v>
       </c>
-      <c r="O8">
-        <v>19</v>
+      <c r="O8" s="1">
+        <v>154</v>
       </c>
       <c r="P8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="1">
         <v>1174</v>
@@ -1226,854 +1349,2306 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1">
+        <v>80</v>
+      </c>
+      <c r="D9">
+        <v>198</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" ref="E9" si="1">D9*10</f>
+        <v>1980</v>
+      </c>
+      <c r="F9">
+        <v>790</v>
+      </c>
+      <c r="G9">
+        <v>740</v>
+      </c>
+      <c r="H9">
+        <v>560</v>
+      </c>
+      <c r="I9">
+        <v>510</v>
+      </c>
+      <c r="J9">
+        <v>1050</v>
+      </c>
+      <c r="K9">
+        <v>200</v>
+      </c>
+      <c r="L9">
+        <v>600</v>
+      </c>
+      <c r="M9">
+        <v>450</v>
+      </c>
+      <c r="O9">
+        <v>292</v>
+      </c>
+      <c r="P9">
+        <v>45</v>
+      </c>
+      <c r="S9" s="1">
+        <v>130</v>
+      </c>
+      <c r="T9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F10">
+        <v>970</v>
+      </c>
+      <c r="G10">
+        <v>970</v>
+      </c>
+      <c r="H10">
+        <v>720</v>
+      </c>
+      <c r="I10" s="1">
+        <v>720</v>
+      </c>
+      <c r="J10">
+        <v>900</v>
+      </c>
+      <c r="K10">
+        <v>250</v>
+      </c>
+      <c r="L10">
+        <v>650</v>
+      </c>
+      <c r="M10">
+        <v>610</v>
+      </c>
+      <c r="O10">
+        <v>341</v>
+      </c>
+      <c r="P10">
+        <v>48</v>
+      </c>
+      <c r="S10" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="B11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="1">
+        <v>100</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" ref="E11:E18" si="2">D11*10</f>
+        <v>1000</v>
+      </c>
+      <c r="F11" s="1">
         <v>650</v>
       </c>
-      <c r="G9" s="1">
-        <v>621</v>
-      </c>
-      <c r="H9" s="1">
-        <v>410</v>
-      </c>
-      <c r="I9" s="1">
-        <v>410</v>
-      </c>
-      <c r="J9" s="1">
-        <v>650</v>
-      </c>
-      <c r="K9" s="1">
-        <v>200</v>
-      </c>
-      <c r="L9" s="1">
-        <v>500</v>
-      </c>
-      <c r="M9" s="1">
-        <v>350</v>
-      </c>
-      <c r="N9" s="1">
-        <v>200</v>
-      </c>
-      <c r="O9" s="1">
-        <v>24</v>
-      </c>
-      <c r="P9" s="1">
-        <v>18</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R9" s="1">
-        <v>704</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1">
-        <v>85</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F10" s="1">
-        <v>650</v>
-      </c>
-      <c r="G10" s="1">
-        <v>621</v>
-      </c>
-      <c r="H10" s="1">
-        <v>410</v>
-      </c>
-      <c r="I10" s="1">
-        <v>410</v>
-      </c>
-      <c r="J10" s="1">
-        <v>650</v>
-      </c>
-      <c r="K10" s="1">
-        <v>200</v>
-      </c>
-      <c r="L10" s="1">
-        <v>500</v>
-      </c>
-      <c r="M10" s="1">
-        <v>350</v>
-      </c>
-      <c r="N10" s="1">
-        <v>200</v>
-      </c>
-      <c r="O10" s="1">
-        <v>30</v>
-      </c>
-      <c r="P10" s="1">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R10" s="1">
-        <v>704</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>85</v>
-      </c>
-      <c r="E11" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F11">
-        <v>650</v>
-      </c>
-      <c r="G11">
-        <v>621</v>
-      </c>
-      <c r="H11">
-        <v>410</v>
+      <c r="G11" s="1">
+        <v>600</v>
+      </c>
+      <c r="H11" s="1">
+        <v>460</v>
       </c>
       <c r="I11" s="1">
         <v>410</v>
       </c>
-      <c r="J11">
-        <v>650</v>
-      </c>
-      <c r="K11">
-        <v>200</v>
-      </c>
-      <c r="L11">
-        <v>500</v>
-      </c>
-      <c r="M11">
+      <c r="J11" s="1">
+        <v>800</v>
+      </c>
+      <c r="K11" s="1">
+        <v>150</v>
+      </c>
+      <c r="L11" s="1">
+        <v>450</v>
+      </c>
+      <c r="M11" s="1">
         <v>350</v>
       </c>
-      <c r="N11">
-        <v>200</v>
-      </c>
-      <c r="O11">
-        <v>47</v>
-      </c>
-      <c r="P11">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R11" s="1">
-        <v>704</v>
-      </c>
-      <c r="T11" t="s">
-        <v>19</v>
+      <c r="N11" s="1">
+        <v>150</v>
+      </c>
+      <c r="O11" s="1">
+        <v>202</v>
+      </c>
+      <c r="P11" s="1">
+        <v>40</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>86</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="D12" s="1">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F12" s="1">
-        <v>650</v>
-      </c>
-      <c r="G12" s="1">
-        <v>621</v>
+        <f t="shared" si="2"/>
+        <v>1300</v>
       </c>
       <c r="H12" s="1">
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="I12" s="1">
-        <v>410</v>
-      </c>
-      <c r="J12" s="1">
-        <v>650</v>
+        <v>530</v>
       </c>
       <c r="K12" s="1">
+        <v>150</v>
+      </c>
+      <c r="M12" s="1">
         <v>400</v>
       </c>
-      <c r="L12" s="1">
-        <v>700</v>
-      </c>
-      <c r="M12" s="1">
-        <v>350</v>
-      </c>
       <c r="N12" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="O12" s="1">
-        <v>85</v>
-      </c>
-      <c r="P12" s="1">
-        <v>33</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R12" s="1">
-        <v>704</v>
+        <v>250</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="1">
+        <v>180</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="2"/>
+        <v>1800</v>
+      </c>
+      <c r="H13" s="1">
+        <v>570</v>
+      </c>
+      <c r="I13" s="1">
+        <v>570</v>
+      </c>
+      <c r="K13" s="1">
+        <v>150</v>
+      </c>
+      <c r="M13" s="1">
+        <v>450</v>
+      </c>
+      <c r="N13" s="1">
+        <v>150</v>
+      </c>
+      <c r="O13" s="1">
+        <v>300</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1">
+        <v>220</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="2"/>
+        <v>2200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>650</v>
+      </c>
+      <c r="I14" s="1">
+        <v>650</v>
+      </c>
+      <c r="K14" s="1">
+        <v>150</v>
+      </c>
+      <c r="M14" s="1">
+        <v>500</v>
+      </c>
+      <c r="N14" s="1">
+        <v>150</v>
+      </c>
+      <c r="O14" s="1">
+        <v>350</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="1">
+        <v>500</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="H15" s="1">
+        <v>830</v>
+      </c>
+      <c r="I15" s="1">
+        <v>830</v>
+      </c>
+      <c r="K15" s="1">
+        <v>150</v>
+      </c>
+      <c r="M15" s="1">
+        <v>700</v>
+      </c>
+      <c r="N15" s="1">
+        <v>150</v>
+      </c>
+      <c r="O15" s="1">
+        <v>600</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="1">
+        <v>85</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+      <c r="H16" s="1">
+        <v>470</v>
+      </c>
+      <c r="I16" s="1">
+        <v>420</v>
+      </c>
+      <c r="K16" s="1">
+        <v>150</v>
+      </c>
+      <c r="M16" s="1">
+        <v>320</v>
+      </c>
+      <c r="N16" s="1">
+        <v>150</v>
+      </c>
+      <c r="O16" s="1">
+        <v>23</v>
+      </c>
+      <c r="P16" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="1">
+        <v>450</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H17" s="1">
+        <v>920</v>
+      </c>
+      <c r="I17" s="1">
+        <v>920</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1625</v>
+      </c>
+      <c r="K17" s="1">
+        <v>350</v>
+      </c>
+      <c r="L17" s="1">
+        <v>800</v>
+      </c>
+      <c r="M17" s="1">
+        <v>825</v>
+      </c>
+      <c r="O17" s="1">
+        <v>390</v>
+      </c>
+      <c r="P17" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>7500</v>
+      </c>
+      <c r="R17" s="1">
+        <v>5000</v>
+      </c>
+      <c r="S17" s="1">
+        <v>220</v>
+      </c>
+      <c r="T17" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="1">
+        <v>450</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="2"/>
+        <v>4500</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H18" s="1">
+        <v>920</v>
+      </c>
+      <c r="I18" s="1">
+        <v>920</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1625</v>
+      </c>
+      <c r="K18" s="1">
+        <v>350</v>
+      </c>
+      <c r="L18" s="1">
+        <v>800</v>
+      </c>
+      <c r="M18" s="1">
+        <v>825</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1390</v>
+      </c>
+      <c r="P18" s="1">
+        <v>80</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>7500</v>
+      </c>
+      <c r="R18" s="1">
+        <v>5000</v>
+      </c>
+      <c r="S18" s="1">
+        <v>220</v>
+      </c>
+      <c r="T18" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1">
+        <f>E19/10</f>
+        <v>25</v>
+      </c>
+      <c r="E19" s="1">
+        <v>250</v>
+      </c>
+      <c r="F19" s="1">
+        <v>380</v>
+      </c>
+      <c r="G19" s="1">
+        <v>380</v>
+      </c>
+      <c r="H19" s="1">
+        <v>220</v>
+      </c>
+      <c r="I19" s="1">
+        <v>220</v>
+      </c>
+      <c r="J19" s="1">
+        <v>475</v>
+      </c>
+      <c r="K19" s="1">
+        <v>200</v>
+      </c>
+      <c r="L19" s="9">
+        <v>425</v>
+      </c>
+      <c r="M19" s="1">
+        <v>275</v>
+      </c>
+      <c r="O19" s="9">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="P19" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>800</v>
+      </c>
+      <c r="S19" s="1">
+        <v>95</v>
+      </c>
+      <c r="T19" s="1">
+        <v>110</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" ref="D20:D44" si="3">E20/10</f>
+        <v>25</v>
+      </c>
+      <c r="E20" s="1">
+        <v>250</v>
+      </c>
+      <c r="F20" s="1">
+        <v>380</v>
+      </c>
+      <c r="G20" s="1">
+        <v>380</v>
+      </c>
+      <c r="H20" s="1">
+        <v>220</v>
+      </c>
+      <c r="I20" s="1">
+        <v>220</v>
+      </c>
+      <c r="J20" s="1">
+        <v>475</v>
+      </c>
+      <c r="K20" s="1">
+        <v>200</v>
+      </c>
+      <c r="L20" s="9">
+        <v>425</v>
+      </c>
+      <c r="M20" s="1">
+        <v>275</v>
+      </c>
+      <c r="O20" s="1">
+        <v>48</v>
+      </c>
+      <c r="P20" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>800</v>
+      </c>
+      <c r="S20" s="1">
+        <v>95</v>
+      </c>
+      <c r="T20" s="1">
+        <v>110</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E21" s="1">
+        <v>250</v>
+      </c>
+      <c r="F21" s="1">
+        <v>380</v>
+      </c>
+      <c r="G21" s="1">
+        <v>380</v>
+      </c>
+      <c r="H21" s="1">
+        <v>270</v>
+      </c>
+      <c r="I21" s="1">
+        <v>270</v>
+      </c>
+      <c r="J21" s="1">
+        <v>550</v>
+      </c>
+      <c r="K21" s="1">
+        <v>200</v>
+      </c>
+      <c r="L21" s="1">
+        <v>500</v>
+      </c>
+      <c r="M21" s="1">
+        <v>90</v>
+      </c>
+      <c r="O21" s="1">
         <v>21</v>
       </c>
-      <c r="D13" s="1">
-        <v>85</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F13" s="1">
-        <v>650</v>
-      </c>
-      <c r="G13" s="1">
-        <v>621</v>
-      </c>
-      <c r="H13" s="1">
-        <v>410</v>
-      </c>
-      <c r="I13" s="1">
-        <v>410</v>
-      </c>
-      <c r="J13" s="1">
-        <v>650</v>
-      </c>
-      <c r="K13" s="1">
+      <c r="P21" s="1">
+        <v>18</v>
+      </c>
+      <c r="R21" s="1">
+        <v>135</v>
+      </c>
+      <c r="T21" s="1">
+        <v>110</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E22" s="1">
+        <v>250</v>
+      </c>
+      <c r="F22" s="1">
+        <v>380</v>
+      </c>
+      <c r="G22" s="1">
+        <v>380</v>
+      </c>
+      <c r="H22" s="1">
+        <v>270</v>
+      </c>
+      <c r="I22" s="1">
+        <v>270</v>
+      </c>
+      <c r="J22" s="1">
+        <v>550</v>
+      </c>
+      <c r="K22" s="1">
+        <v>200</v>
+      </c>
+      <c r="L22" s="1">
+        <v>500</v>
+      </c>
+      <c r="M22" s="1">
+        <v>90</v>
+      </c>
+      <c r="O22" s="1">
+        <v>31</v>
+      </c>
+      <c r="P22" s="1">
+        <v>22</v>
+      </c>
+      <c r="R22" s="1">
+        <v>135</v>
+      </c>
+      <c r="T22" s="1">
+        <v>110</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E23" s="1">
+        <v>250</v>
+      </c>
+      <c r="F23" s="1">
+        <v>380</v>
+      </c>
+      <c r="G23" s="1">
+        <v>380</v>
+      </c>
+      <c r="H23" s="1">
+        <v>270</v>
+      </c>
+      <c r="I23" s="1">
+        <v>270</v>
+      </c>
+      <c r="J23" s="1">
+        <v>550</v>
+      </c>
+      <c r="K23" s="1">
+        <v>200</v>
+      </c>
+      <c r="L23" s="1">
+        <v>500</v>
+      </c>
+      <c r="M23" s="1">
+        <v>90</v>
+      </c>
+      <c r="O23" s="1">
+        <v>40</v>
+      </c>
+      <c r="P23" s="1">
+        <v>25</v>
+      </c>
+      <c r="R23" s="1">
+        <v>135</v>
+      </c>
+      <c r="T23" s="1">
+        <v>110</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E24" s="1">
+        <v>250</v>
+      </c>
+      <c r="F24" s="1">
+        <v>380</v>
+      </c>
+      <c r="G24" s="1">
+        <v>380</v>
+      </c>
+      <c r="H24" s="1">
+        <v>270</v>
+      </c>
+      <c r="I24" s="1">
+        <v>270</v>
+      </c>
+      <c r="J24" s="1">
+        <v>550</v>
+      </c>
+      <c r="K24" s="1">
+        <v>200</v>
+      </c>
+      <c r="L24" s="1">
+        <v>500</v>
+      </c>
+      <c r="M24" s="1">
+        <v>90</v>
+      </c>
+      <c r="O24" s="1">
+        <v>29</v>
+      </c>
+      <c r="P24" s="1">
+        <v>20</v>
+      </c>
+      <c r="R24" s="1">
+        <v>135</v>
+      </c>
+      <c r="T24" s="1">
+        <v>110</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E25" s="1">
+        <v>250</v>
+      </c>
+      <c r="F25" s="1">
+        <v>380</v>
+      </c>
+      <c r="G25" s="1">
+        <v>380</v>
+      </c>
+      <c r="H25" s="1">
+        <v>270</v>
+      </c>
+      <c r="I25" s="1">
+        <v>270</v>
+      </c>
+      <c r="J25" s="1">
+        <v>550</v>
+      </c>
+      <c r="K25" s="1">
+        <v>200</v>
+      </c>
+      <c r="L25" s="1">
+        <v>500</v>
+      </c>
+      <c r="M25" s="1">
+        <v>90</v>
+      </c>
+      <c r="O25" s="1">
+        <v>45</v>
+      </c>
+      <c r="P25" s="1">
+        <v>25</v>
+      </c>
+      <c r="R25" s="1">
+        <v>135</v>
+      </c>
+      <c r="T25" s="1">
+        <v>110</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E26" s="1">
+        <v>250</v>
+      </c>
+      <c r="F26" s="1">
+        <v>380</v>
+      </c>
+      <c r="G26" s="1">
+        <v>380</v>
+      </c>
+      <c r="H26" s="1">
+        <v>270</v>
+      </c>
+      <c r="I26" s="1">
+        <v>270</v>
+      </c>
+      <c r="J26" s="1">
+        <v>550</v>
+      </c>
+      <c r="K26" s="1">
+        <v>200</v>
+      </c>
+      <c r="L26" s="1">
+        <v>500</v>
+      </c>
+      <c r="M26" s="1">
+        <v>90</v>
+      </c>
+      <c r="O26" s="1">
+        <v>65</v>
+      </c>
+      <c r="P26" s="1">
+        <v>30</v>
+      </c>
+      <c r="R26" s="1">
+        <v>135</v>
+      </c>
+      <c r="T26" s="1">
+        <v>110</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E27" s="1">
+        <v>350</v>
+      </c>
+      <c r="F27" s="1">
+        <v>380</v>
+      </c>
+      <c r="G27" s="1">
+        <v>380</v>
+      </c>
+      <c r="H27" s="1">
+        <v>270</v>
+      </c>
+      <c r="I27" s="1">
+        <v>270</v>
+      </c>
+      <c r="J27" s="1">
+        <v>550</v>
+      </c>
+      <c r="K27" s="1">
+        <v>200</v>
+      </c>
+      <c r="L27" s="1">
+        <v>500</v>
+      </c>
+      <c r="M27" s="1">
+        <v>90</v>
+      </c>
+      <c r="O27" s="1">
+        <v>21</v>
+      </c>
+      <c r="P27" s="1">
+        <v>18</v>
+      </c>
+      <c r="R27" s="1">
+        <v>135</v>
+      </c>
+      <c r="T27" s="1">
+        <v>110</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E28" s="1">
+        <v>350</v>
+      </c>
+      <c r="F28" s="1">
+        <v>380</v>
+      </c>
+      <c r="G28" s="1">
+        <v>380</v>
+      </c>
+      <c r="H28" s="1">
+        <v>270</v>
+      </c>
+      <c r="I28" s="1">
+        <v>270</v>
+      </c>
+      <c r="J28" s="1">
+        <v>550</v>
+      </c>
+      <c r="K28" s="1">
+        <v>200</v>
+      </c>
+      <c r="L28" s="1">
+        <v>500</v>
+      </c>
+      <c r="M28" s="1">
+        <v>90</v>
+      </c>
+      <c r="O28" s="1">
+        <v>31</v>
+      </c>
+      <c r="P28" s="1">
+        <v>22</v>
+      </c>
+      <c r="R28" s="1">
+        <v>135</v>
+      </c>
+      <c r="T28" s="1">
+        <v>110</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E29" s="1">
+        <v>350</v>
+      </c>
+      <c r="F29" s="1">
+        <v>380</v>
+      </c>
+      <c r="G29" s="1">
+        <v>380</v>
+      </c>
+      <c r="H29" s="1">
+        <v>270</v>
+      </c>
+      <c r="I29" s="1">
+        <v>270</v>
+      </c>
+      <c r="J29" s="1">
+        <v>550</v>
+      </c>
+      <c r="K29" s="1">
+        <v>200</v>
+      </c>
+      <c r="L29" s="1">
+        <v>500</v>
+      </c>
+      <c r="M29" s="1">
+        <v>90</v>
+      </c>
+      <c r="O29" s="1">
+        <v>40</v>
+      </c>
+      <c r="P29" s="1">
+        <v>25</v>
+      </c>
+      <c r="R29" s="1">
+        <v>135</v>
+      </c>
+      <c r="T29" s="1">
+        <v>110</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E30" s="1">
+        <v>350</v>
+      </c>
+      <c r="F30" s="1">
+        <v>380</v>
+      </c>
+      <c r="G30" s="1">
+        <v>380</v>
+      </c>
+      <c r="H30" s="1">
+        <v>270</v>
+      </c>
+      <c r="I30" s="1">
+        <v>270</v>
+      </c>
+      <c r="J30" s="1">
+        <v>550</v>
+      </c>
+      <c r="K30" s="1">
+        <v>200</v>
+      </c>
+      <c r="L30" s="1">
+        <v>500</v>
+      </c>
+      <c r="M30" s="1">
+        <v>90</v>
+      </c>
+      <c r="O30" s="1">
+        <v>29</v>
+      </c>
+      <c r="P30" s="1">
+        <v>20</v>
+      </c>
+      <c r="R30" s="1">
+        <v>135</v>
+      </c>
+      <c r="T30" s="1">
+        <v>110</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E31" s="1">
+        <v>350</v>
+      </c>
+      <c r="F31" s="1">
+        <v>380</v>
+      </c>
+      <c r="G31" s="1">
+        <v>380</v>
+      </c>
+      <c r="H31" s="1">
+        <v>270</v>
+      </c>
+      <c r="I31" s="1">
+        <v>270</v>
+      </c>
+      <c r="J31" s="1">
+        <v>550</v>
+      </c>
+      <c r="K31" s="1">
+        <v>200</v>
+      </c>
+      <c r="L31" s="1">
+        <v>500</v>
+      </c>
+      <c r="M31" s="1">
+        <v>90</v>
+      </c>
+      <c r="O31" s="1">
+        <v>45</v>
+      </c>
+      <c r="P31" s="1">
+        <v>25</v>
+      </c>
+      <c r="R31" s="1">
+        <v>135</v>
+      </c>
+      <c r="T31" s="1">
+        <v>110</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E32" s="1">
+        <v>350</v>
+      </c>
+      <c r="F32" s="1">
+        <v>380</v>
+      </c>
+      <c r="G32" s="1">
+        <v>380</v>
+      </c>
+      <c r="H32" s="1">
+        <v>270</v>
+      </c>
+      <c r="I32" s="1">
+        <v>270</v>
+      </c>
+      <c r="J32" s="1">
+        <v>550</v>
+      </c>
+      <c r="K32" s="1">
+        <v>200</v>
+      </c>
+      <c r="L32" s="1">
+        <v>500</v>
+      </c>
+      <c r="M32" s="1">
+        <v>90</v>
+      </c>
+      <c r="O32" s="1">
+        <v>65</v>
+      </c>
+      <c r="P32" s="1">
+        <v>30</v>
+      </c>
+      <c r="R32" s="1">
+        <v>135</v>
+      </c>
+      <c r="T32" s="1">
+        <v>110</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E33" s="1">
+        <v>350</v>
+      </c>
+      <c r="F33" s="1">
+        <v>380</v>
+      </c>
+      <c r="G33" s="1">
+        <v>380</v>
+      </c>
+      <c r="H33" s="1">
+        <v>270</v>
+      </c>
+      <c r="I33" s="1">
+        <v>270</v>
+      </c>
+      <c r="J33" s="1">
+        <v>550</v>
+      </c>
+      <c r="K33" s="1">
+        <v>200</v>
+      </c>
+      <c r="L33" s="1">
+        <v>500</v>
+      </c>
+      <c r="M33" s="1">
+        <v>90</v>
+      </c>
+      <c r="O33" s="1">
+        <v>54</v>
+      </c>
+      <c r="P33" s="1">
+        <v>25</v>
+      </c>
+      <c r="R33" s="1">
+        <v>135</v>
+      </c>
+      <c r="T33" s="1">
+        <v>110</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E34" s="1">
+        <v>350</v>
+      </c>
+      <c r="F34" s="1">
+        <v>380</v>
+      </c>
+      <c r="G34" s="1">
+        <v>380</v>
+      </c>
+      <c r="H34" s="1">
+        <v>270</v>
+      </c>
+      <c r="I34" s="1">
+        <v>270</v>
+      </c>
+      <c r="J34" s="1">
+        <v>550</v>
+      </c>
+      <c r="K34" s="1">
+        <v>200</v>
+      </c>
+      <c r="L34" s="1">
+        <v>500</v>
+      </c>
+      <c r="M34" s="1">
+        <v>90</v>
+      </c>
+      <c r="O34" s="1">
+        <v>77</v>
+      </c>
+      <c r="P34" s="1">
+        <v>30</v>
+      </c>
+      <c r="R34" s="1">
+        <v>135</v>
+      </c>
+      <c r="T34" s="1">
+        <v>110</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E35" s="1">
+        <v>350</v>
+      </c>
+      <c r="F35" s="1">
+        <v>380</v>
+      </c>
+      <c r="G35" s="1">
+        <v>380</v>
+      </c>
+      <c r="H35" s="1">
+        <v>270</v>
+      </c>
+      <c r="I35" s="1">
+        <v>270</v>
+      </c>
+      <c r="J35" s="1">
+        <v>550</v>
+      </c>
+      <c r="K35" s="1">
+        <v>200</v>
+      </c>
+      <c r="L35" s="1">
+        <v>500</v>
+      </c>
+      <c r="M35" s="1">
+        <v>90</v>
+      </c>
+      <c r="O35" s="1">
+        <v>105</v>
+      </c>
+      <c r="P35" s="1">
+        <v>35</v>
+      </c>
+      <c r="R35" s="1">
+        <v>135</v>
+      </c>
+      <c r="T35" s="1">
+        <v>110</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E36" s="1">
         <v>400</v>
       </c>
-      <c r="L13" s="1">
-        <v>700</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="F36" s="1">
+        <v>380</v>
+      </c>
+      <c r="G36" s="1">
+        <v>380</v>
+      </c>
+      <c r="H36" s="1">
+        <v>270</v>
+      </c>
+      <c r="I36" s="1">
+        <v>270</v>
+      </c>
+      <c r="J36" s="1">
+        <v>550</v>
+      </c>
+      <c r="K36" s="1">
+        <v>200</v>
+      </c>
+      <c r="L36" s="1">
+        <v>500</v>
+      </c>
+      <c r="M36" s="1">
+        <v>90</v>
+      </c>
+      <c r="O36" s="1">
+        <v>21</v>
+      </c>
+      <c r="P36" s="1">
+        <v>18</v>
+      </c>
+      <c r="R36" s="1">
+        <v>135</v>
+      </c>
+      <c r="T36" s="1">
+        <v>110</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E37" s="1">
+        <v>400</v>
+      </c>
+      <c r="F37" s="1">
+        <v>380</v>
+      </c>
+      <c r="G37" s="1">
+        <v>380</v>
+      </c>
+      <c r="H37" s="1">
+        <v>270</v>
+      </c>
+      <c r="I37" s="1">
+        <v>270</v>
+      </c>
+      <c r="J37" s="1">
+        <v>550</v>
+      </c>
+      <c r="K37" s="1">
+        <v>200</v>
+      </c>
+      <c r="L37" s="1">
+        <v>500</v>
+      </c>
+      <c r="M37" s="1">
+        <v>90</v>
+      </c>
+      <c r="O37" s="1">
+        <v>31</v>
+      </c>
+      <c r="P37" s="1">
+        <v>22</v>
+      </c>
+      <c r="R37" s="1">
+        <v>135</v>
+      </c>
+      <c r="T37" s="1">
+        <v>110</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E38" s="1">
+        <v>400</v>
+      </c>
+      <c r="F38" s="1">
+        <v>380</v>
+      </c>
+      <c r="G38" s="1">
+        <v>380</v>
+      </c>
+      <c r="H38" s="1">
+        <v>270</v>
+      </c>
+      <c r="I38" s="1">
+        <v>270</v>
+      </c>
+      <c r="J38" s="1">
+        <v>550</v>
+      </c>
+      <c r="K38" s="1">
+        <v>200</v>
+      </c>
+      <c r="L38" s="1">
+        <v>500</v>
+      </c>
+      <c r="M38" s="1">
+        <v>90</v>
+      </c>
+      <c r="O38" s="1">
+        <v>40</v>
+      </c>
+      <c r="P38" s="1">
+        <v>25</v>
+      </c>
+      <c r="R38" s="1">
+        <v>135</v>
+      </c>
+      <c r="T38" s="1">
+        <v>110</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E39" s="1">
+        <v>400</v>
+      </c>
+      <c r="F39" s="1">
+        <v>380</v>
+      </c>
+      <c r="G39" s="1">
+        <v>380</v>
+      </c>
+      <c r="H39" s="1">
+        <v>270</v>
+      </c>
+      <c r="I39" s="1">
+        <v>270</v>
+      </c>
+      <c r="J39" s="1">
+        <v>550</v>
+      </c>
+      <c r="K39" s="1">
+        <v>200</v>
+      </c>
+      <c r="L39" s="1">
+        <v>500</v>
+      </c>
+      <c r="M39" s="1">
+        <v>90</v>
+      </c>
+      <c r="O39" s="1">
+        <v>29</v>
+      </c>
+      <c r="P39" s="1">
+        <v>20</v>
+      </c>
+      <c r="R39" s="1">
+        <v>135</v>
+      </c>
+      <c r="T39" s="1">
+        <v>110</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E40" s="1">
+        <v>400</v>
+      </c>
+      <c r="F40" s="1">
+        <v>380</v>
+      </c>
+      <c r="G40" s="1">
+        <v>380</v>
+      </c>
+      <c r="H40" s="1">
+        <v>270</v>
+      </c>
+      <c r="I40" s="1">
+        <v>270</v>
+      </c>
+      <c r="J40" s="1">
+        <v>550</v>
+      </c>
+      <c r="K40" s="1">
+        <v>200</v>
+      </c>
+      <c r="L40" s="1">
+        <v>500</v>
+      </c>
+      <c r="M40" s="1">
+        <v>90</v>
+      </c>
+      <c r="O40" s="1">
+        <v>45</v>
+      </c>
+      <c r="P40" s="1">
+        <v>25</v>
+      </c>
+      <c r="R40" s="1">
+        <v>135</v>
+      </c>
+      <c r="T40" s="1">
+        <v>110</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E41" s="1">
+        <v>400</v>
+      </c>
+      <c r="F41" s="1">
+        <v>380</v>
+      </c>
+      <c r="G41" s="1">
+        <v>380</v>
+      </c>
+      <c r="H41" s="1">
+        <v>270</v>
+      </c>
+      <c r="I41" s="1">
+        <v>270</v>
+      </c>
+      <c r="J41" s="1">
+        <v>550</v>
+      </c>
+      <c r="K41" s="1">
+        <v>200</v>
+      </c>
+      <c r="L41" s="1">
+        <v>500</v>
+      </c>
+      <c r="M41" s="1">
+        <v>90</v>
+      </c>
+      <c r="O41" s="1">
+        <v>65</v>
+      </c>
+      <c r="P41" s="1">
+        <v>30</v>
+      </c>
+      <c r="R41" s="1">
+        <v>135</v>
+      </c>
+      <c r="T41" s="1">
+        <v>110</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E42" s="1">
+        <v>400</v>
+      </c>
+      <c r="F42" s="1">
+        <v>380</v>
+      </c>
+      <c r="G42" s="1">
+        <v>380</v>
+      </c>
+      <c r="H42" s="1">
+        <v>270</v>
+      </c>
+      <c r="I42" s="1">
+        <v>270</v>
+      </c>
+      <c r="J42" s="1">
+        <v>550</v>
+      </c>
+      <c r="K42" s="1">
+        <v>200</v>
+      </c>
+      <c r="L42" s="1">
+        <v>500</v>
+      </c>
+      <c r="M42" s="1">
+        <v>90</v>
+      </c>
+      <c r="O42" s="1">
+        <v>54</v>
+      </c>
+      <c r="P42" s="1">
+        <v>25</v>
+      </c>
+      <c r="R42" s="1">
+        <v>135</v>
+      </c>
+      <c r="T42" s="1">
+        <v>110</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E43" s="1">
+        <v>400</v>
+      </c>
+      <c r="F43" s="1">
+        <v>380</v>
+      </c>
+      <c r="G43" s="1">
+        <v>380</v>
+      </c>
+      <c r="H43" s="1">
+        <v>270</v>
+      </c>
+      <c r="I43" s="1">
+        <v>270</v>
+      </c>
+      <c r="J43" s="1">
+        <v>550</v>
+      </c>
+      <c r="K43" s="1">
+        <v>200</v>
+      </c>
+      <c r="L43" s="1">
+        <v>500</v>
+      </c>
+      <c r="M43" s="1">
+        <v>90</v>
+      </c>
+      <c r="O43" s="1">
+        <v>77</v>
+      </c>
+      <c r="P43" s="1">
+        <v>30</v>
+      </c>
+      <c r="R43" s="1">
+        <v>135</v>
+      </c>
+      <c r="T43" s="1">
+        <v>110</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="E44" s="1">
+        <v>400</v>
+      </c>
+      <c r="F44" s="1">
+        <v>380</v>
+      </c>
+      <c r="G44" s="1">
+        <v>380</v>
+      </c>
+      <c r="H44" s="1">
+        <v>270</v>
+      </c>
+      <c r="I44" s="1">
+        <v>270</v>
+      </c>
+      <c r="J44" s="1">
+        <v>550</v>
+      </c>
+      <c r="K44" s="1">
+        <v>200</v>
+      </c>
+      <c r="L44" s="1">
+        <v>500</v>
+      </c>
+      <c r="M44" s="1">
+        <v>90</v>
+      </c>
+      <c r="O44" s="1">
+        <v>105</v>
+      </c>
+      <c r="P44" s="1">
+        <v>35</v>
+      </c>
+      <c r="R44" s="1">
+        <v>135</v>
+      </c>
+      <c r="T44" s="1">
+        <v>110</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="1">
+        <v>50</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" ref="E45:E50" si="4">D45*10</f>
+        <v>500</v>
+      </c>
+      <c r="F45" s="1">
+        <v>446</v>
+      </c>
+      <c r="G45" s="1">
+        <v>446</v>
+      </c>
+      <c r="H45" s="1">
+        <v>320</v>
+      </c>
+      <c r="I45" s="1">
+        <v>320</v>
+      </c>
+      <c r="J45" s="1">
+        <v>550</v>
+      </c>
+      <c r="K45" s="1">
+        <v>200</v>
+      </c>
+      <c r="M45" s="1">
         <v>350</v>
       </c>
-      <c r="N13" s="1">
-        <v>200</v>
-      </c>
-      <c r="O13" s="1">
-        <v>113</v>
-      </c>
-      <c r="P13" s="1">
-        <v>36</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R13" s="1">
-        <v>704</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14">
-        <v>85</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="F14">
-        <v>650</v>
-      </c>
-      <c r="G14">
-        <v>621</v>
-      </c>
-      <c r="H14">
-        <v>410</v>
-      </c>
-      <c r="I14">
-        <v>410</v>
-      </c>
-      <c r="J14">
-        <v>650</v>
-      </c>
-      <c r="K14">
-        <v>400</v>
-      </c>
-      <c r="L14">
-        <v>700</v>
-      </c>
-      <c r="M14">
+      <c r="O45" s="1">
+        <v>29</v>
+      </c>
+      <c r="P45" s="1">
+        <v>20</v>
+      </c>
+      <c r="R45" s="1">
+        <v>180</v>
+      </c>
+      <c r="S45" s="1">
+        <v>125</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="1">
+        <v>50</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="F46" s="1">
+        <v>446</v>
+      </c>
+      <c r="G46" s="1">
+        <v>446</v>
+      </c>
+      <c r="H46" s="1">
+        <v>320</v>
+      </c>
+      <c r="I46" s="1">
+        <v>320</v>
+      </c>
+      <c r="J46" s="1">
+        <v>550</v>
+      </c>
+      <c r="K46" s="1">
+        <v>200</v>
+      </c>
+      <c r="M46" s="1">
         <v>350</v>
       </c>
-      <c r="N14">
-        <v>200</v>
-      </c>
-      <c r="O14" s="1">
-        <v>154</v>
-      </c>
-      <c r="P14">
-        <v>40</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>1174</v>
-      </c>
-      <c r="R14" s="1">
-        <v>704</v>
-      </c>
-      <c r="T14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15">
-        <v>198</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" ref="E15" si="2">D15*10</f>
-        <v>1980</v>
-      </c>
-      <c r="F15">
-        <v>790</v>
-      </c>
-      <c r="G15">
-        <v>740</v>
-      </c>
-      <c r="H15">
-        <v>560</v>
-      </c>
-      <c r="I15">
-        <v>510</v>
-      </c>
-      <c r="J15">
-        <v>1050</v>
-      </c>
-      <c r="K15">
-        <v>200</v>
-      </c>
-      <c r="L15">
-        <v>600</v>
-      </c>
-      <c r="M15">
-        <v>450</v>
-      </c>
-      <c r="O15">
-        <v>292</v>
-      </c>
-      <c r="P15">
+      <c r="O46" s="1">
         <v>45</v>
       </c>
-      <c r="S15" s="1">
-        <v>130</v>
-      </c>
-      <c r="T15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16">
-        <v>300</v>
-      </c>
-      <c r="E16" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F16">
-        <v>970</v>
-      </c>
-      <c r="G16">
-        <v>970</v>
-      </c>
-      <c r="H16">
-        <v>720</v>
-      </c>
-      <c r="I16" s="1">
-        <v>720</v>
-      </c>
-      <c r="J16">
-        <v>900</v>
-      </c>
-      <c r="K16">
-        <v>250</v>
-      </c>
-      <c r="L16">
-        <v>650</v>
-      </c>
-      <c r="M16">
-        <v>610</v>
-      </c>
-      <c r="O16">
-        <v>341</v>
-      </c>
-      <c r="P16">
-        <v>48</v>
-      </c>
-      <c r="S16" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="1">
-        <v>100</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" ref="E17:E24" si="3">D17*10</f>
-        <v>1000</v>
-      </c>
-      <c r="F17" s="1">
-        <v>650</v>
-      </c>
-      <c r="G17" s="1">
-        <v>600</v>
-      </c>
-      <c r="H17" s="1">
-        <v>460</v>
-      </c>
-      <c r="I17" s="1">
-        <v>410</v>
-      </c>
-      <c r="J17" s="1">
-        <v>800</v>
-      </c>
-      <c r="K17" s="1">
-        <v>150</v>
-      </c>
-      <c r="L17" s="1">
-        <v>450</v>
-      </c>
-      <c r="M17" s="1">
+      <c r="P46" s="1">
+        <v>25</v>
+      </c>
+      <c r="R46" s="1">
+        <v>180</v>
+      </c>
+      <c r="S46" s="1">
+        <v>125</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="1">
+        <v>50</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="F47" s="1">
+        <v>446</v>
+      </c>
+      <c r="G47" s="1">
+        <v>446</v>
+      </c>
+      <c r="H47" s="1">
+        <v>320</v>
+      </c>
+      <c r="I47" s="1">
+        <v>320</v>
+      </c>
+      <c r="J47" s="1">
+        <v>550</v>
+      </c>
+      <c r="K47" s="1">
+        <v>200</v>
+      </c>
+      <c r="M47" s="1">
         <v>350</v>
       </c>
-      <c r="N17" s="1">
-        <v>150</v>
-      </c>
-      <c r="O17" s="1">
-        <v>202</v>
-      </c>
-      <c r="P17" s="1">
-        <v>40</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="1">
-        <v>130</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="3"/>
-        <v>1300</v>
-      </c>
-      <c r="H18" s="1">
-        <v>530</v>
-      </c>
-      <c r="I18" s="1">
-        <v>530</v>
-      </c>
-      <c r="K18" s="1">
-        <v>150</v>
-      </c>
-      <c r="M18" s="1">
-        <v>400</v>
-      </c>
-      <c r="N18" s="1">
-        <v>150</v>
-      </c>
-      <c r="O18" s="1">
-        <v>250</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="O47" s="1">
+        <v>65</v>
+      </c>
+      <c r="P47" s="1">
+        <v>30</v>
+      </c>
+      <c r="R47" s="1">
         <v>180</v>
       </c>
-      <c r="E19" s="1">
-        <f t="shared" si="3"/>
-        <v>1800</v>
-      </c>
-      <c r="H19" s="1">
-        <v>570</v>
-      </c>
-      <c r="I19" s="1">
-        <v>570</v>
-      </c>
-      <c r="K19" s="1">
-        <v>150</v>
-      </c>
-      <c r="M19" s="1">
-        <v>450</v>
-      </c>
-      <c r="N19" s="1">
-        <v>150</v>
-      </c>
-      <c r="O19" s="1">
-        <v>300</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="1">
-        <v>220</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="3"/>
-        <v>2200</v>
-      </c>
-      <c r="H20" s="1">
-        <v>650</v>
-      </c>
-      <c r="I20" s="1">
-        <v>650</v>
-      </c>
-      <c r="K20" s="1">
-        <v>150</v>
-      </c>
-      <c r="M20" s="1">
+      <c r="S47" s="1">
+        <v>125</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="1">
+        <v>50</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="N20" s="1">
-        <v>150</v>
-      </c>
-      <c r="O20" s="1">
+      <c r="F48" s="1">
+        <v>446</v>
+      </c>
+      <c r="G48" s="1">
+        <v>446</v>
+      </c>
+      <c r="H48" s="1">
+        <v>320</v>
+      </c>
+      <c r="I48" s="1">
+        <v>320</v>
+      </c>
+      <c r="J48" s="1">
+        <v>550</v>
+      </c>
+      <c r="K48" s="1">
+        <v>200</v>
+      </c>
+      <c r="M48" s="1">
         <v>350</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="O48" s="1">
+        <v>54</v>
+      </c>
+      <c r="P48" s="1">
+        <v>25</v>
+      </c>
+      <c r="R48" s="1">
+        <v>180</v>
+      </c>
+      <c r="S48" s="1">
+        <v>125</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="1">
+        <v>50</v>
+      </c>
+      <c r="E49" s="1">
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="E21" s="1">
-        <f t="shared" si="3"/>
-        <v>5000</v>
-      </c>
-      <c r="H21" s="1">
-        <v>830</v>
-      </c>
-      <c r="I21" s="1">
-        <v>830</v>
-      </c>
-      <c r="K21" s="1">
-        <v>150</v>
-      </c>
-      <c r="M21" s="1">
-        <v>700</v>
-      </c>
-      <c r="N21" s="1">
-        <v>150</v>
-      </c>
-      <c r="O21" s="1">
-        <v>600</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="1">
-        <v>85</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="3"/>
-        <v>850</v>
-      </c>
-      <c r="H22" s="1">
-        <v>470</v>
-      </c>
-      <c r="I22" s="1">
-        <v>420</v>
-      </c>
-      <c r="K22" s="1">
-        <v>150</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="F49" s="1">
+        <v>446</v>
+      </c>
+      <c r="G49" s="1">
+        <v>446</v>
+      </c>
+      <c r="H49" s="1">
         <v>320</v>
       </c>
-      <c r="N22" s="1">
-        <v>150</v>
-      </c>
-      <c r="O22" s="1">
-        <v>23</v>
-      </c>
-      <c r="P22" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="1">
-        <v>450</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" si="3"/>
-        <v>4500</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1300</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1300</v>
-      </c>
-      <c r="H23" s="1">
-        <v>920</v>
-      </c>
-      <c r="I23" s="1">
-        <v>920</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1625</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="I49" s="1">
+        <v>320</v>
+      </c>
+      <c r="J49" s="1">
+        <v>550</v>
+      </c>
+      <c r="K49" s="1">
+        <v>200</v>
+      </c>
+      <c r="M49" s="1">
         <v>350</v>
       </c>
-      <c r="L23" s="1">
-        <v>800</v>
-      </c>
-      <c r="M23" s="1">
-        <v>825</v>
-      </c>
-      <c r="O23" s="1">
-        <v>390</v>
-      </c>
-      <c r="P23" s="1">
+      <c r="O49" s="1">
+        <v>77</v>
+      </c>
+      <c r="P49" s="1">
+        <v>30</v>
+      </c>
+      <c r="R49" s="1">
+        <v>180</v>
+      </c>
+      <c r="S49" s="1">
+        <v>125</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="1">
         <v>50</v>
       </c>
-      <c r="Q23" s="1">
-        <v>7500</v>
-      </c>
-      <c r="R23" s="1">
-        <v>5000</v>
-      </c>
-      <c r="S23" s="1">
-        <v>220</v>
-      </c>
-      <c r="T23" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E50" s="1">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="F50" s="1">
+        <v>446</v>
+      </c>
+      <c r="G50" s="1">
+        <v>446</v>
+      </c>
+      <c r="H50" s="1">
+        <v>320</v>
+      </c>
+      <c r="I50" s="1">
+        <v>320</v>
+      </c>
+      <c r="J50" s="1">
+        <v>550</v>
+      </c>
+      <c r="K50" s="1">
+        <v>200</v>
+      </c>
+      <c r="M50" s="1">
+        <v>350</v>
+      </c>
+      <c r="O50" s="1">
         <v>105</v>
       </c>
-      <c r="D24" s="1">
-        <v>450</v>
-      </c>
-      <c r="E24" s="1">
-        <f t="shared" si="3"/>
-        <v>4500</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1300</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1300</v>
-      </c>
-      <c r="H24" s="1">
-        <v>920</v>
-      </c>
-      <c r="I24" s="1">
-        <v>920</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1625</v>
-      </c>
-      <c r="K24" s="1">
-        <v>350</v>
-      </c>
-      <c r="L24" s="1">
-        <v>800</v>
-      </c>
-      <c r="M24" s="1">
-        <v>825</v>
-      </c>
-      <c r="O24" s="1">
-        <v>1390</v>
-      </c>
-      <c r="P24" s="1">
-        <v>80</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>7500</v>
-      </c>
-      <c r="R24" s="1">
-        <v>5000</v>
-      </c>
-      <c r="S24" s="1">
-        <v>220</v>
-      </c>
-      <c r="T24" s="1">
-        <v>150</v>
+      <c r="P50" s="1">
+        <v>35</v>
+      </c>
+      <c r="R50" s="1">
+        <v>180</v>
+      </c>
+      <c r="S50" s="1">
+        <v>125</v>
+      </c>
+      <c r="U50" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T15">
-    <sortCondition ref="A2:A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T9">
+    <sortCondition ref="A2:A9"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F5110E-6DD2-4A5B-A462-B92C9B16E192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FFB070-5BF4-44B2-9562-09B03B9B5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20052" yWindow="-288" windowWidth="20376" windowHeight="12096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="147">
   <si>
     <t>OEM</t>
   </si>
@@ -433,13 +433,55 @@
   </si>
   <si>
     <t>270 S 400-170-35</t>
+  </si>
+  <si>
+    <t>Locating Hole Diameter (mm)</t>
+  </si>
+  <si>
+    <t>UBE</t>
+  </si>
+  <si>
+    <t>Synthetic Spec</t>
+  </si>
+  <si>
+    <t>UBE-65T</t>
+  </si>
+  <si>
+    <t>Synthetic realistic engineering estimate</t>
+  </si>
+  <si>
+    <t>UBE-85T</t>
+  </si>
+  <si>
+    <t>UBE-105T</t>
+  </si>
+  <si>
+    <t>UBE-130T</t>
+  </si>
+  <si>
+    <t>UBE-160T</t>
+  </si>
+  <si>
+    <t>UBE-220T</t>
+  </si>
+  <si>
+    <t>UBE-280T</t>
+  </si>
+  <si>
+    <t>UBE-350T</t>
+  </si>
+  <si>
+    <t>UBE-450T</t>
+  </si>
+  <si>
+    <t>UBE-550T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,6 +514,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -521,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -542,6 +591,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -864,10 +914,11 @@
     <col min="17" max="17" width="22.7109375" style="1" customWidth="1"/>
     <col min="18" max="18" width="19.28515625" style="1" customWidth="1"/>
     <col min="19" max="19" width="13.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -926,10 +977,13 @@
         <v>75</v>
       </c>
       <c r="T1" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="U1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -989,7 +1043,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1049,7 +1103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1109,7 +1163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1169,7 +1223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1229,7 +1283,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1289,7 +1343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1349,7 +1403,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>78</v>
       </c>
@@ -1403,7 +1457,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -1453,7 +1507,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
@@ -1507,7 +1561,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>85</v>
       </c>
@@ -1549,7 +1603,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>85</v>
       </c>
@@ -1591,7 +1645,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>85</v>
       </c>
@@ -1633,7 +1687,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>85</v>
       </c>
@@ -1675,7 +1729,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>85</v>
       </c>
@@ -3357,6 +3411,9 @@
       <c r="K45" s="1">
         <v>200</v>
       </c>
+      <c r="L45" s="1">
+        <v>500</v>
+      </c>
       <c r="M45" s="1">
         <v>350</v>
       </c>
@@ -3411,6 +3468,9 @@
       <c r="K46" s="1">
         <v>200</v>
       </c>
+      <c r="L46" s="1">
+        <v>500</v>
+      </c>
       <c r="M46" s="1">
         <v>350</v>
       </c>
@@ -3465,6 +3525,9 @@
       <c r="K47" s="1">
         <v>200</v>
       </c>
+      <c r="L47" s="1">
+        <v>500</v>
+      </c>
       <c r="M47" s="1">
         <v>350</v>
       </c>
@@ -3519,6 +3582,9 @@
       <c r="K48" s="1">
         <v>200</v>
       </c>
+      <c r="L48" s="1">
+        <v>500</v>
+      </c>
       <c r="M48" s="1">
         <v>350</v>
       </c>
@@ -3573,6 +3639,9 @@
       <c r="K49" s="1">
         <v>200</v>
       </c>
+      <c r="L49" s="1">
+        <v>500</v>
+      </c>
       <c r="M49" s="1">
         <v>350</v>
       </c>
@@ -3627,6 +3696,9 @@
       <c r="K50" s="1">
         <v>200</v>
       </c>
+      <c r="L50" s="1">
+        <v>500</v>
+      </c>
       <c r="M50" s="1">
         <v>350</v>
       </c>
@@ -3644,6 +3716,656 @@
       </c>
       <c r="U50" s="1" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="10">
+        <v>65</v>
+      </c>
+      <c r="E51" s="10">
+        <v>650</v>
+      </c>
+      <c r="F51" s="10">
+        <v>575</v>
+      </c>
+      <c r="G51" s="10">
+        <v>575</v>
+      </c>
+      <c r="H51" s="10">
+        <v>448</v>
+      </c>
+      <c r="I51" s="10">
+        <v>448</v>
+      </c>
+      <c r="J51" s="10">
+        <v>567</v>
+      </c>
+      <c r="K51" s="10">
+        <v>158</v>
+      </c>
+      <c r="L51" s="10">
+        <v>442</v>
+      </c>
+      <c r="M51" s="10">
+        <v>329</v>
+      </c>
+      <c r="N51" s="10">
+        <v>158</v>
+      </c>
+      <c r="O51" s="10">
+        <v>143</v>
+      </c>
+      <c r="P51" s="10">
+        <v>26</v>
+      </c>
+      <c r="Q51" s="10">
+        <v>780</v>
+      </c>
+      <c r="R51" s="10">
+        <v>455</v>
+      </c>
+      <c r="S51" s="10">
+        <v>150</v>
+      </c>
+      <c r="T51" s="10">
+        <v>100</v>
+      </c>
+      <c r="U51" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52" s="10">
+        <v>85</v>
+      </c>
+      <c r="E52" s="10">
+        <v>850</v>
+      </c>
+      <c r="F52" s="10">
+        <v>608</v>
+      </c>
+      <c r="G52" s="10">
+        <v>608</v>
+      </c>
+      <c r="H52" s="10">
+        <v>474</v>
+      </c>
+      <c r="I52" s="10">
+        <v>474</v>
+      </c>
+      <c r="J52" s="10">
+        <v>603</v>
+      </c>
+      <c r="K52" s="10">
+        <v>168</v>
+      </c>
+      <c r="L52" s="10">
+        <v>470</v>
+      </c>
+      <c r="M52" s="10">
+        <v>355</v>
+      </c>
+      <c r="N52" s="10">
+        <v>168</v>
+      </c>
+      <c r="O52" s="10">
+        <v>187</v>
+      </c>
+      <c r="P52" s="10">
+        <v>30</v>
+      </c>
+      <c r="Q52" s="10">
+        <v>1020</v>
+      </c>
+      <c r="R52" s="10">
+        <v>595</v>
+      </c>
+      <c r="S52" s="10">
+        <v>150</v>
+      </c>
+      <c r="T52" s="10">
+        <v>100</v>
+      </c>
+      <c r="U52" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" s="10">
+        <v>105</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1050</v>
+      </c>
+      <c r="F53" s="10">
+        <v>636</v>
+      </c>
+      <c r="G53" s="10">
+        <v>636</v>
+      </c>
+      <c r="H53" s="10">
+        <v>496</v>
+      </c>
+      <c r="I53" s="10">
+        <v>496</v>
+      </c>
+      <c r="J53" s="10">
+        <v>639</v>
+      </c>
+      <c r="K53" s="10">
+        <v>178</v>
+      </c>
+      <c r="L53" s="10">
+        <v>498</v>
+      </c>
+      <c r="M53" s="10">
+        <v>381</v>
+      </c>
+      <c r="N53" s="10">
+        <v>178</v>
+      </c>
+      <c r="O53" s="10">
+        <v>231</v>
+      </c>
+      <c r="P53" s="10">
+        <v>33</v>
+      </c>
+      <c r="Q53" s="10">
+        <v>1260</v>
+      </c>
+      <c r="R53" s="10">
+        <v>735</v>
+      </c>
+      <c r="S53" s="10">
+        <v>150</v>
+      </c>
+      <c r="T53" s="10">
+        <v>100</v>
+      </c>
+      <c r="U53" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="10">
+        <v>130</v>
+      </c>
+      <c r="E54" s="10">
+        <v>1300</v>
+      </c>
+      <c r="F54" s="10">
+        <v>669</v>
+      </c>
+      <c r="G54" s="10">
+        <v>669</v>
+      </c>
+      <c r="H54" s="10">
+        <v>521</v>
+      </c>
+      <c r="I54" s="10">
+        <v>521</v>
+      </c>
+      <c r="J54" s="10">
+        <v>684</v>
+      </c>
+      <c r="K54" s="10">
+        <v>191</v>
+      </c>
+      <c r="L54" s="10">
+        <v>533</v>
+      </c>
+      <c r="M54" s="10">
+        <v>413</v>
+      </c>
+      <c r="N54" s="10">
+        <v>191</v>
+      </c>
+      <c r="O54" s="10">
+        <v>286</v>
+      </c>
+      <c r="P54" s="10">
+        <v>37</v>
+      </c>
+      <c r="Q54" s="10">
+        <v>1560</v>
+      </c>
+      <c r="R54" s="10">
+        <v>910</v>
+      </c>
+      <c r="S54" s="10">
+        <v>150</v>
+      </c>
+      <c r="T54" s="10">
+        <v>100</v>
+      </c>
+      <c r="U54" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="10">
+        <v>160</v>
+      </c>
+      <c r="E55" s="10">
+        <v>1600</v>
+      </c>
+      <c r="F55" s="10">
+        <v>704</v>
+      </c>
+      <c r="G55" s="10">
+        <v>704</v>
+      </c>
+      <c r="H55" s="10">
+        <v>549</v>
+      </c>
+      <c r="I55" s="10">
+        <v>549</v>
+      </c>
+      <c r="J55" s="10">
+        <v>738</v>
+      </c>
+      <c r="K55" s="10">
+        <v>206</v>
+      </c>
+      <c r="L55" s="10">
+        <v>575</v>
+      </c>
+      <c r="M55" s="10">
+        <v>452</v>
+      </c>
+      <c r="N55" s="10">
+        <v>206</v>
+      </c>
+      <c r="O55" s="10">
+        <v>352</v>
+      </c>
+      <c r="P55" s="10">
+        <v>41</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>1920</v>
+      </c>
+      <c r="R55" s="10">
+        <v>1120</v>
+      </c>
+      <c r="S55" s="10">
+        <v>150</v>
+      </c>
+      <c r="T55" s="10">
+        <v>100</v>
+      </c>
+      <c r="U55" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" s="10">
+        <v>220</v>
+      </c>
+      <c r="E56" s="10">
+        <v>2200</v>
+      </c>
+      <c r="F56" s="10">
+        <v>765</v>
+      </c>
+      <c r="G56" s="10">
+        <v>765</v>
+      </c>
+      <c r="H56" s="10">
+        <v>596</v>
+      </c>
+      <c r="I56" s="10">
+        <v>596</v>
+      </c>
+      <c r="J56" s="10">
+        <v>846</v>
+      </c>
+      <c r="K56" s="10">
+        <v>236</v>
+      </c>
+      <c r="L56" s="10">
+        <v>659</v>
+      </c>
+      <c r="M56" s="10">
+        <v>530</v>
+      </c>
+      <c r="N56" s="10">
+        <v>236</v>
+      </c>
+      <c r="O56" s="10">
+        <v>484</v>
+      </c>
+      <c r="P56" s="10">
+        <v>48</v>
+      </c>
+      <c r="Q56" s="10">
+        <v>2640</v>
+      </c>
+      <c r="R56" s="10">
+        <v>1540</v>
+      </c>
+      <c r="S56" s="10">
+        <v>200</v>
+      </c>
+      <c r="T56" s="10">
+        <v>125</v>
+      </c>
+      <c r="U56" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="10">
+        <v>280</v>
+      </c>
+      <c r="E57" s="10">
+        <v>2800</v>
+      </c>
+      <c r="F57" s="10">
+        <v>818</v>
+      </c>
+      <c r="G57" s="10">
+        <v>818</v>
+      </c>
+      <c r="H57" s="10">
+        <v>638</v>
+      </c>
+      <c r="I57" s="10">
+        <v>638</v>
+      </c>
+      <c r="J57" s="10">
+        <v>954</v>
+      </c>
+      <c r="K57" s="10">
+        <v>267</v>
+      </c>
+      <c r="L57" s="10">
+        <v>744</v>
+      </c>
+      <c r="M57" s="10">
+        <v>607</v>
+      </c>
+      <c r="N57" s="10">
+        <v>267</v>
+      </c>
+      <c r="O57" s="10">
+        <v>616</v>
+      </c>
+      <c r="P57" s="10">
+        <v>55</v>
+      </c>
+      <c r="Q57" s="10">
+        <v>3360</v>
+      </c>
+      <c r="R57" s="10">
+        <v>1960</v>
+      </c>
+      <c r="S57" s="10">
+        <v>200</v>
+      </c>
+      <c r="T57" s="10">
+        <v>125</v>
+      </c>
+      <c r="U57" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="10">
+        <v>350</v>
+      </c>
+      <c r="E58" s="10">
+        <v>3500</v>
+      </c>
+      <c r="F58" s="10">
+        <v>873</v>
+      </c>
+      <c r="G58" s="10">
+        <v>873</v>
+      </c>
+      <c r="H58" s="10">
+        <v>680</v>
+      </c>
+      <c r="I58" s="10">
+        <v>680</v>
+      </c>
+      <c r="J58" s="10">
+        <v>1080</v>
+      </c>
+      <c r="K58" s="10">
+        <v>302</v>
+      </c>
+      <c r="L58" s="10">
+        <v>842</v>
+      </c>
+      <c r="M58" s="10">
+        <v>698</v>
+      </c>
+      <c r="N58" s="10">
+        <v>302</v>
+      </c>
+      <c r="O58" s="10">
+        <v>770</v>
+      </c>
+      <c r="P58" s="10">
+        <v>61</v>
+      </c>
+      <c r="Q58" s="10">
+        <v>4200</v>
+      </c>
+      <c r="R58" s="10">
+        <v>2450</v>
+      </c>
+      <c r="S58" s="10">
+        <v>200</v>
+      </c>
+      <c r="T58" s="10">
+        <v>125</v>
+      </c>
+      <c r="U58" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="10">
+        <v>450</v>
+      </c>
+      <c r="E59" s="10">
+        <v>4500</v>
+      </c>
+      <c r="F59" s="10">
+        <v>943</v>
+      </c>
+      <c r="G59" s="10">
+        <v>943</v>
+      </c>
+      <c r="H59" s="10">
+        <v>735</v>
+      </c>
+      <c r="I59" s="10">
+        <v>735</v>
+      </c>
+      <c r="J59" s="10">
+        <v>1260</v>
+      </c>
+      <c r="K59" s="10">
+        <v>352</v>
+      </c>
+      <c r="L59" s="10">
+        <v>982</v>
+      </c>
+      <c r="M59" s="10">
+        <v>828</v>
+      </c>
+      <c r="N59" s="10">
+        <v>352</v>
+      </c>
+      <c r="O59" s="10">
+        <v>990</v>
+      </c>
+      <c r="P59" s="10">
+        <v>69</v>
+      </c>
+      <c r="Q59" s="10">
+        <v>5400</v>
+      </c>
+      <c r="R59" s="10">
+        <v>3150</v>
+      </c>
+      <c r="S59" s="10">
+        <v>200</v>
+      </c>
+      <c r="T59" s="10">
+        <v>125</v>
+      </c>
+      <c r="U59" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60" s="10">
+        <v>550</v>
+      </c>
+      <c r="E60" s="10">
+        <v>5500</v>
+      </c>
+      <c r="F60" s="10">
+        <v>1006</v>
+      </c>
+      <c r="G60" s="10">
+        <v>1006</v>
+      </c>
+      <c r="H60" s="10">
+        <v>784</v>
+      </c>
+      <c r="I60" s="10">
+        <v>784</v>
+      </c>
+      <c r="J60" s="10">
+        <v>1440</v>
+      </c>
+      <c r="K60" s="10">
+        <v>403</v>
+      </c>
+      <c r="L60" s="10">
+        <v>1123</v>
+      </c>
+      <c r="M60" s="10">
+        <v>957</v>
+      </c>
+      <c r="N60" s="10">
+        <v>403</v>
+      </c>
+      <c r="O60" s="10">
+        <v>1210</v>
+      </c>
+      <c r="P60" s="10">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="10">
+        <v>6600</v>
+      </c>
+      <c r="R60" s="10">
+        <v>3850</v>
+      </c>
+      <c r="S60" s="10">
+        <v>250</v>
+      </c>
+      <c r="T60" s="10">
+        <v>160</v>
+      </c>
+      <c r="U60" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C08161-0EC1-4DA3-99D4-994F5A3B8E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16BF9ECA-FCF8-4EF4-B414-62B55B6994E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="614">
   <si>
     <t>OEM</t>
   </si>
@@ -1855,6 +1855,27 @@
   </si>
   <si>
     <t>ELION 2200-N870-60</t>
+  </si>
+  <si>
+    <t>BOY</t>
+  </si>
+  <si>
+    <t>25E</t>
+  </si>
+  <si>
+    <t>35E</t>
+  </si>
+  <si>
+    <t>25E-22</t>
+  </si>
+  <si>
+    <t>25E-32</t>
+  </si>
+  <si>
+    <t>35E-24</t>
+  </si>
+  <si>
+    <t>35E-25</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1992,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2009,6 +2030,11 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2311,12 +2337,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:AA181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="23" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" style="11" customWidth="1"/>
@@ -2346,7 +2372,7 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -2429,7 +2455,7 @@
       <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="13">
@@ -2490,7 +2516,7 @@
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="22" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="13">
@@ -2551,7 +2577,7 @@
       <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="22" t="s">
         <v>334</v>
       </c>
       <c r="D4" s="13">
@@ -2609,7 +2635,7 @@
       <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="22" t="s">
         <v>335</v>
       </c>
       <c r="D5" s="13">
@@ -2667,7 +2693,7 @@
       <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="22" t="s">
         <v>336</v>
       </c>
       <c r="D6" s="13">
@@ -2725,7 +2751,7 @@
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="22" t="s">
         <v>337</v>
       </c>
       <c r="D7" s="13">
@@ -2783,7 +2809,7 @@
       <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="22" t="s">
         <v>338</v>
       </c>
       <c r="D8" s="13">
@@ -2841,7 +2867,7 @@
       <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="22" t="s">
         <v>339</v>
       </c>
       <c r="D9" s="13">
@@ -2899,7 +2925,7 @@
       <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="22" t="s">
         <v>340</v>
       </c>
       <c r="D10" s="13">
@@ -2957,7 +2983,7 @@
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="22" t="s">
         <v>341</v>
       </c>
       <c r="D11" s="13">
@@ -3015,7 +3041,7 @@
       <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="22" t="s">
         <v>342</v>
       </c>
       <c r="D12" s="13">
@@ -3073,7 +3099,7 @@
       <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="22" t="s">
         <v>349</v>
       </c>
       <c r="D13" s="13">
@@ -3131,7 +3157,7 @@
       <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="22" t="s">
         <v>343</v>
       </c>
       <c r="D14" s="13">
@@ -3189,7 +3215,7 @@
       <c r="B15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="22" t="s">
         <v>348</v>
       </c>
       <c r="D15" s="13">
@@ -3247,7 +3273,7 @@
       <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="22" t="s">
         <v>344</v>
       </c>
       <c r="D16" s="13">
@@ -3305,7 +3331,7 @@
       <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="22" t="s">
         <v>347</v>
       </c>
       <c r="D17" s="13">
@@ -3363,7 +3389,7 @@
       <c r="B18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="22" t="s">
         <v>346</v>
       </c>
       <c r="D18" s="13">
@@ -3421,7 +3447,7 @@
       <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="22" t="s">
         <v>350</v>
       </c>
       <c r="D19" s="13">
@@ -3479,7 +3505,7 @@
       <c r="B20" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="22" t="s">
         <v>351</v>
       </c>
       <c r="D20" s="13">
@@ -3537,7 +3563,7 @@
       <c r="B21" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="22" t="s">
         <v>352</v>
       </c>
       <c r="D21" s="13">
@@ -3595,7 +3621,7 @@
       <c r="B22" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="22" t="s">
         <v>353</v>
       </c>
       <c r="D22" s="13">
@@ -3653,7 +3679,7 @@
       <c r="B23" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="22" t="s">
         <v>354</v>
       </c>
       <c r="D23" s="13">
@@ -3711,7 +3737,7 @@
       <c r="B24" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="22" t="s">
         <v>355</v>
       </c>
       <c r="D24" s="13">
@@ -3769,7 +3795,7 @@
       <c r="B25" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="22" t="s">
         <v>357</v>
       </c>
       <c r="D25" s="13">
@@ -3827,7 +3853,7 @@
       <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="22" t="s">
         <v>356</v>
       </c>
       <c r="D26" s="13">
@@ -3885,7 +3911,7 @@
       <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="22" t="s">
         <v>345</v>
       </c>
       <c r="D27" s="13">
@@ -3943,7 +3969,7 @@
       <c r="B28" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="22" t="s">
         <v>319</v>
       </c>
       <c r="D28" s="13">
@@ -4001,7 +4027,7 @@
       <c r="B29" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="22" t="s">
         <v>319</v>
       </c>
       <c r="D29" s="13">
@@ -4059,7 +4085,7 @@
       <c r="B30" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="22" t="s">
         <v>319</v>
       </c>
       <c r="D30" s="13">
@@ -4117,7 +4143,7 @@
       <c r="B31" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="22" t="s">
         <v>320</v>
       </c>
       <c r="D31" s="13">
@@ -4175,7 +4201,7 @@
       <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="22" t="s">
         <v>320</v>
       </c>
       <c r="D32" s="13">
@@ -4233,7 +4259,7 @@
       <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="22" t="s">
         <v>320</v>
       </c>
       <c r="D33" s="13">
@@ -4291,7 +4317,7 @@
       <c r="B34" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="22" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="13">
@@ -4350,7 +4376,7 @@
       <c r="B35" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="22" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="13">
@@ -4409,7 +4435,7 @@
       <c r="B36" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="22" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="13">
@@ -4468,7 +4494,7 @@
       <c r="B37" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="22" t="s">
         <v>471</v>
       </c>
       <c r="D37" s="13">
@@ -4528,7 +4554,7 @@
       <c r="B38" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="22" t="s">
         <v>472</v>
       </c>
       <c r="D38" s="13">
@@ -4588,7 +4614,7 @@
       <c r="B39" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="22" t="s">
         <v>473</v>
       </c>
       <c r="D39" s="13">
@@ -4648,7 +4674,7 @@
       <c r="B40" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="22" t="s">
         <v>475</v>
       </c>
       <c r="D40" s="13">
@@ -4708,7 +4734,7 @@
       <c r="B41" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="22" t="s">
         <v>474</v>
       </c>
       <c r="D41" s="13">
@@ -4768,7 +4794,7 @@
       <c r="B42" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="22" t="s">
         <v>476</v>
       </c>
       <c r="D42" s="13">
@@ -4828,7 +4854,7 @@
       <c r="B43" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="22" t="s">
         <v>477</v>
       </c>
       <c r="D43" s="13">
@@ -4888,7 +4914,7 @@
       <c r="B44" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="22" t="s">
         <v>478</v>
       </c>
       <c r="D44" s="13">
@@ -4948,7 +4974,7 @@
       <c r="B45" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="22" t="s">
         <v>479</v>
       </c>
       <c r="D45" s="13">
@@ -5008,7 +5034,7 @@
       <c r="B46" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="22" t="s">
         <v>480</v>
       </c>
       <c r="D46" s="13">
@@ -5068,7 +5094,7 @@
       <c r="B47" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="22" t="s">
         <v>481</v>
       </c>
       <c r="D47" s="13">
@@ -5128,7 +5154,7 @@
       <c r="B48" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="22" t="s">
         <v>482</v>
       </c>
       <c r="D48" s="13">
@@ -5188,7 +5214,7 @@
       <c r="B49" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="22" t="s">
         <v>483</v>
       </c>
       <c r="D49" s="13">
@@ -5248,7 +5274,7 @@
       <c r="B50" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="22" t="s">
         <v>484</v>
       </c>
       <c r="D50" s="13">
@@ -5308,7 +5334,7 @@
       <c r="B51" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="22" t="s">
         <v>485</v>
       </c>
       <c r="D51" s="13">
@@ -5368,7 +5394,7 @@
       <c r="B52" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="22" t="s">
         <v>486</v>
       </c>
       <c r="D52" s="13">
@@ -5428,7 +5454,7 @@
       <c r="B53" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="22" t="s">
         <v>487</v>
       </c>
       <c r="D53" s="13">
@@ -5488,7 +5514,7 @@
       <c r="B54" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="22" t="s">
         <v>488</v>
       </c>
       <c r="D54" s="13">
@@ -5548,7 +5574,7 @@
       <c r="B55" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="22" t="s">
         <v>489</v>
       </c>
       <c r="D55" s="13">
@@ -5608,7 +5634,7 @@
       <c r="B56" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="22" t="s">
         <v>490</v>
       </c>
       <c r="D56" s="13">
@@ -5668,7 +5694,7 @@
       <c r="B57" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="22" t="s">
         <v>491</v>
       </c>
       <c r="D57" s="13">
@@ -5728,7 +5754,7 @@
       <c r="B58" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="22" t="s">
         <v>492</v>
       </c>
       <c r="D58" s="13">
@@ -5788,7 +5814,7 @@
       <c r="B59" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="22" t="s">
         <v>493</v>
       </c>
       <c r="D59" s="13">
@@ -5848,7 +5874,7 @@
       <c r="B60" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="22" t="s">
         <v>494</v>
       </c>
       <c r="D60" s="13">
@@ -5908,7 +5934,7 @@
       <c r="B61" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="22" t="s">
         <v>495</v>
       </c>
       <c r="D61" s="13">
@@ -5968,7 +5994,7 @@
       <c r="B62" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="22" t="s">
         <v>496</v>
       </c>
       <c r="D62" s="13">
@@ -6028,7 +6054,7 @@
       <c r="B63" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="22" t="s">
         <v>497</v>
       </c>
       <c r="D63" s="13">
@@ -6088,7 +6114,7 @@
       <c r="B64" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="22" t="s">
         <v>499</v>
       </c>
       <c r="D64" s="14">
@@ -6147,7 +6173,7 @@
       <c r="B65" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="22" t="s">
         <v>498</v>
       </c>
       <c r="D65" s="14">
@@ -6206,7 +6232,7 @@
       <c r="B66" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="22" t="s">
         <v>500</v>
       </c>
       <c r="D66" s="13">
@@ -6271,7 +6297,7 @@
       <c r="B67" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="22" t="s">
         <v>501</v>
       </c>
       <c r="D67" s="14">
@@ -6333,7 +6359,7 @@
       <c r="B68" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="22" t="s">
         <v>503</v>
       </c>
       <c r="D68" s="14">
@@ -6393,7 +6419,7 @@
       <c r="B69" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="22" t="s">
         <v>502</v>
       </c>
       <c r="D69" s="14">
@@ -6450,7 +6476,7 @@
       <c r="B70" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="22" t="s">
         <v>504</v>
       </c>
       <c r="D70" s="14">
@@ -6507,7 +6533,7 @@
       <c r="B71" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="22" t="s">
         <v>43</v>
       </c>
       <c r="D71" s="14">
@@ -6567,7 +6593,7 @@
       <c r="B72" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="22" t="s">
         <v>505</v>
       </c>
       <c r="D72" s="15">
@@ -6624,7 +6650,7 @@
       <c r="B73" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="22" t="s">
         <v>507</v>
       </c>
       <c r="D73" s="15">
@@ -6681,7 +6707,7 @@
       <c r="B74" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="22" t="s">
         <v>45</v>
       </c>
       <c r="D74" s="15">
@@ -6741,7 +6767,7 @@
       <c r="B75" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="22" t="s">
         <v>506</v>
       </c>
       <c r="D75" s="15">
@@ -6798,7 +6824,7 @@
       <c r="B76" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="22" t="s">
         <v>508</v>
       </c>
       <c r="D76" s="15">
@@ -6858,7 +6884,7 @@
       <c r="B77" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="22" t="s">
         <v>47</v>
       </c>
       <c r="D77" s="15">
@@ -6915,7 +6941,7 @@
       <c r="B78" t="s">
         <v>31</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="22" t="s">
         <v>509</v>
       </c>
       <c r="D78" s="15">
@@ -6972,7 +6998,7 @@
       <c r="B79" t="s">
         <v>439</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="22" t="s">
         <v>437</v>
       </c>
       <c r="D79">
@@ -7031,7 +7057,7 @@
       <c r="B80" t="s">
         <v>439</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="22" t="s">
         <v>437</v>
       </c>
       <c r="D80">
@@ -7090,7 +7116,7 @@
       <c r="B81" t="s">
         <v>439</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="22" t="s">
         <v>437</v>
       </c>
       <c r="D81">
@@ -7149,7 +7175,7 @@
       <c r="B82" t="s">
         <v>439</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="22" t="s">
         <v>438</v>
       </c>
       <c r="D82">
@@ -7208,7 +7234,7 @@
       <c r="B83" t="s">
         <v>439</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="22" t="s">
         <v>438</v>
       </c>
       <c r="D83">
@@ -7267,7 +7293,7 @@
       <c r="B84" t="s">
         <v>439</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="22" t="s">
         <v>438</v>
       </c>
       <c r="D84">
@@ -7326,7 +7352,7 @@
       <c r="B85" t="s">
         <v>512</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="22" t="s">
         <v>510</v>
       </c>
       <c r="D85">
@@ -7377,7 +7403,7 @@
       <c r="B86" t="s">
         <v>512</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="22" t="s">
         <v>511</v>
       </c>
       <c r="D86">
@@ -7428,7 +7454,7 @@
       <c r="B87" t="s">
         <v>460</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="22" t="s">
         <v>514</v>
       </c>
       <c r="D87">
@@ -7478,7 +7504,7 @@
       <c r="B88" t="s">
         <v>460</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="22" t="s">
         <v>515</v>
       </c>
       <c r="D88">
@@ -7528,7 +7554,7 @@
       <c r="B89" t="s">
         <v>460</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="22" t="s">
         <v>516</v>
       </c>
       <c r="D89">
@@ -7578,7 +7604,7 @@
       <c r="B90" t="s">
         <v>460</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="22" t="s">
         <v>547</v>
       </c>
       <c r="D90">
@@ -7628,7 +7654,7 @@
       <c r="B91" t="s">
         <v>460</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="22" t="s">
         <v>517</v>
       </c>
       <c r="D91">
@@ -7678,7 +7704,7 @@
       <c r="B92" t="s">
         <v>460</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="22" t="s">
         <v>548</v>
       </c>
       <c r="D92">
@@ -7728,7 +7754,7 @@
       <c r="B93" t="s">
         <v>460</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="22" t="s">
         <v>518</v>
       </c>
       <c r="D93">
@@ -7778,7 +7804,7 @@
       <c r="B94" t="s">
         <v>460</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="22" t="s">
         <v>519</v>
       </c>
       <c r="D94">
@@ -7828,7 +7854,7 @@
       <c r="B95" t="s">
         <v>460</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="22" t="s">
         <v>520</v>
       </c>
       <c r="D95">
@@ -7878,7 +7904,7 @@
       <c r="B96" t="s">
         <v>460</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="22" t="s">
         <v>521</v>
       </c>
       <c r="D96">
@@ -7928,7 +7954,7 @@
       <c r="B97" t="s">
         <v>460</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="22" t="s">
         <v>522</v>
       </c>
       <c r="D97">
@@ -7978,7 +8004,7 @@
       <c r="B98" t="s">
         <v>460</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="22" t="s">
         <v>523</v>
       </c>
       <c r="D98">
@@ -8028,7 +8054,7 @@
       <c r="B99" t="s">
         <v>460</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="22" t="s">
         <v>524</v>
       </c>
       <c r="D99">
@@ -8078,7 +8104,7 @@
       <c r="B100" t="s">
         <v>460</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="22" t="s">
         <v>525</v>
       </c>
       <c r="D100">
@@ -8128,7 +8154,7 @@
       <c r="B101" t="s">
         <v>460</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="22" t="s">
         <v>526</v>
       </c>
       <c r="D101">
@@ -8178,7 +8204,7 @@
       <c r="B102" t="s">
         <v>460</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="22" t="s">
         <v>527</v>
       </c>
       <c r="D102">
@@ -8228,7 +8254,7 @@
       <c r="B103" t="s">
         <v>460</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="22" t="s">
         <v>528</v>
       </c>
       <c r="D103">
@@ -8278,7 +8304,7 @@
       <c r="B104" t="s">
         <v>460</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="22" t="s">
         <v>549</v>
       </c>
       <c r="D104">
@@ -8328,7 +8354,7 @@
       <c r="B105" t="s">
         <v>16</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D105">
@@ -8394,7 +8420,7 @@
       <c r="B106" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="22" t="s">
         <v>456</v>
       </c>
       <c r="D106">
@@ -8475,7 +8501,7 @@
       <c r="B107" t="s">
         <v>191</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="22" t="s">
         <v>586</v>
       </c>
       <c r="D107">
@@ -8534,7 +8560,7 @@
       <c r="B108" t="s">
         <v>191</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="22" t="s">
         <v>587</v>
       </c>
       <c r="D108">
@@ -8593,7 +8619,7 @@
       <c r="B109" t="s">
         <v>191</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="22" t="s">
         <v>588</v>
       </c>
       <c r="D109">
@@ -8652,7 +8678,7 @@
       <c r="B110" t="s">
         <v>191</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="22" t="s">
         <v>589</v>
       </c>
       <c r="D110">
@@ -8711,7 +8737,7 @@
       <c r="B111" t="s">
         <v>191</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="22" t="s">
         <v>590</v>
       </c>
       <c r="D111">
@@ -8770,7 +8796,7 @@
       <c r="B112" t="s">
         <v>191</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="22" t="s">
         <v>591</v>
       </c>
       <c r="D112">
@@ -8829,7 +8855,7 @@
       <c r="B113" t="s">
         <v>191</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="22" t="s">
         <v>592</v>
       </c>
       <c r="D113">
@@ -8888,7 +8914,7 @@
       <c r="B114" t="s">
         <v>191</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="22" t="s">
         <v>264</v>
       </c>
       <c r="D114">
@@ -8956,7 +8982,7 @@
       <c r="B115" t="s">
         <v>191</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="22" t="s">
         <v>264</v>
       </c>
       <c r="D115">
@@ -9024,7 +9050,7 @@
       <c r="B116" t="s">
         <v>191</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="22" t="s">
         <v>593</v>
       </c>
       <c r="D116">
@@ -9092,7 +9118,7 @@
       <c r="B117" t="s">
         <v>191</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="22" t="s">
         <v>594</v>
       </c>
       <c r="D117">
@@ -9160,7 +9186,7 @@
       <c r="B118" t="s">
         <v>191</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="22" t="s">
         <v>596</v>
       </c>
       <c r="D118">
@@ -9228,7 +9254,7 @@
       <c r="B119" t="s">
         <v>191</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="22" t="s">
         <v>595</v>
       </c>
       <c r="D119">
@@ -9296,7 +9322,7 @@
       <c r="B120" t="s">
         <v>191</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="22" t="s">
         <v>597</v>
       </c>
       <c r="D120">
@@ -9364,7 +9390,7 @@
       <c r="B121" t="s">
         <v>191</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="22" t="s">
         <v>598</v>
       </c>
       <c r="D121">
@@ -9432,7 +9458,7 @@
       <c r="B122" t="s">
         <v>191</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="22" t="s">
         <v>599</v>
       </c>
       <c r="D122">
@@ -9500,7 +9526,7 @@
       <c r="B123" t="s">
         <v>191</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="22" t="s">
         <v>600</v>
       </c>
       <c r="D123">
@@ -9568,7 +9594,7 @@
       <c r="B124" t="s">
         <v>191</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="22" t="s">
         <v>584</v>
       </c>
       <c r="D124">
@@ -9636,7 +9662,7 @@
       <c r="B125" t="s">
         <v>191</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="22" t="s">
         <v>585</v>
       </c>
       <c r="D125">
@@ -9704,7 +9730,7 @@
       <c r="B126" t="s">
         <v>191</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="22" t="s">
         <v>605</v>
       </c>
       <c r="D126">
@@ -9772,7 +9798,7 @@
       <c r="B127" t="s">
         <v>191</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="22" t="s">
         <v>606</v>
       </c>
       <c r="D127">
@@ -9840,7 +9866,7 @@
       <c r="B128" t="s">
         <v>191</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="22" t="s">
         <v>601</v>
       </c>
       <c r="D128">
@@ -9908,7 +9934,7 @@
       <c r="B129" t="s">
         <v>191</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="22" t="s">
         <v>602</v>
       </c>
       <c r="D129">
@@ -9976,7 +10002,7 @@
       <c r="B130" t="s">
         <v>191</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="22" t="s">
         <v>603</v>
       </c>
       <c r="D130">
@@ -10044,7 +10070,7 @@
       <c r="B131" t="s">
         <v>191</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="22" t="s">
         <v>604</v>
       </c>
       <c r="D131">
@@ -10112,7 +10138,7 @@
       <c r="B132" t="s">
         <v>91</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="22" t="s">
         <v>550</v>
       </c>
       <c r="D132">
@@ -10168,7 +10194,7 @@
       <c r="B133" t="s">
         <v>91</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="22" t="s">
         <v>551</v>
       </c>
       <c r="D133">
@@ -10224,7 +10250,7 @@
       <c r="B134" t="s">
         <v>91</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="22" t="s">
         <v>553</v>
       </c>
       <c r="D134">
@@ -10280,7 +10306,7 @@
       <c r="B135" t="s">
         <v>91</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="22" t="s">
         <v>554</v>
       </c>
       <c r="D135">
@@ -10336,7 +10362,7 @@
       <c r="B136" t="s">
         <v>91</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="22" t="s">
         <v>555</v>
       </c>
       <c r="D136">
@@ -10392,7 +10418,7 @@
       <c r="B137" t="s">
         <v>91</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="22" t="s">
         <v>556</v>
       </c>
       <c r="D137">
@@ -10448,7 +10474,7 @@
       <c r="B138" t="s">
         <v>91</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="22" t="s">
         <v>557</v>
       </c>
       <c r="D138">
@@ -10504,7 +10530,7 @@
       <c r="B139" t="s">
         <v>91</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="22" t="s">
         <v>558</v>
       </c>
       <c r="D139">
@@ -10560,7 +10586,7 @@
       <c r="B140" t="s">
         <v>91</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="22" t="s">
         <v>559</v>
       </c>
       <c r="D140">
@@ -10616,7 +10642,7 @@
       <c r="B141" t="s">
         <v>91</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="22" t="s">
         <v>560</v>
       </c>
       <c r="D141">
@@ -10672,7 +10698,7 @@
       <c r="B142" t="s">
         <v>91</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="22" t="s">
         <v>561</v>
       </c>
       <c r="D142">
@@ -10728,7 +10754,7 @@
       <c r="B143" t="s">
         <v>91</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="22" t="s">
         <v>562</v>
       </c>
       <c r="D143">
@@ -10784,7 +10810,7 @@
       <c r="B144" t="s">
         <v>570</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="22" t="s">
         <v>563</v>
       </c>
       <c r="D144">
@@ -10846,7 +10872,7 @@
       <c r="B145" t="s">
         <v>570</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="22" t="s">
         <v>564</v>
       </c>
       <c r="D145">
@@ -10908,7 +10934,7 @@
       <c r="B146" t="s">
         <v>570</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="22" t="s">
         <v>566</v>
       </c>
       <c r="D146">
@@ -10970,7 +10996,7 @@
       <c r="B147" t="s">
         <v>570</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C147" s="22" t="s">
         <v>565</v>
       </c>
       <c r="D147">
@@ -11032,7 +11058,7 @@
       <c r="B148" t="s">
         <v>570</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="C148" s="22" t="s">
         <v>568</v>
       </c>
       <c r="D148">
@@ -11094,7 +11120,7 @@
       <c r="B149" t="s">
         <v>570</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="22" t="s">
         <v>569</v>
       </c>
       <c r="D149">
@@ -11156,7 +11182,7 @@
       <c r="B150" t="s">
         <v>570</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" s="22" t="s">
         <v>572</v>
       </c>
       <c r="D150">
@@ -11218,7 +11244,7 @@
       <c r="B151" t="s">
         <v>570</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" s="22" t="s">
         <v>571</v>
       </c>
       <c r="D151">
@@ -11280,7 +11306,7 @@
       <c r="B152" t="s">
         <v>570</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" s="22" t="s">
         <v>574</v>
       </c>
       <c r="D152">
@@ -11342,7 +11368,7 @@
       <c r="B153" t="s">
         <v>570</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="C153" s="22" t="s">
         <v>573</v>
       </c>
       <c r="D153">
@@ -11404,7 +11430,7 @@
       <c r="B154" t="s">
         <v>570</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="22" t="s">
         <v>577</v>
       </c>
       <c r="D154">
@@ -11466,7 +11492,7 @@
       <c r="B155" t="s">
         <v>570</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C155" s="22" t="s">
         <v>578</v>
       </c>
       <c r="D155">
@@ -11528,7 +11554,7 @@
       <c r="B156" t="s">
         <v>570</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C156" s="22" t="s">
         <v>575</v>
       </c>
       <c r="D156">
@@ -11590,7 +11616,7 @@
       <c r="B157" t="s">
         <v>570</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C157" s="22" t="s">
         <v>576</v>
       </c>
       <c r="D157">
@@ -11652,7 +11678,7 @@
       <c r="B158" t="s">
         <v>570</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" s="22" t="s">
         <v>579</v>
       </c>
       <c r="D158">
@@ -11714,7 +11740,7 @@
       <c r="B159" t="s">
         <v>570</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C159" s="22" t="s">
         <v>580</v>
       </c>
       <c r="D159">
@@ -11776,7 +11802,7 @@
       <c r="B160" t="s">
         <v>330</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" s="22" t="s">
         <v>332</v>
       </c>
       <c r="D160">
@@ -11835,7 +11861,7 @@
       <c r="B161" t="s">
         <v>330</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="C161" s="22" t="s">
         <v>333</v>
       </c>
       <c r="D161">
@@ -11894,7 +11920,7 @@
       <c r="B162" t="s">
         <v>322</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="C162" s="22" t="s">
         <v>454</v>
       </c>
       <c r="D162">
@@ -11960,7 +11986,7 @@
       <c r="B163" t="s">
         <v>322</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="C163" s="22" t="s">
         <v>455</v>
       </c>
       <c r="D163">
@@ -12026,7 +12052,7 @@
       <c r="B164" t="s">
         <v>322</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="C164" s="22" t="s">
         <v>445</v>
       </c>
       <c r="D164">
@@ -12093,7 +12119,7 @@
       <c r="B165" t="s">
         <v>322</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="C165" s="22" t="s">
         <v>446</v>
       </c>
       <c r="D165">
@@ -12160,7 +12186,7 @@
       <c r="B166" t="s">
         <v>322</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="C166" s="22" t="s">
         <v>447</v>
       </c>
       <c r="D166">
@@ -12227,7 +12253,7 @@
       <c r="B167" t="s">
         <v>322</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="C167" s="22" t="s">
         <v>448</v>
       </c>
       <c r="D167">
@@ -12294,7 +12320,7 @@
       <c r="B168" t="s">
         <v>322</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="C168" s="22" t="s">
         <v>449</v>
       </c>
       <c r="D168">
@@ -12360,7 +12386,7 @@
       <c r="B169" t="s">
         <v>322</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C169" s="22" t="s">
         <v>450</v>
       </c>
       <c r="D169">
@@ -12426,7 +12452,7 @@
       <c r="B170" t="s">
         <v>322</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="C170" s="22" t="s">
         <v>451</v>
       </c>
       <c r="D170">
@@ -12492,7 +12518,7 @@
       <c r="B171" t="s">
         <v>322</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C171" s="22" t="s">
         <v>452</v>
       </c>
       <c r="D171">
@@ -12558,7 +12584,7 @@
       <c r="B172" t="s">
         <v>322</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="C172" s="22" t="s">
         <v>453</v>
       </c>
       <c r="D172">
@@ -12624,7 +12650,7 @@
       <c r="B173" t="s">
         <v>322</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="C173" s="22" t="s">
         <v>323</v>
       </c>
       <c r="D173">
@@ -12678,7 +12704,7 @@
       <c r="B174" t="s">
         <v>322</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="C174" s="22" t="s">
         <v>581</v>
       </c>
       <c r="D174">
@@ -12743,7 +12769,7 @@
       <c r="B175" t="s">
         <v>322</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="C175" s="22" t="s">
         <v>582</v>
       </c>
       <c r="D175">
@@ -12808,7 +12834,7 @@
       <c r="B176" t="s">
         <v>322</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="C176" s="22" t="s">
         <v>583</v>
       </c>
       <c r="D176">
@@ -12873,7 +12899,7 @@
       <c r="B177" t="s">
         <v>326</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="C177" s="22" t="s">
         <v>327</v>
       </c>
       <c r="D177">
@@ -12914,6 +12940,242 @@
       </c>
       <c r="X177">
         <v>150</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>607</v>
+      </c>
+      <c r="B178" t="s">
+        <v>608</v>
+      </c>
+      <c r="C178" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="D178">
+        <v>28</v>
+      </c>
+      <c r="E178">
+        <v>250</v>
+      </c>
+      <c r="F178" s="11">
+        <v>254</v>
+      </c>
+      <c r="G178" s="11">
+        <v>240</v>
+      </c>
+      <c r="J178" s="11">
+        <v>254</v>
+      </c>
+      <c r="K178" s="11">
+        <v>240</v>
+      </c>
+      <c r="L178" s="20">
+        <v>10</v>
+      </c>
+      <c r="N178">
+        <v>40</v>
+      </c>
+      <c r="O178">
+        <v>400</v>
+      </c>
+      <c r="P178">
+        <v>200</v>
+      </c>
+      <c r="R178">
+        <v>200</v>
+      </c>
+      <c r="T178">
+        <v>27.7</v>
+      </c>
+      <c r="U178">
+        <v>22</v>
+      </c>
+      <c r="W178">
+        <v>150</v>
+      </c>
+      <c r="X178">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>607</v>
+      </c>
+      <c r="B179" t="s">
+        <v>608</v>
+      </c>
+      <c r="C179" s="22" t="s">
+        <v>611</v>
+      </c>
+      <c r="D179">
+        <v>28</v>
+      </c>
+      <c r="E179">
+        <v>250</v>
+      </c>
+      <c r="F179" s="11">
+        <v>254</v>
+      </c>
+      <c r="G179" s="11">
+        <v>240</v>
+      </c>
+      <c r="J179" s="11">
+        <v>254</v>
+      </c>
+      <c r="K179" s="11">
+        <v>240</v>
+      </c>
+      <c r="L179" s="20">
+        <v>10</v>
+      </c>
+      <c r="N179">
+        <v>40</v>
+      </c>
+      <c r="O179">
+        <v>400</v>
+      </c>
+      <c r="P179">
+        <v>200</v>
+      </c>
+      <c r="R179">
+        <v>200</v>
+      </c>
+      <c r="T179">
+        <v>69.5</v>
+      </c>
+      <c r="U179">
+        <v>32</v>
+      </c>
+      <c r="W179">
+        <v>150</v>
+      </c>
+      <c r="X179">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>607</v>
+      </c>
+      <c r="B180" t="s">
+        <v>609</v>
+      </c>
+      <c r="C180" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="D180">
+        <v>38.5</v>
+      </c>
+      <c r="E180">
+        <v>350</v>
+      </c>
+      <c r="F180" s="11">
+        <v>425</v>
+      </c>
+      <c r="G180" s="11">
+        <v>400</v>
+      </c>
+      <c r="J180" s="11">
+        <v>280</v>
+      </c>
+      <c r="K180" s="11">
+        <v>254</v>
+      </c>
+      <c r="L180" s="20">
+        <v>11.02</v>
+      </c>
+      <c r="M180" s="20">
+        <v>10</v>
+      </c>
+      <c r="N180">
+        <v>40</v>
+      </c>
+      <c r="O180">
+        <v>500</v>
+      </c>
+      <c r="P180">
+        <v>200</v>
+      </c>
+      <c r="R180">
+        <v>300</v>
+      </c>
+      <c r="T180">
+        <v>5.6</v>
+      </c>
+      <c r="U180">
+        <v>14</v>
+      </c>
+      <c r="V180">
+        <v>350</v>
+      </c>
+      <c r="W180">
+        <v>220</v>
+      </c>
+      <c r="X180">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>607</v>
+      </c>
+      <c r="B181" t="s">
+        <v>609</v>
+      </c>
+      <c r="C181" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="D181">
+        <v>38.5</v>
+      </c>
+      <c r="E181">
+        <v>350</v>
+      </c>
+      <c r="F181" s="11">
+        <v>425</v>
+      </c>
+      <c r="G181" s="11">
+        <v>400</v>
+      </c>
+      <c r="J181" s="11">
+        <v>280</v>
+      </c>
+      <c r="K181" s="11">
+        <v>254</v>
+      </c>
+      <c r="L181" s="20">
+        <v>11.02</v>
+      </c>
+      <c r="M181" s="20">
+        <v>10</v>
+      </c>
+      <c r="N181">
+        <v>40</v>
+      </c>
+      <c r="O181">
+        <v>500</v>
+      </c>
+      <c r="P181">
+        <v>200</v>
+      </c>
+      <c r="R181">
+        <v>300</v>
+      </c>
+      <c r="T181">
+        <v>69.5</v>
+      </c>
+      <c r="U181">
+        <v>32</v>
+      </c>
+      <c r="V181">
+        <v>350</v>
+      </c>
+      <c r="W181">
+        <v>220</v>
+      </c>
+      <c r="X181">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/machines_clean.xlsx
+++ b/machines_clean.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\moldmatch-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16BF9ECA-FCF8-4EF4-B414-62B55B6994E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00E41AB-DB7F-4D99-99E1-500B7657DCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="616">
   <si>
     <t>OEM</t>
   </si>
@@ -1876,6 +1876,12 @@
   </si>
   <si>
     <t>35E-25</t>
+  </si>
+  <si>
+    <t>Babyplast</t>
+  </si>
+  <si>
+    <t>6/10</t>
   </si>
 </sst>
 </file>
@@ -2337,7 +2343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA181"/>
+  <dimension ref="A1:AA183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -13178,6 +13184,56 @@
         <v>80</v>
       </c>
     </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>614</v>
+      </c>
+      <c r="B182" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="D182">
+        <v>7</v>
+      </c>
+      <c r="E182">
+        <v>62.5</v>
+      </c>
+      <c r="F182" s="11">
+        <v>75</v>
+      </c>
+      <c r="G182" s="11">
+        <v>75</v>
+      </c>
+      <c r="J182" s="11">
+        <v>75</v>
+      </c>
+      <c r="K182" s="11">
+        <v>75</v>
+      </c>
+      <c r="O182">
+        <v>140</v>
+      </c>
+      <c r="P182">
+        <v>70</v>
+      </c>
+      <c r="R182">
+        <v>110</v>
+      </c>
+      <c r="S182">
+        <v>30</v>
+      </c>
+      <c r="T182">
+        <v>11</v>
+      </c>
+      <c r="U182">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B183" s="23"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AA174">
     <sortCondition ref="A3:A174"/>
